--- a/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_TecnolGestAmbiental_VNAL.xlsx
+++ b/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_TecnolGestAmbiental_VNAL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/FORMATOS RA CICLO UNO RC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/FORMATOS RA CICLO UNO RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{65619CD8-07B6-41FC-BB7F-A5D9158D239C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA5267D1-6D13-4641-A447-9A60BCCACEE3}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{65619CD8-07B6-41FC-BB7F-A5D9158D239C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{576D446A-70C4-4F4D-8D61-7BBDA6778396}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Paso 3 Redacción RA '!$A$2:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Paso 4 Estrategias mesocurricu'!$A$2:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Paso 5 Estrategias micro'!$A$1:$Q$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Paso 5 Estrategias micro'!$A$2:$R$139</definedName>
     <definedName name="actitudinalB" localSheetId="4">Tabla5785[ActitudinalB]</definedName>
     <definedName name="actitudinalB">Tabla5785[ActitudinalB]</definedName>
     <definedName name="ActitudinalBAK">'Taxonomias para RA'!$AC$3:$AG$3</definedName>
@@ -4187,31 +4187,78 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4226,35 +4273,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4265,76 +4321,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8429,23 +8429,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FA7EDF-246F-4EE0-BFE4-7EACACD45C48}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.26953125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.21875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="49.81640625" style="21" customWidth="1"/>
-    <col min="4" max="4" width="51.81640625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="27.54296875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="21" customWidth="1"/>
+    <col min="3" max="3" width="49.77734375" style="21" customWidth="1"/>
+    <col min="4" max="4" width="51.77734375" style="21" customWidth="1"/>
+    <col min="5" max="5" width="27.5546875" style="21" customWidth="1"/>
     <col min="6" max="6" width="36" style="12" customWidth="1"/>
     <col min="7" max="7" width="51" style="21" customWidth="1"/>
-    <col min="8" max="8" width="23.54296875" style="21" customWidth="1"/>
-    <col min="9" max="9" width="62.1796875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="25.7265625" style="21" customWidth="1"/>
-    <col min="11" max="11" width="47.7265625" style="21" customWidth="1"/>
-    <col min="12" max="16384" width="76.26953125" style="21"/>
+    <col min="8" max="8" width="23.5546875" style="21" customWidth="1"/>
+    <col min="9" max="9" width="62.21875" style="21" customWidth="1"/>
+    <col min="10" max="10" width="25.77734375" style="21" customWidth="1"/>
+    <col min="11" max="11" width="47.77734375" style="21" customWidth="1"/>
+    <col min="12" max="16384" width="76.21875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="19" customFormat="1" ht="55.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="19" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -8458,21 +8458,21 @@
       <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="121" t="s">
+      <c r="E1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121" t="s">
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
       <c r="K1" s="97" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>7</v>
       </c>
@@ -8507,17 +8507,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="66" x14ac:dyDescent="0.35">
-      <c r="A3" s="122" t="s">
+    <row r="3" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+      <c r="A3" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="119" t="s">
+      <c r="C3" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="119" t="s">
+      <c r="D3" s="138" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="21" t="s">
@@ -8529,24 +8529,24 @@
       <c r="G3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="119" t="s">
+      <c r="H3" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="119" t="s">
+      <c r="I3" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="119" t="s">
+      <c r="J3" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="120" t="s">
+      <c r="K3" s="144" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="49.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="122"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
+    <row r="4" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+      <c r="A4" s="120"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
       <c r="E4" s="21" t="s">
         <v>29</v>
       </c>
@@ -8556,16 +8556,16 @@
       <c r="G4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
-    </row>
-    <row r="5" spans="1:11" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="122"/>
-      <c r="B5" s="122"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="144"/>
+    </row>
+    <row r="5" spans="1:11" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="120"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
       <c r="E5" s="47" t="s">
         <v>32</v>
       </c>
@@ -8575,16 +8575,16 @@
       <c r="G5" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="120"/>
-    </row>
-    <row r="6" spans="1:11" ht="66" x14ac:dyDescent="0.35">
-      <c r="A6" s="122"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="144"/>
+    </row>
+    <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="120"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
       <c r="E6" s="21" t="s">
         <v>35</v>
       </c>
@@ -8594,51 +8594,51 @@
       <c r="G6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="120"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+      <c r="K6" s="144"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E7" s="22"/>
       <c r="F7" s="16"/>
       <c r="G7" s="22"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="20"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="F15" s="21"/>
     </row>
   </sheetData>
@@ -8666,30 +8666,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C1850E-A9C8-4F69-8E80-DEAF9721FFBF}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="19" customWidth="1"/>
     <col min="2" max="2" width="18" style="21" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" style="21" customWidth="1"/>
     <col min="4" max="4" width="34" style="21" customWidth="1"/>
-    <col min="5" max="5" width="45.1796875" style="21" customWidth="1"/>
-    <col min="6" max="6" width="90.453125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="32.453125" style="21" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="21"/>
+    <col min="5" max="5" width="45.21875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="90.44140625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" style="21" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="123" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-    </row>
-    <row r="2" spans="1:7" s="31" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+    </row>
+    <row r="2" spans="1:7" s="31" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
         <v>39</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="36" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="36" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>46</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="20" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="20" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="45">
         <v>2</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="91" customFormat="1" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" s="91" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="104">
         <v>3</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>4</v>
       </c>
@@ -8827,46 +8827,46 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C10"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
       <c r="F11" s="20"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C12" s="22"/>
       <c r="E12" s="22"/>
       <c r="F12" s="20"/>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" s="21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D21" s="22"/>
     </row>
   </sheetData>
@@ -8889,21 +8889,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAF649-42F4-466A-BE11-44357078F961}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="77.453125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="19" customWidth="1"/>
+    <col min="1" max="1" width="77.44140625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="19" customWidth="1"/>
     <col min="3" max="3" width="23" style="21" customWidth="1"/>
-    <col min="4" max="4" width="30.7265625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="25.54296875" style="21" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.81640625" style="21" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="27.453125" style="12" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" style="21" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" style="21" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" style="21" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" style="12" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="12" customWidth="1"/>
     <col min="9" max="9" width="72" style="46" customWidth="1"/>
-    <col min="10" max="16384" width="11.453125" style="16"/>
+    <col min="10" max="16384" width="11.44140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="40" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="40" customFormat="1" ht="48" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>65</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="41" t="s">
         <v>74</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>54</v>
       </c>
@@ -8990,7 +8990,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>54</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="47" t="s">
         <v>54</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="66" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.5">
       <c r="A6" s="53" t="s">
         <v>57</v>
       </c>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K6" s="72"/>
     </row>
-    <row r="7" spans="1:11" ht="66" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.5">
       <c r="A7" s="21" t="s">
         <v>57</v>
       </c>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="K7" s="72"/>
     </row>
-    <row r="8" spans="1:11" ht="83" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" ht="90.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="47" t="s">
         <v>57</v>
       </c>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="K8" s="72"/>
     </row>
-    <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" ht="54" x14ac:dyDescent="0.5">
       <c r="A9" s="21" t="s">
         <v>95</v>
       </c>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="K9" s="72"/>
     </row>
-    <row r="10" spans="1:11" ht="49.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" ht="54" x14ac:dyDescent="0.5">
       <c r="A10" s="21" t="s">
         <v>95</v>
       </c>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="K10" s="72"/>
     </row>
-    <row r="11" spans="1:11" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="47" t="s">
         <v>95</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>62</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -9266,7 +9266,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="16"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -9276,7 +9276,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="16"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -9286,7 +9286,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="16"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -9296,7 +9296,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -9306,7 +9306,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="16"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -9316,7 +9316,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
@@ -9363,17 +9363,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F726B80-E6B4-4ED4-A764-E59AF4E18393}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="70" style="12" customWidth="1"/>
-    <col min="2" max="2" width="49.1796875" style="55" customWidth="1"/>
-    <col min="3" max="4" width="55.54296875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="39.1796875" style="12" customWidth="1"/>
-    <col min="6" max="6" width="47.7265625" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="11.453125" style="12"/>
+    <col min="2" max="2" width="49.21875" style="55" customWidth="1"/>
+    <col min="3" max="4" width="55.5546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="47.77734375" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>107</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
         <v>113</v>
       </c>
@@ -9413,443 +9413,431 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="106" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="134" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="157" t="s">
         <v>121</v>
       </c>
       <c r="D3" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="127" t="s">
+      <c r="E3" s="137" t="s">
         <v>123</v>
       </c>
       <c r="F3" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="143"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="158"/>
       <c r="D4" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="119"/>
+      <c r="E4" s="138"/>
       <c r="F4" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="140"/>
-      <c r="C5" s="143"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="158"/>
       <c r="D5" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="119"/>
+      <c r="E5" s="138"/>
       <c r="F5" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="140"/>
-      <c r="C6" s="143"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="158"/>
       <c r="D6" s="50"/>
-      <c r="E6" s="119"/>
+      <c r="E6" s="138"/>
       <c r="F6" s="21"/>
     </row>
-    <row r="7" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="140"/>
-      <c r="C7" s="143"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="158"/>
       <c r="D7" s="50"/>
-      <c r="E7" s="119"/>
+      <c r="E7" s="138"/>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="141"/>
-      <c r="C8" s="144"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="159"/>
       <c r="D8" s="51"/>
-      <c r="E8" s="126"/>
+      <c r="E8" s="139"/>
       <c r="F8" s="47"/>
     </row>
-    <row r="9" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="135" t="s">
+      <c r="B9" s="153" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="125" t="s">
+      <c r="C9" s="155" t="s">
         <v>133</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="127" t="s">
+      <c r="E9" s="137" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="136"/>
-      <c r="C10" s="119"/>
+      <c r="B10" s="147"/>
+      <c r="C10" s="138"/>
       <c r="D10" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="119"/>
+      <c r="E10" s="138"/>
       <c r="F10" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="136"/>
-      <c r="C11" s="119"/>
+      <c r="B11" s="147"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E11" s="119"/>
+      <c r="E11" s="138"/>
       <c r="F11" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="B12" s="136"/>
-      <c r="C12" s="119"/>
-      <c r="E12" s="119"/>
+      <c r="B12" s="147"/>
+      <c r="C12" s="138"/>
+      <c r="E12" s="138"/>
       <c r="F12" s="21"/>
     </row>
-    <row r="13" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="156"/>
       <c r="D13" s="92"/>
-      <c r="E13" s="138"/>
+      <c r="E13" s="156"/>
       <c r="F13" s="92"/>
     </row>
-    <row r="14" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="B14" s="135" t="s">
+      <c r="B14" s="153" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="155" t="s">
         <v>136</v>
       </c>
       <c r="D14" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="127" t="s">
+      <c r="E14" s="137" t="s">
         <v>137</v>
       </c>
       <c r="F14" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="119"/>
+      <c r="B15" s="147"/>
+      <c r="C15" s="138"/>
       <c r="D15" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="119"/>
+      <c r="E15" s="138"/>
       <c r="F15" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A16" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="136"/>
-      <c r="C16" s="119"/>
+      <c r="B16" s="147"/>
+      <c r="C16" s="138"/>
       <c r="D16" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E16" s="119"/>
+      <c r="E16" s="138"/>
       <c r="F16" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="119"/>
-      <c r="E17" s="119"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="138"/>
+      <c r="E17" s="138"/>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="137"/>
-      <c r="C18" s="138"/>
+      <c r="B18" s="154"/>
+      <c r="C18" s="156"/>
       <c r="D18" s="92"/>
-      <c r="E18" s="138"/>
+      <c r="E18" s="156"/>
       <c r="F18" s="92"/>
     </row>
-    <row r="19" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="106" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="135" t="s">
+      <c r="B19" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="155" t="s">
         <v>139</v>
       </c>
       <c r="D19" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="127" t="s">
+      <c r="E19" s="137" t="s">
         <v>140</v>
       </c>
       <c r="F19" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A20" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="119"/>
+      <c r="B20" s="147"/>
+      <c r="C20" s="138"/>
       <c r="D20" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="119"/>
+      <c r="E20" s="138"/>
       <c r="F20" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="136"/>
-      <c r="C21" s="119"/>
+      <c r="B21" s="147"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="119"/>
+      <c r="E21" s="138"/>
       <c r="F21" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A22" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="136"/>
-      <c r="C22" s="119"/>
-      <c r="E22" s="119"/>
+      <c r="B22" s="147"/>
+      <c r="C22" s="138"/>
+      <c r="E22" s="138"/>
       <c r="F22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="137"/>
-      <c r="C23" s="138"/>
+      <c r="B23" s="154"/>
+      <c r="C23" s="156"/>
       <c r="D23" s="92"/>
-      <c r="E23" s="138"/>
+      <c r="E23" s="156"/>
       <c r="F23" s="92"/>
     </row>
-    <row r="24" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="133" t="s">
+      <c r="B24" s="160" t="s">
         <v>141</v>
       </c>
-      <c r="C24" s="134" t="s">
+      <c r="C24" s="161" t="s">
         <v>142</v>
       </c>
       <c r="D24" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E24" s="125" t="s">
+      <c r="E24" s="155" t="s">
         <v>143</v>
       </c>
       <c r="F24" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="129"/>
-      <c r="C25" s="120"/>
+      <c r="B25" s="141"/>
+      <c r="C25" s="144"/>
       <c r="D25" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="119"/>
+      <c r="E25" s="138"/>
       <c r="F25" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="B26" s="130"/>
-      <c r="C26" s="132"/>
+      <c r="B26" s="142"/>
+      <c r="C26" s="145"/>
       <c r="D26" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="126"/>
+      <c r="E26" s="139"/>
       <c r="F26" s="47" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="128" t="s">
+      <c r="B27" s="140" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="131" t="s">
+      <c r="C27" s="143" t="s">
         <v>145</v>
       </c>
       <c r="D27" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E27" s="127" t="s">
+      <c r="E27" s="137" t="s">
         <v>146</v>
       </c>
       <c r="F27" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A28" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="129"/>
-      <c r="C28" s="120"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="144"/>
       <c r="D28" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="119"/>
+      <c r="E28" s="138"/>
       <c r="F28" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="130"/>
-      <c r="C29" s="132"/>
+      <c r="B29" s="142"/>
+      <c r="C29" s="145"/>
       <c r="D29" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="126"/>
+      <c r="E29" s="139"/>
       <c r="F29" s="47" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A30" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="128" t="s">
+      <c r="B30" s="140" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="131" t="s">
+      <c r="C30" s="143" t="s">
         <v>148</v>
       </c>
       <c r="D30" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="E30" s="127" t="s">
+      <c r="E30" s="137" t="s">
         <v>149</v>
       </c>
       <c r="F30" s="53" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A31" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="129"/>
-      <c r="C31" s="120"/>
+      <c r="B31" s="141"/>
+      <c r="C31" s="144"/>
       <c r="D31" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E31" s="119"/>
+      <c r="E31" s="138"/>
       <c r="F31" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="130"/>
-      <c r="C32" s="132"/>
+      <c r="B32" s="142"/>
+      <c r="C32" s="145"/>
       <c r="D32" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="126"/>
+      <c r="E32" s="139"/>
       <c r="F32" s="47" t="s">
         <v>130</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="C9:C13"/>
-    <mergeCell ref="E9:E13"/>
-    <mergeCell ref="E3:E8"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="C3:C8"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="E14:E18"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="C19:C23"/>
-    <mergeCell ref="E19:E23"/>
     <mergeCell ref="E24:E26"/>
     <mergeCell ref="E27:E29"/>
     <mergeCell ref="E30:E32"/>
@@ -9859,6 +9847,18 @@
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="E9:E13"/>
+    <mergeCell ref="E3:E8"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:C8"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A32" xr:uid="{D048ED25-334D-4F32-B2A7-D11385F03FF6}">
@@ -9874,30 +9874,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CB1331-AF3E-489A-B433-09E21B4DF482}">
   <dimension ref="A1:Q213"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="58.7265625" defaultRowHeight="16" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="58.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" style="70" customWidth="1"/>
-    <col min="2" max="2" width="75.26953125" style="62" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="56" customWidth="1"/>
-    <col min="4" max="4" width="27.26953125" style="57" customWidth="1"/>
-    <col min="5" max="5" width="69.7265625" style="70" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" style="56" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" style="56" customWidth="1"/>
-    <col min="8" max="8" width="14.26953125" style="56" customWidth="1"/>
-    <col min="9" max="9" width="19.1796875" style="56" customWidth="1"/>
-    <col min="10" max="10" width="14.26953125" style="56" customWidth="1"/>
-    <col min="11" max="11" width="16.7265625" style="56" customWidth="1"/>
-    <col min="12" max="12" width="19.54296875" style="56" customWidth="1"/>
-    <col min="13" max="13" width="16.7265625" style="56" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="70" customWidth="1"/>
+    <col min="2" max="2" width="75.21875" style="62" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" style="56" customWidth="1"/>
+    <col min="4" max="4" width="27.21875" style="57" customWidth="1"/>
+    <col min="5" max="5" width="69.77734375" style="70" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" style="56" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="56" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" style="56" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" style="56" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" style="56" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" style="56" customWidth="1"/>
+    <col min="12" max="12" width="19.5546875" style="56" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" style="56" customWidth="1"/>
     <col min="14" max="14" width="36" style="70" customWidth="1"/>
-    <col min="15" max="15" width="40.453125" style="70" customWidth="1"/>
-    <col min="16" max="16" width="45.81640625" style="70" customWidth="1"/>
-    <col min="17" max="17" width="58.7265625" style="70"/>
-    <col min="18" max="18" width="15.81640625" style="56" customWidth="1"/>
-    <col min="19" max="16384" width="58.7265625" style="56"/>
+    <col min="15" max="15" width="40.44140625" style="70" customWidth="1"/>
+    <col min="16" max="16" width="45.77734375" style="70" customWidth="1"/>
+    <col min="17" max="17" width="58.77734375" style="70"/>
+    <col min="18" max="18" width="15.77734375" style="56" customWidth="1"/>
+    <col min="19" max="16384" width="58.77734375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="12" customFormat="1" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="12" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>150</v>
       </c>
@@ -9916,11 +9916,11 @@
       <c r="F1" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G1" s="155" t="s">
+      <c r="G1" s="136" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
       <c r="J1" s="15" t="s">
         <v>157</v>
       </c>
@@ -9946,7 +9946,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="12" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" s="12" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
         <v>165</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10007,52 +10007,52 @@
       <c r="B3" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="150">
+      <c r="C3" s="146">
         <v>1</v>
       </c>
-      <c r="D3" s="139" t="s">
+      <c r="D3" s="134" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="147" t="s">
+      <c r="E3" s="125" t="s">
         <v>182</v>
       </c>
-      <c r="F3" s="150" t="s">
+      <c r="F3" s="146" t="s">
         <v>183</v>
       </c>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150" t="s">
+      <c r="G3" s="146"/>
+      <c r="H3" s="146" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150">
+      <c r="I3" s="146"/>
+      <c r="J3" s="146">
         <v>3</v>
       </c>
-      <c r="K3" s="139">
+      <c r="K3" s="134">
         <f>J3*12</f>
         <v>36</v>
       </c>
-      <c r="L3" s="139">
+      <c r="L3" s="134">
         <f>36*J3</f>
         <v>108</v>
       </c>
-      <c r="M3" s="139">
+      <c r="M3" s="134">
         <f>SUM(K3:L3)</f>
         <v>144</v>
       </c>
-      <c r="N3" s="152" t="s">
+      <c r="N3" s="122" t="s">
         <v>185</v>
       </c>
-      <c r="O3" s="147" t="s">
+      <c r="O3" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="P3" s="147" t="s">
+      <c r="P3" s="125" t="s">
         <v>187</v>
       </c>
-      <c r="Q3" s="127" t="s">
+      <c r="Q3" s="137" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10060,23 +10060,23 @@
       <c r="B4" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="136"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="153"/>
-      <c r="O4" s="148"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="119"/>
-    </row>
-    <row r="5" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C4" s="147"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="138"/>
+    </row>
+    <row r="5" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10084,23 +10084,23 @@
       <c r="B5" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="148"/>
-      <c r="Q5" s="119"/>
-    </row>
-    <row r="6" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C5" s="147"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="135"/>
+      <c r="L5" s="135"/>
+      <c r="M5" s="135"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="129"/>
+      <c r="P5" s="129"/>
+      <c r="Q5" s="138"/>
+    </row>
+    <row r="6" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10108,23 +10108,23 @@
       <c r="B6" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="136"/>
-      <c r="D6" s="140"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="140"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="119"/>
-    </row>
-    <row r="7" spans="1:17" s="108" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="147"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="147"/>
+      <c r="I6" s="147"/>
+      <c r="J6" s="147"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="129"/>
+      <c r="P6" s="129"/>
+      <c r="Q6" s="138"/>
+    </row>
+    <row r="7" spans="1:17" s="108" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="95" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10132,23 +10132,23 @@
       <c r="B7" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="151"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="149"/>
-      <c r="F7" s="151"/>
-      <c r="G7" s="151"/>
-      <c r="H7" s="151"/>
-      <c r="I7" s="151"/>
-      <c r="J7" s="151"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="154"/>
-      <c r="O7" s="149"/>
-      <c r="P7" s="149"/>
-      <c r="Q7" s="126"/>
-    </row>
-    <row r="8" spans="1:17" s="55" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="C7" s="148"/>
+      <c r="D7" s="149"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="149"/>
+      <c r="L7" s="149"/>
+      <c r="M7" s="149"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="139"/>
+    </row>
+    <row r="8" spans="1:17" s="55" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="90" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10201,7 +10201,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="55" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="55" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="90" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10254,7 +10254,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10262,52 +10262,52 @@
       <c r="B10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="128">
+      <c r="C10" s="140">
         <v>1</v>
       </c>
-      <c r="D10" s="145" t="s">
+      <c r="D10" s="119" t="s">
         <v>199</v>
       </c>
-      <c r="E10" s="127" t="s">
+      <c r="E10" s="137" t="s">
         <v>200</v>
       </c>
-      <c r="F10" s="145" t="s">
+      <c r="F10" s="119" t="s">
         <v>201</v>
       </c>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145" t="s">
+      <c r="G10" s="119"/>
+      <c r="H10" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145">
+      <c r="I10" s="119"/>
+      <c r="J10" s="119">
         <v>3</v>
       </c>
-      <c r="K10" s="145">
+      <c r="K10" s="119">
         <f>J10*12</f>
         <v>36</v>
       </c>
-      <c r="L10" s="145">
+      <c r="L10" s="119">
         <f>36*J10</f>
         <v>108</v>
       </c>
-      <c r="M10" s="145">
+      <c r="M10" s="119">
         <f>SUM(K10:L10)</f>
         <v>144</v>
       </c>
-      <c r="N10" s="131" t="s">
+      <c r="N10" s="143" t="s">
         <v>202</v>
       </c>
-      <c r="O10" s="127" t="s">
+      <c r="O10" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="P10" s="127" t="s">
+      <c r="P10" s="137" t="s">
         <v>203</v>
       </c>
-      <c r="Q10" s="127" t="s">
+      <c r="Q10" s="137" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="str">
         <f>_xlfn.XLOOKUP(B11,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10315,23 +10315,23 @@
       <c r="B11" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="129"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="119"/>
-      <c r="P11" s="119"/>
-      <c r="Q11" s="119"/>
-    </row>
-    <row r="12" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C11" s="141"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="120"/>
+      <c r="K11" s="120"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
+      <c r="Q11" s="138"/>
+    </row>
+    <row r="12" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="str">
         <f>_xlfn.XLOOKUP(B12,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10339,23 +10339,23 @@
       <c r="B12" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="129"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="119"/>
-      <c r="Q12" s="119"/>
-    </row>
-    <row r="13" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C12" s="141"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="138"/>
+      <c r="P12" s="138"/>
+      <c r="Q12" s="138"/>
+    </row>
+    <row r="13" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10363,23 +10363,23 @@
       <c r="B13" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="129"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="122"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="119"/>
-    </row>
-    <row r="14" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C13" s="141"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="120"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="138"/>
+      <c r="P13" s="138"/>
+      <c r="Q13" s="138"/>
+    </row>
+    <row r="14" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="95" t="str">
         <f>_xlfn.XLOOKUP(B14,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10387,23 +10387,23 @@
       <c r="B14" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="130"/>
-      <c r="D14" s="146"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="146"/>
-      <c r="H14" s="146"/>
-      <c r="I14" s="146"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="132"/>
-      <c r="O14" s="126"/>
-      <c r="P14" s="126"/>
-      <c r="Q14" s="126"/>
-    </row>
-    <row r="15" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C14" s="142"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="145"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="139"/>
+      <c r="Q14" s="139"/>
+    </row>
+    <row r="15" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10411,52 +10411,52 @@
       <c r="B15" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="128">
+      <c r="C15" s="140">
         <v>1</v>
       </c>
-      <c r="D15" s="145" t="s">
+      <c r="D15" s="119" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="147" t="s">
+      <c r="E15" s="125" t="s">
         <v>205</v>
       </c>
-      <c r="F15" s="128" t="s">
+      <c r="F15" s="140" t="s">
         <v>201</v>
       </c>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128" t="s">
+      <c r="G15" s="140"/>
+      <c r="H15" s="140" t="s">
         <v>184</v>
       </c>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128">
+      <c r="I15" s="140"/>
+      <c r="J15" s="140">
         <v>3</v>
       </c>
-      <c r="K15" s="128">
+      <c r="K15" s="140">
         <f>J15*12</f>
         <v>36</v>
       </c>
-      <c r="L15" s="128">
+      <c r="L15" s="140">
         <f>36*J15</f>
         <v>108</v>
       </c>
-      <c r="M15" s="128">
+      <c r="M15" s="140">
         <f>SUM(K15:L15)</f>
         <v>144</v>
       </c>
-      <c r="N15" s="152" t="s">
+      <c r="N15" s="122" t="s">
         <v>206</v>
       </c>
-      <c r="O15" s="147" t="s">
+      <c r="O15" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="P15" s="147" t="s">
+      <c r="P15" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="Q15" s="152" t="s">
+      <c r="Q15" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10464,23 +10464,23 @@
       <c r="B16" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="129"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-      <c r="M16" s="129"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="148"/>
-      <c r="P16" s="148"/>
-      <c r="Q16" s="153"/>
-    </row>
-    <row r="17" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C16" s="141"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="141"/>
+      <c r="I16" s="141"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="141"/>
+      <c r="M16" s="141"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="129"/>
+      <c r="P16" s="129"/>
+      <c r="Q16" s="123"/>
+    </row>
+    <row r="17" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10488,23 +10488,23 @@
       <c r="B17" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="129"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="148"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="148"/>
-      <c r="P17" s="148"/>
-      <c r="Q17" s="153"/>
-    </row>
-    <row r="18" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C17" s="141"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="141"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="129"/>
+      <c r="Q17" s="123"/>
+    </row>
+    <row r="18" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10512,23 +10512,23 @@
       <c r="B18" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="129"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="153"/>
-      <c r="O18" s="148"/>
-      <c r="P18" s="148"/>
-      <c r="Q18" s="153"/>
-    </row>
-    <row r="19" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C18" s="141"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="141"/>
+      <c r="I18" s="141"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="141"/>
+      <c r="L18" s="141"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="129"/>
+      <c r="P18" s="129"/>
+      <c r="Q18" s="123"/>
+    </row>
+    <row r="19" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10536,23 +10536,23 @@
       <c r="B19" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="129"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="148"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="129"/>
-      <c r="K19" s="129"/>
-      <c r="L19" s="129"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="153"/>
-      <c r="O19" s="148"/>
-      <c r="P19" s="148"/>
-      <c r="Q19" s="153"/>
-    </row>
-    <row r="20" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="141"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="141"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="141"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="129"/>
+      <c r="P19" s="129"/>
+      <c r="Q19" s="123"/>
+    </row>
+    <row r="20" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="95" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10560,23 +10560,23 @@
       <c r="B20" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="130"/>
-      <c r="D20" s="146"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="130"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="130"/>
-      <c r="N20" s="154"/>
-      <c r="O20" s="149"/>
-      <c r="P20" s="149"/>
-      <c r="Q20" s="154"/>
-    </row>
-    <row r="21" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C20" s="142"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="142"/>
+      <c r="G20" s="142"/>
+      <c r="H20" s="142"/>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="142"/>
+      <c r="L20" s="142"/>
+      <c r="M20" s="142"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="130"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="124"/>
+    </row>
+    <row r="21" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10584,52 +10584,52 @@
       <c r="B21" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="145">
+      <c r="C21" s="119">
         <v>1</v>
       </c>
-      <c r="D21" s="145" t="s">
+      <c r="D21" s="119" t="s">
         <v>208</v>
       </c>
-      <c r="E21" s="147" t="s">
+      <c r="E21" s="125" t="s">
         <v>209</v>
       </c>
-      <c r="F21" s="145" t="s">
+      <c r="F21" s="119" t="s">
         <v>201</v>
       </c>
-      <c r="G21" s="145"/>
-      <c r="H21" s="145" t="s">
+      <c r="G21" s="119"/>
+      <c r="H21" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I21" s="145"/>
-      <c r="J21" s="145">
+      <c r="I21" s="119"/>
+      <c r="J21" s="119">
         <v>3</v>
       </c>
-      <c r="K21" s="145">
+      <c r="K21" s="119">
         <f>J21*12</f>
         <v>36</v>
       </c>
-      <c r="L21" s="145">
+      <c r="L21" s="119">
         <f>36*J21</f>
         <v>108</v>
       </c>
-      <c r="M21" s="145">
+      <c r="M21" s="119">
         <f>SUM(K21:L21)</f>
         <v>144</v>
       </c>
-      <c r="N21" s="152" t="s">
+      <c r="N21" s="122" t="s">
         <v>210</v>
       </c>
-      <c r="O21" s="147" t="s">
+      <c r="O21" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="P21" s="147" t="s">
+      <c r="P21" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="Q21" s="152" t="s">
+      <c r="Q21" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10637,23 +10637,23 @@
       <c r="B22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="122"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="122"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="122"/>
-      <c r="L22" s="122"/>
-      <c r="M22" s="122"/>
-      <c r="N22" s="153"/>
-      <c r="O22" s="148"/>
-      <c r="P22" s="148"/>
-      <c r="Q22" s="153"/>
-    </row>
-    <row r="23" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C22" s="120"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="120"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="129"/>
+      <c r="P22" s="129"/>
+      <c r="Q22" s="123"/>
+    </row>
+    <row r="23" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10661,23 +10661,23 @@
       <c r="B23" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="122"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="122"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="122"/>
-      <c r="L23" s="122"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="153"/>
-      <c r="O23" s="148"/>
-      <c r="P23" s="148"/>
-      <c r="Q23" s="153"/>
-    </row>
-    <row r="24" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="120"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="129"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="120"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="129"/>
+      <c r="Q23" s="123"/>
+    </row>
+    <row r="24" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="95" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10685,23 +10685,23 @@
       <c r="B24" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="146"/>
-      <c r="D24" s="146"/>
-      <c r="E24" s="149"/>
-      <c r="F24" s="146"/>
-      <c r="G24" s="146"/>
-      <c r="H24" s="146"/>
-      <c r="I24" s="146"/>
-      <c r="J24" s="146"/>
-      <c r="K24" s="146"/>
-      <c r="L24" s="146"/>
-      <c r="M24" s="146"/>
-      <c r="N24" s="154"/>
-      <c r="O24" s="149"/>
-      <c r="P24" s="149"/>
-      <c r="Q24" s="154"/>
-    </row>
-    <row r="25" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C24" s="121"/>
+      <c r="D24" s="121"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="121"/>
+      <c r="G24" s="121"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="121"/>
+      <c r="L24" s="121"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="130"/>
+      <c r="P24" s="130"/>
+      <c r="Q24" s="124"/>
+    </row>
+    <row r="25" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10709,52 +10709,52 @@
       <c r="B25" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="145">
+      <c r="C25" s="119">
         <v>2</v>
       </c>
-      <c r="D25" s="145" t="s">
+      <c r="D25" s="119" t="s">
         <v>211</v>
       </c>
-      <c r="E25" s="152" t="s">
+      <c r="E25" s="122" t="s">
         <v>212</v>
       </c>
-      <c r="F25" s="145" t="s">
+      <c r="F25" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G25" s="145"/>
-      <c r="H25" s="145" t="s">
+      <c r="G25" s="119"/>
+      <c r="H25" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I25" s="145"/>
-      <c r="J25" s="145">
+      <c r="I25" s="119"/>
+      <c r="J25" s="119">
         <v>3</v>
       </c>
-      <c r="K25" s="145">
+      <c r="K25" s="119">
         <f>J25*12</f>
         <v>36</v>
       </c>
-      <c r="L25" s="145">
+      <c r="L25" s="119">
         <f>36*J25</f>
         <v>108</v>
       </c>
-      <c r="M25" s="145">
+      <c r="M25" s="119">
         <f>SUM(K25:L25)</f>
         <v>144</v>
       </c>
-      <c r="N25" s="152" t="s">
+      <c r="N25" s="122" t="s">
         <v>213</v>
       </c>
-      <c r="O25" s="152" t="s">
+      <c r="O25" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P25" s="152" t="s">
+      <c r="P25" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q25" s="152" t="s">
+      <c r="Q25" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10762,23 +10762,23 @@
       <c r="B26" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="153"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="122"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="122"/>
-      <c r="J26" s="122"/>
-      <c r="K26" s="122"/>
-      <c r="L26" s="122"/>
-      <c r="M26" s="122"/>
-      <c r="N26" s="153"/>
-      <c r="O26" s="153"/>
-      <c r="P26" s="153"/>
-      <c r="Q26" s="153"/>
-    </row>
-    <row r="27" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="123"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="123"/>
+    </row>
+    <row r="27" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="str">
         <f>_xlfn.XLOOKUP(B27,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10786,23 +10786,23 @@
       <c r="B27" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="122"/>
-      <c r="D27" s="122"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="122"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="122"/>
-      <c r="J27" s="122"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="122"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="153"/>
-      <c r="O27" s="153"/>
-      <c r="P27" s="153"/>
-      <c r="Q27" s="153"/>
-    </row>
-    <row r="28" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="123"/>
+      <c r="O27" s="123"/>
+      <c r="P27" s="123"/>
+      <c r="Q27" s="123"/>
+    </row>
+    <row r="28" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="95" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10810,23 +10810,23 @@
       <c r="B28" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="122"/>
-      <c r="D28" s="122"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="122"/>
-      <c r="G28" s="122"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="122"/>
-      <c r="J28" s="122"/>
-      <c r="K28" s="122"/>
-      <c r="L28" s="122"/>
-      <c r="M28" s="122"/>
-      <c r="N28" s="153"/>
-      <c r="O28" s="153"/>
-      <c r="P28" s="153"/>
-      <c r="Q28" s="153"/>
-    </row>
-    <row r="29" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="123"/>
+      <c r="O28" s="123"/>
+      <c r="P28" s="123"/>
+      <c r="Q28" s="123"/>
+    </row>
+    <row r="29" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10834,52 +10834,52 @@
       <c r="B29" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="145">
+      <c r="C29" s="119">
         <v>2</v>
       </c>
-      <c r="D29" s="145" t="s">
+      <c r="D29" s="119" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="152" t="s">
+      <c r="E29" s="122" t="s">
         <v>215</v>
       </c>
-      <c r="F29" s="145" t="s">
+      <c r="F29" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145" t="s">
+      <c r="G29" s="119"/>
+      <c r="H29" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145">
+      <c r="I29" s="119"/>
+      <c r="J29" s="119">
         <v>3</v>
       </c>
-      <c r="K29" s="145">
+      <c r="K29" s="119">
         <f>J29*12</f>
         <v>36</v>
       </c>
-      <c r="L29" s="145">
+      <c r="L29" s="119">
         <f>36*J29</f>
         <v>108</v>
       </c>
-      <c r="M29" s="145">
+      <c r="M29" s="119">
         <f>SUM(K29:L29)</f>
         <v>144</v>
       </c>
-      <c r="N29" s="152" t="s">
+      <c r="N29" s="122" t="s">
         <v>216</v>
       </c>
-      <c r="O29" s="152" t="s">
+      <c r="O29" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P29" s="152" t="s">
+      <c r="P29" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q29" s="152" t="s">
+      <c r="Q29" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10887,23 +10887,23 @@
       <c r="B30" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="122"/>
-      <c r="D30" s="122"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="122"/>
-      <c r="G30" s="122"/>
-      <c r="H30" s="122"/>
-      <c r="I30" s="122"/>
-      <c r="J30" s="122"/>
-      <c r="K30" s="122"/>
-      <c r="L30" s="122"/>
-      <c r="M30" s="122"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="153"/>
-      <c r="P30" s="153"/>
-      <c r="Q30" s="153"/>
-    </row>
-    <row r="31" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C30" s="120"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="120"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="120"/>
+      <c r="K30" s="120"/>
+      <c r="L30" s="120"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="123"/>
+      <c r="O30" s="123"/>
+      <c r="P30" s="123"/>
+      <c r="Q30" s="123"/>
+    </row>
+    <row r="31" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="str">
         <f>_xlfn.XLOOKUP(B31,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10911,23 +10911,23 @@
       <c r="B31" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="122"/>
-      <c r="D31" s="122"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="122"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="122"/>
-      <c r="I31" s="122"/>
-      <c r="J31" s="122"/>
-      <c r="K31" s="122"/>
-      <c r="L31" s="122"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="153"/>
-      <c r="O31" s="153"/>
-      <c r="P31" s="153"/>
-      <c r="Q31" s="153"/>
-    </row>
-    <row r="32" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C31" s="120"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="123"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="123"/>
+      <c r="O31" s="123"/>
+      <c r="P31" s="123"/>
+      <c r="Q31" s="123"/>
+    </row>
+    <row r="32" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="95" t="str">
         <f>_xlfn.XLOOKUP(B32,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10935,23 +10935,23 @@
       <c r="B32" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="122"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="122"/>
-      <c r="G32" s="122"/>
-      <c r="H32" s="122"/>
-      <c r="I32" s="122"/>
-      <c r="J32" s="122"/>
-      <c r="K32" s="122"/>
-      <c r="L32" s="122"/>
-      <c r="M32" s="122"/>
-      <c r="N32" s="153"/>
-      <c r="O32" s="153"/>
-      <c r="P32" s="153"/>
-      <c r="Q32" s="153"/>
-    </row>
-    <row r="33" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C32" s="120"/>
+      <c r="D32" s="120"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="120"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+      <c r="K32" s="120"/>
+      <c r="L32" s="120"/>
+      <c r="M32" s="120"/>
+      <c r="N32" s="123"/>
+      <c r="O32" s="123"/>
+      <c r="P32" s="123"/>
+      <c r="Q32" s="123"/>
+    </row>
+    <row r="33" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A33" s="24" t="str">
         <f>_xlfn.XLOOKUP(B33,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10959,52 +10959,52 @@
       <c r="B33" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="145">
+      <c r="C33" s="119">
         <v>2</v>
       </c>
-      <c r="D33" s="145" t="s">
+      <c r="D33" s="119" t="s">
         <v>217</v>
       </c>
-      <c r="E33" s="147" t="s">
+      <c r="E33" s="125" t="s">
         <v>218</v>
       </c>
-      <c r="F33" s="145" t="s">
+      <c r="F33" s="119" t="s">
         <v>201</v>
       </c>
-      <c r="G33" s="145"/>
-      <c r="H33" s="145" t="s">
+      <c r="G33" s="119"/>
+      <c r="H33" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I33" s="145"/>
-      <c r="J33" s="145">
+      <c r="I33" s="119"/>
+      <c r="J33" s="119">
         <v>3</v>
       </c>
-      <c r="K33" s="145">
+      <c r="K33" s="119">
         <f>J33*12</f>
         <v>36</v>
       </c>
-      <c r="L33" s="145">
+      <c r="L33" s="119">
         <f>36*J33</f>
         <v>108</v>
       </c>
-      <c r="M33" s="145">
+      <c r="M33" s="119">
         <f>SUM(K33:L33)</f>
         <v>144</v>
       </c>
-      <c r="N33" s="152" t="s">
+      <c r="N33" s="122" t="s">
         <v>219</v>
       </c>
-      <c r="O33" s="152" t="s">
+      <c r="O33" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P33" s="152" t="s">
+      <c r="P33" s="122" t="s">
         <v>203</v>
       </c>
-      <c r="Q33" s="152" t="s">
+      <c r="Q33" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A34" s="24" t="str">
         <f>_xlfn.XLOOKUP(B34,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11012,23 +11012,23 @@
       <c r="B34" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="148"/>
-      <c r="F34" s="122"/>
-      <c r="G34" s="122"/>
-      <c r="H34" s="122"/>
-      <c r="I34" s="122"/>
-      <c r="J34" s="122"/>
-      <c r="K34" s="122"/>
-      <c r="L34" s="122"/>
-      <c r="M34" s="122"/>
-      <c r="N34" s="153"/>
-      <c r="O34" s="153"/>
-      <c r="P34" s="153"/>
-      <c r="Q34" s="153"/>
-    </row>
-    <row r="35" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C34" s="120"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="129"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="120"/>
+      <c r="M34" s="120"/>
+      <c r="N34" s="123"/>
+      <c r="O34" s="123"/>
+      <c r="P34" s="123"/>
+      <c r="Q34" s="123"/>
+    </row>
+    <row r="35" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="str">
         <f>_xlfn.XLOOKUP(B35,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11036,23 +11036,23 @@
       <c r="B35" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="122"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="148"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="122"/>
-      <c r="H35" s="122"/>
-      <c r="I35" s="122"/>
-      <c r="J35" s="122"/>
-      <c r="K35" s="122"/>
-      <c r="L35" s="122"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="153"/>
-      <c r="O35" s="153"/>
-      <c r="P35" s="153"/>
-      <c r="Q35" s="153"/>
-    </row>
-    <row r="36" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C35" s="120"/>
+      <c r="D35" s="120"/>
+      <c r="E35" s="129"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="120"/>
+      <c r="H35" s="120"/>
+      <c r="I35" s="120"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="120"/>
+      <c r="N35" s="123"/>
+      <c r="O35" s="123"/>
+      <c r="P35" s="123"/>
+      <c r="Q35" s="123"/>
+    </row>
+    <row r="36" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="str">
         <f>_xlfn.XLOOKUP(B36,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11060,23 +11060,23 @@
       <c r="B36" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="122"/>
-      <c r="D36" s="122"/>
-      <c r="E36" s="148"/>
-      <c r="F36" s="122"/>
-      <c r="G36" s="122"/>
-      <c r="H36" s="122"/>
-      <c r="I36" s="122"/>
-      <c r="J36" s="122"/>
-      <c r="K36" s="122"/>
-      <c r="L36" s="122"/>
-      <c r="M36" s="122"/>
-      <c r="N36" s="153"/>
-      <c r="O36" s="153"/>
-      <c r="P36" s="153"/>
-      <c r="Q36" s="153"/>
-    </row>
-    <row r="37" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="120"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+      <c r="L36" s="120"/>
+      <c r="M36" s="120"/>
+      <c r="N36" s="123"/>
+      <c r="O36" s="123"/>
+      <c r="P36" s="123"/>
+      <c r="Q36" s="123"/>
+    </row>
+    <row r="37" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="95" t="str">
         <f>_xlfn.XLOOKUP(B37,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11084,23 +11084,23 @@
       <c r="B37" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
-      <c r="E37" s="148"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="122"/>
-      <c r="H37" s="122"/>
-      <c r="I37" s="122"/>
-      <c r="J37" s="122"/>
-      <c r="K37" s="122"/>
-      <c r="L37" s="122"/>
-      <c r="M37" s="122"/>
-      <c r="N37" s="153"/>
-      <c r="O37" s="153"/>
-      <c r="P37" s="153"/>
-      <c r="Q37" s="153"/>
-    </row>
-    <row r="38" spans="1:17" s="55" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C37" s="120"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="129"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="120"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="120"/>
+      <c r="L37" s="120"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="123"/>
+      <c r="O37" s="123"/>
+      <c r="P37" s="123"/>
+      <c r="Q37" s="123"/>
+    </row>
+    <row r="38" spans="1:17" s="55" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="90" t="str">
         <f>_xlfn.XLOOKUP(B38,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11153,7 +11153,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="str">
         <f>_xlfn.XLOOKUP(B39,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11161,52 +11161,52 @@
       <c r="B39" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="145">
+      <c r="C39" s="119">
         <v>2</v>
       </c>
-      <c r="D39" s="145" t="s">
+      <c r="D39" s="119" t="s">
         <v>223</v>
       </c>
-      <c r="E39" s="147" t="s">
+      <c r="E39" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="F39" s="145" t="s">
+      <c r="F39" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G39" s="145"/>
-      <c r="H39" s="145" t="s">
+      <c r="G39" s="119"/>
+      <c r="H39" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I39" s="145"/>
-      <c r="J39" s="145">
+      <c r="I39" s="119"/>
+      <c r="J39" s="119">
         <v>3</v>
       </c>
-      <c r="K39" s="145">
+      <c r="K39" s="119">
         <f>J39*12</f>
         <v>36</v>
       </c>
-      <c r="L39" s="145">
+      <c r="L39" s="119">
         <f>36*J39</f>
         <v>108</v>
       </c>
-      <c r="M39" s="145">
+      <c r="M39" s="119">
         <f>SUM(K39:L39)</f>
         <v>144</v>
       </c>
-      <c r="N39" s="152" t="s">
+      <c r="N39" s="122" t="s">
         <v>225</v>
       </c>
-      <c r="O39" s="152" t="s">
+      <c r="O39" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P39" s="152" t="s">
+      <c r="P39" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q39" s="152" t="s">
+      <c r="Q39" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="str">
         <f>_xlfn.XLOOKUP(B40,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11214,23 +11214,23 @@
       <c r="B40" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="122"/>
-      <c r="D40" s="122"/>
-      <c r="E40" s="148"/>
-      <c r="F40" s="122"/>
-      <c r="G40" s="122"/>
-      <c r="H40" s="122"/>
-      <c r="I40" s="122"/>
-      <c r="J40" s="122"/>
-      <c r="K40" s="122"/>
-      <c r="L40" s="122"/>
-      <c r="M40" s="122"/>
-      <c r="N40" s="153"/>
-      <c r="O40" s="153"/>
-      <c r="P40" s="153"/>
-      <c r="Q40" s="153"/>
-    </row>
-    <row r="41" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C40" s="120"/>
+      <c r="D40" s="120"/>
+      <c r="E40" s="129"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="120"/>
+      <c r="H40" s="120"/>
+      <c r="I40" s="120"/>
+      <c r="J40" s="120"/>
+      <c r="K40" s="120"/>
+      <c r="L40" s="120"/>
+      <c r="M40" s="120"/>
+      <c r="N40" s="123"/>
+      <c r="O40" s="123"/>
+      <c r="P40" s="123"/>
+      <c r="Q40" s="123"/>
+    </row>
+    <row r="41" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="str">
         <f>_xlfn.XLOOKUP(B41,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11238,23 +11238,23 @@
       <c r="B41" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="122"/>
-      <c r="D41" s="122"/>
-      <c r="E41" s="148"/>
-      <c r="F41" s="122"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="122"/>
-      <c r="I41" s="122"/>
-      <c r="J41" s="122"/>
-      <c r="K41" s="122"/>
-      <c r="L41" s="122"/>
-      <c r="M41" s="122"/>
-      <c r="N41" s="153"/>
-      <c r="O41" s="153"/>
-      <c r="P41" s="153"/>
-      <c r="Q41" s="153"/>
-    </row>
-    <row r="42" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="129"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="120"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="123"/>
+      <c r="O41" s="123"/>
+      <c r="P41" s="123"/>
+      <c r="Q41" s="123"/>
+    </row>
+    <row r="42" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="str">
         <f>_xlfn.XLOOKUP(B42,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11262,23 +11262,23 @@
       <c r="B42" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C42" s="122"/>
-      <c r="D42" s="122"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="122"/>
-      <c r="G42" s="122"/>
-      <c r="H42" s="122"/>
-      <c r="I42" s="122"/>
-      <c r="J42" s="122"/>
-      <c r="K42" s="122"/>
-      <c r="L42" s="122"/>
-      <c r="M42" s="122"/>
-      <c r="N42" s="153"/>
-      <c r="O42" s="153"/>
-      <c r="P42" s="153"/>
-      <c r="Q42" s="153"/>
-    </row>
-    <row r="43" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C42" s="120"/>
+      <c r="D42" s="120"/>
+      <c r="E42" s="129"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="120"/>
+      <c r="H42" s="120"/>
+      <c r="I42" s="120"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="120"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="120"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="123"/>
+    </row>
+    <row r="43" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="95" t="str">
         <f>_xlfn.XLOOKUP(B43,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11286,23 +11286,23 @@
       <c r="B43" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="122"/>
-      <c r="D43" s="122"/>
-      <c r="E43" s="148"/>
-      <c r="F43" s="122"/>
-      <c r="G43" s="122"/>
-      <c r="H43" s="122"/>
-      <c r="I43" s="122"/>
-      <c r="J43" s="122"/>
-      <c r="K43" s="122"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="153"/>
-      <c r="O43" s="153"/>
-      <c r="P43" s="153"/>
-      <c r="Q43" s="153"/>
-    </row>
-    <row r="44" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C43" s="120"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="129"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="H43" s="120"/>
+      <c r="I43" s="120"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="120"/>
+      <c r="M43" s="120"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="123"/>
+      <c r="Q43" s="123"/>
+    </row>
+    <row r="44" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="str">
         <f>_xlfn.XLOOKUP(B44,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11310,52 +11310,52 @@
       <c r="B44" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C44" s="145">
+      <c r="C44" s="119">
         <v>2</v>
       </c>
-      <c r="D44" s="145" t="s">
+      <c r="D44" s="119" t="s">
         <v>226</v>
       </c>
-      <c r="E44" s="156" t="s">
+      <c r="E44" s="127" t="s">
         <v>227</v>
       </c>
-      <c r="F44" s="145" t="s">
+      <c r="F44" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G44" s="145"/>
-      <c r="H44" s="145" t="s">
+      <c r="G44" s="119"/>
+      <c r="H44" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I44" s="145"/>
-      <c r="J44" s="145">
+      <c r="I44" s="119"/>
+      <c r="J44" s="119">
         <v>3</v>
       </c>
-      <c r="K44" s="145">
+      <c r="K44" s="119">
         <f>J44*12</f>
         <v>36</v>
       </c>
-      <c r="L44" s="145">
+      <c r="L44" s="119">
         <f>36*J44</f>
         <v>108</v>
       </c>
-      <c r="M44" s="145">
+      <c r="M44" s="119">
         <f>SUM(K44:L44)</f>
         <v>144</v>
       </c>
-      <c r="N44" s="152" t="s">
+      <c r="N44" s="122" t="s">
         <v>228</v>
       </c>
-      <c r="O44" s="152" t="s">
+      <c r="O44" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P44" s="152" t="s">
+      <c r="P44" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q44" s="152" t="s">
+      <c r="Q44" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="str">
         <f>_xlfn.XLOOKUP(B45,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11363,23 +11363,23 @@
       <c r="B45" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="122"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="157"/>
-      <c r="F45" s="122"/>
-      <c r="G45" s="122"/>
-      <c r="H45" s="122"/>
-      <c r="I45" s="122"/>
-      <c r="J45" s="122"/>
-      <c r="K45" s="122"/>
-      <c r="L45" s="122"/>
-      <c r="M45" s="122"/>
-      <c r="N45" s="153"/>
-      <c r="O45" s="153"/>
-      <c r="P45" s="153"/>
-      <c r="Q45" s="153"/>
-    </row>
-    <row r="46" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C45" s="120"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="128"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="120"/>
+      <c r="H45" s="120"/>
+      <c r="I45" s="120"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="120"/>
+      <c r="L45" s="120"/>
+      <c r="M45" s="120"/>
+      <c r="N45" s="123"/>
+      <c r="O45" s="123"/>
+      <c r="P45" s="123"/>
+      <c r="Q45" s="123"/>
+    </row>
+    <row r="46" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="str">
         <f>_xlfn.XLOOKUP(B46,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11387,23 +11387,23 @@
       <c r="B46" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="122"/>
-      <c r="D46" s="122"/>
-      <c r="E46" s="157"/>
-      <c r="F46" s="122"/>
-      <c r="G46" s="122"/>
-      <c r="H46" s="122"/>
-      <c r="I46" s="122"/>
-      <c r="J46" s="122"/>
-      <c r="K46" s="122"/>
-      <c r="L46" s="122"/>
-      <c r="M46" s="122"/>
-      <c r="N46" s="153"/>
-      <c r="O46" s="153"/>
-      <c r="P46" s="153"/>
-      <c r="Q46" s="153"/>
-    </row>
-    <row r="47" spans="1:17" s="55" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+      <c r="C46" s="120"/>
+      <c r="D46" s="120"/>
+      <c r="E46" s="128"/>
+      <c r="F46" s="120"/>
+      <c r="G46" s="120"/>
+      <c r="H46" s="120"/>
+      <c r="I46" s="120"/>
+      <c r="J46" s="120"/>
+      <c r="K46" s="120"/>
+      <c r="L46" s="120"/>
+      <c r="M46" s="120"/>
+      <c r="N46" s="123"/>
+      <c r="O46" s="123"/>
+      <c r="P46" s="123"/>
+      <c r="Q46" s="123"/>
+    </row>
+    <row r="47" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="95" t="str">
         <f>_xlfn.XLOOKUP(B47,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11411,23 +11411,23 @@
       <c r="B47" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="122"/>
-      <c r="E47" s="157"/>
-      <c r="F47" s="122"/>
-      <c r="G47" s="122"/>
-      <c r="H47" s="122"/>
-      <c r="I47" s="122"/>
-      <c r="J47" s="122"/>
-      <c r="K47" s="122"/>
-      <c r="L47" s="122"/>
-      <c r="M47" s="122"/>
-      <c r="N47" s="153"/>
-      <c r="O47" s="153"/>
-      <c r="P47" s="153"/>
-      <c r="Q47" s="153"/>
-    </row>
-    <row r="48" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C47" s="120"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="128"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="120"/>
+      <c r="H47" s="120"/>
+      <c r="I47" s="120"/>
+      <c r="J47" s="120"/>
+      <c r="K47" s="120"/>
+      <c r="L47" s="120"/>
+      <c r="M47" s="120"/>
+      <c r="N47" s="123"/>
+      <c r="O47" s="123"/>
+      <c r="P47" s="123"/>
+      <c r="Q47" s="123"/>
+    </row>
+    <row r="48" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="str">
         <f>_xlfn.XLOOKUP(B48,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11435,51 +11435,51 @@
       <c r="B48" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="139">
+      <c r="C48" s="134">
         <v>3</v>
       </c>
-      <c r="D48" s="145" t="s">
+      <c r="D48" s="119" t="s">
         <v>229</v>
       </c>
-      <c r="E48" s="147" t="s">
+      <c r="E48" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="F48" s="139" t="s">
+      <c r="F48" s="134" t="s">
         <v>183</v>
       </c>
-      <c r="G48" s="139"/>
-      <c r="H48" s="139" t="s">
+      <c r="G48" s="134"/>
+      <c r="H48" s="134" t="s">
         <v>184</v>
       </c>
-      <c r="I48" s="139"/>
-      <c r="J48" s="139">
+      <c r="I48" s="134"/>
+      <c r="J48" s="134">
         <v>3</v>
       </c>
-      <c r="K48" s="139">
+      <c r="K48" s="134">
         <v>36</v>
       </c>
-      <c r="L48" s="139">
+      <c r="L48" s="134">
         <f>36*J48</f>
         <v>108</v>
       </c>
-      <c r="M48" s="139">
+      <c r="M48" s="134">
         <f>SUM(K48:L48)</f>
         <v>144</v>
       </c>
-      <c r="N48" s="147" t="s">
+      <c r="N48" s="125" t="s">
         <v>231</v>
       </c>
-      <c r="O48" s="147" t="s">
+      <c r="O48" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="P48" s="147" t="s">
+      <c r="P48" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="Q48" s="147" t="s">
+      <c r="Q48" s="125" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="str">
         <f>_xlfn.XLOOKUP(B49,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11487,23 +11487,23 @@
       <c r="B49" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="140"/>
-      <c r="D49" s="122"/>
-      <c r="E49" s="148"/>
-      <c r="F49" s="140"/>
-      <c r="G49" s="140"/>
-      <c r="H49" s="140"/>
-      <c r="I49" s="140"/>
-      <c r="J49" s="140"/>
-      <c r="K49" s="140"/>
-      <c r="L49" s="140"/>
-      <c r="M49" s="140"/>
-      <c r="N49" s="148"/>
-      <c r="O49" s="148"/>
-      <c r="P49" s="148"/>
-      <c r="Q49" s="148"/>
-    </row>
-    <row r="50" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C49" s="135"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="129"/>
+      <c r="F49" s="135"/>
+      <c r="G49" s="135"/>
+      <c r="H49" s="135"/>
+      <c r="I49" s="135"/>
+      <c r="J49" s="135"/>
+      <c r="K49" s="135"/>
+      <c r="L49" s="135"/>
+      <c r="M49" s="135"/>
+      <c r="N49" s="129"/>
+      <c r="O49" s="129"/>
+      <c r="P49" s="129"/>
+      <c r="Q49" s="129"/>
+    </row>
+    <row r="50" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A50" s="24" t="str">
         <f>_xlfn.XLOOKUP(B50,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11511,23 +11511,23 @@
       <c r="B50" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="140"/>
-      <c r="D50" s="122"/>
-      <c r="E50" s="148"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="140"/>
-      <c r="I50" s="140"/>
-      <c r="J50" s="140"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="140"/>
-      <c r="M50" s="140"/>
-      <c r="N50" s="148"/>
-      <c r="O50" s="148"/>
-      <c r="P50" s="148"/>
-      <c r="Q50" s="148"/>
-    </row>
-    <row r="51" spans="1:17" s="108" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C50" s="135"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="129"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="135"/>
+      <c r="I50" s="135"/>
+      <c r="J50" s="135"/>
+      <c r="K50" s="135"/>
+      <c r="L50" s="135"/>
+      <c r="M50" s="135"/>
+      <c r="N50" s="129"/>
+      <c r="O50" s="129"/>
+      <c r="P50" s="129"/>
+      <c r="Q50" s="129"/>
+    </row>
+    <row r="51" spans="1:17" s="108" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="str">
         <f>_xlfn.XLOOKUP(B51,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11535,23 +11535,23 @@
       <c r="B51" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="140"/>
-      <c r="D51" s="122"/>
-      <c r="E51" s="148"/>
-      <c r="F51" s="140"/>
-      <c r="G51" s="140"/>
-      <c r="H51" s="140"/>
-      <c r="I51" s="140"/>
-      <c r="J51" s="140"/>
-      <c r="K51" s="140"/>
-      <c r="L51" s="140"/>
-      <c r="M51" s="140"/>
-      <c r="N51" s="148"/>
-      <c r="O51" s="148"/>
-      <c r="P51" s="148"/>
-      <c r="Q51" s="148"/>
-    </row>
-    <row r="52" spans="1:17" s="108" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C51" s="135"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="129"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="135"/>
+      <c r="H51" s="135"/>
+      <c r="I51" s="135"/>
+      <c r="J51" s="135"/>
+      <c r="K51" s="135"/>
+      <c r="L51" s="135"/>
+      <c r="M51" s="135"/>
+      <c r="N51" s="129"/>
+      <c r="O51" s="129"/>
+      <c r="P51" s="129"/>
+      <c r="Q51" s="129"/>
+    </row>
+    <row r="52" spans="1:17" s="108" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="95" t="str">
         <f>_xlfn.XLOOKUP(B52,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11559,23 +11559,23 @@
       <c r="B52" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="140"/>
-      <c r="D52" s="122"/>
-      <c r="E52" s="148"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="140"/>
-      <c r="I52" s="140"/>
-      <c r="J52" s="140"/>
-      <c r="K52" s="140"/>
-      <c r="L52" s="140"/>
-      <c r="M52" s="140"/>
-      <c r="N52" s="148"/>
-      <c r="O52" s="148"/>
-      <c r="P52" s="148"/>
-      <c r="Q52" s="148"/>
-    </row>
-    <row r="53" spans="1:17" s="55" customFormat="1" ht="363.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C52" s="135"/>
+      <c r="D52" s="120"/>
+      <c r="E52" s="129"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="135"/>
+      <c r="I52" s="135"/>
+      <c r="J52" s="135"/>
+      <c r="K52" s="135"/>
+      <c r="L52" s="135"/>
+      <c r="M52" s="135"/>
+      <c r="N52" s="129"/>
+      <c r="O52" s="129"/>
+      <c r="P52" s="129"/>
+      <c r="Q52" s="129"/>
+    </row>
+    <row r="53" spans="1:17" s="55" customFormat="1" ht="396.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="90" t="str">
         <f>_xlfn.XLOOKUP(B53,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11628,7 +11628,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="str">
         <f>_xlfn.XLOOKUP(B54,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11636,52 +11636,52 @@
       <c r="B54" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C54" s="145">
+      <c r="C54" s="119">
         <v>3</v>
       </c>
-      <c r="D54" s="145" t="s">
+      <c r="D54" s="119" t="s">
         <v>237</v>
       </c>
-      <c r="E54" s="147" t="s">
+      <c r="E54" s="125" t="s">
         <v>238</v>
       </c>
-      <c r="F54" s="145" t="s">
+      <c r="F54" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G54" s="145"/>
-      <c r="H54" s="145" t="s">
+      <c r="G54" s="119"/>
+      <c r="H54" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I54" s="145"/>
-      <c r="J54" s="145">
+      <c r="I54" s="119"/>
+      <c r="J54" s="119">
         <v>3</v>
       </c>
-      <c r="K54" s="145">
+      <c r="K54" s="119">
         <f>J54*12</f>
         <v>36</v>
       </c>
-      <c r="L54" s="145">
+      <c r="L54" s="119">
         <f>36*J54</f>
         <v>108</v>
       </c>
-      <c r="M54" s="145">
+      <c r="M54" s="119">
         <f>SUM(K54:L54)</f>
         <v>144</v>
       </c>
-      <c r="N54" s="152" t="s">
+      <c r="N54" s="122" t="s">
         <v>239</v>
       </c>
-      <c r="O54" s="152" t="s">
+      <c r="O54" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P54" s="147" t="s">
+      <c r="P54" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="Q54" s="152" t="s">
+      <c r="Q54" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="str">
         <f>_xlfn.XLOOKUP(B55,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11689,23 +11689,23 @@
       <c r="B55" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C55" s="122"/>
-      <c r="D55" s="122"/>
-      <c r="E55" s="148"/>
-      <c r="F55" s="122"/>
-      <c r="G55" s="122"/>
-      <c r="H55" s="122"/>
-      <c r="I55" s="122"/>
-      <c r="J55" s="122"/>
-      <c r="K55" s="122"/>
-      <c r="L55" s="122"/>
-      <c r="M55" s="122"/>
-      <c r="N55" s="153"/>
-      <c r="O55" s="153"/>
-      <c r="P55" s="148"/>
-      <c r="Q55" s="153"/>
-    </row>
-    <row r="56" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="129"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="120"/>
+      <c r="I55" s="120"/>
+      <c r="J55" s="120"/>
+      <c r="K55" s="120"/>
+      <c r="L55" s="120"/>
+      <c r="M55" s="120"/>
+      <c r="N55" s="123"/>
+      <c r="O55" s="123"/>
+      <c r="P55" s="129"/>
+      <c r="Q55" s="123"/>
+    </row>
+    <row r="56" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="str">
         <f>_xlfn.XLOOKUP(B56,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11713,23 +11713,23 @@
       <c r="B56" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="122"/>
-      <c r="D56" s="122"/>
-      <c r="E56" s="148"/>
-      <c r="F56" s="122"/>
-      <c r="G56" s="122"/>
-      <c r="H56" s="122"/>
-      <c r="I56" s="122"/>
-      <c r="J56" s="122"/>
-      <c r="K56" s="122"/>
-      <c r="L56" s="122"/>
-      <c r="M56" s="122"/>
-      <c r="N56" s="153"/>
-      <c r="O56" s="153"/>
-      <c r="P56" s="148"/>
-      <c r="Q56" s="153"/>
-    </row>
-    <row r="57" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C56" s="120"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="129"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="120"/>
+      <c r="I56" s="120"/>
+      <c r="J56" s="120"/>
+      <c r="K56" s="120"/>
+      <c r="L56" s="120"/>
+      <c r="M56" s="120"/>
+      <c r="N56" s="123"/>
+      <c r="O56" s="123"/>
+      <c r="P56" s="129"/>
+      <c r="Q56" s="123"/>
+    </row>
+    <row r="57" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="str">
         <f>_xlfn.XLOOKUP(B57,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11737,23 +11737,23 @@
       <c r="B57" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="122"/>
-      <c r="D57" s="122"/>
-      <c r="E57" s="148"/>
-      <c r="F57" s="122"/>
-      <c r="G57" s="122"/>
-      <c r="H57" s="122"/>
-      <c r="I57" s="122"/>
-      <c r="J57" s="122"/>
-      <c r="K57" s="122"/>
-      <c r="L57" s="122"/>
-      <c r="M57" s="122"/>
-      <c r="N57" s="153"/>
-      <c r="O57" s="153"/>
-      <c r="P57" s="148"/>
-      <c r="Q57" s="153"/>
-    </row>
-    <row r="58" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C57" s="120"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="129"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="120"/>
+      <c r="H57" s="120"/>
+      <c r="I57" s="120"/>
+      <c r="J57" s="120"/>
+      <c r="K57" s="120"/>
+      <c r="L57" s="120"/>
+      <c r="M57" s="120"/>
+      <c r="N57" s="123"/>
+      <c r="O57" s="123"/>
+      <c r="P57" s="129"/>
+      <c r="Q57" s="123"/>
+    </row>
+    <row r="58" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="95" t="str">
         <f>_xlfn.XLOOKUP(B58,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11761,23 +11761,23 @@
       <c r="B58" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="122"/>
-      <c r="D58" s="122"/>
-      <c r="E58" s="148"/>
-      <c r="F58" s="122"/>
-      <c r="G58" s="122"/>
-      <c r="H58" s="122"/>
-      <c r="I58" s="122"/>
-      <c r="J58" s="122"/>
-      <c r="K58" s="122"/>
-      <c r="L58" s="122"/>
-      <c r="M58" s="122"/>
-      <c r="N58" s="153"/>
-      <c r="O58" s="153"/>
-      <c r="P58" s="148"/>
-      <c r="Q58" s="153"/>
-    </row>
-    <row r="59" spans="1:17" s="12" customFormat="1" ht="297" x14ac:dyDescent="0.35">
+      <c r="C58" s="120"/>
+      <c r="D58" s="120"/>
+      <c r="E58" s="129"/>
+      <c r="F58" s="120"/>
+      <c r="G58" s="120"/>
+      <c r="H58" s="120"/>
+      <c r="I58" s="120"/>
+      <c r="J58" s="120"/>
+      <c r="K58" s="120"/>
+      <c r="L58" s="120"/>
+      <c r="M58" s="120"/>
+      <c r="N58" s="123"/>
+      <c r="O58" s="123"/>
+      <c r="P58" s="129"/>
+      <c r="Q58" s="123"/>
+    </row>
+    <row r="59" spans="1:17" s="12" customFormat="1" ht="342.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="90" t="str">
         <f>_xlfn.XLOOKUP(B59,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11830,7 +11830,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="str">
         <f>_xlfn.XLOOKUP(B60,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11838,52 +11838,52 @@
       <c r="B60" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C60" s="145">
+      <c r="C60" s="119">
         <v>3</v>
       </c>
-      <c r="D60" s="145" t="s">
+      <c r="D60" s="119" t="s">
         <v>244</v>
       </c>
-      <c r="E60" s="147" t="s">
+      <c r="E60" s="125" t="s">
         <v>245</v>
       </c>
-      <c r="F60" s="145" t="s">
+      <c r="F60" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G60" s="145"/>
-      <c r="H60" s="145" t="s">
+      <c r="G60" s="119"/>
+      <c r="H60" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I60" s="145"/>
-      <c r="J60" s="145">
+      <c r="I60" s="119"/>
+      <c r="J60" s="119">
         <v>3</v>
       </c>
-      <c r="K60" s="145">
+      <c r="K60" s="119">
         <f>J60*12</f>
         <v>36</v>
       </c>
-      <c r="L60" s="145">
+      <c r="L60" s="119">
         <f>36*J60</f>
         <v>108</v>
       </c>
-      <c r="M60" s="145">
+      <c r="M60" s="119">
         <f>SUM(K60:L60)</f>
         <v>144</v>
       </c>
-      <c r="N60" s="147" t="s">
+      <c r="N60" s="125" t="s">
         <v>246</v>
       </c>
-      <c r="O60" s="152" t="s">
+      <c r="O60" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P60" s="152" t="s">
+      <c r="P60" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q60" s="152" t="s">
+      <c r="Q60" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="str">
         <f>_xlfn.XLOOKUP(B61,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11891,23 +11891,23 @@
       <c r="B61" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="122"/>
-      <c r="D61" s="122"/>
-      <c r="E61" s="148"/>
-      <c r="F61" s="122"/>
-      <c r="G61" s="122"/>
-      <c r="H61" s="122"/>
-      <c r="I61" s="122"/>
-      <c r="J61" s="122"/>
-      <c r="K61" s="122"/>
-      <c r="L61" s="122"/>
-      <c r="M61" s="122"/>
-      <c r="N61" s="148"/>
-      <c r="O61" s="153"/>
-      <c r="P61" s="153"/>
-      <c r="Q61" s="153"/>
-    </row>
-    <row r="62" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C61" s="120"/>
+      <c r="D61" s="120"/>
+      <c r="E61" s="129"/>
+      <c r="F61" s="120"/>
+      <c r="G61" s="120"/>
+      <c r="H61" s="120"/>
+      <c r="I61" s="120"/>
+      <c r="J61" s="120"/>
+      <c r="K61" s="120"/>
+      <c r="L61" s="120"/>
+      <c r="M61" s="120"/>
+      <c r="N61" s="129"/>
+      <c r="O61" s="123"/>
+      <c r="P61" s="123"/>
+      <c r="Q61" s="123"/>
+    </row>
+    <row r="62" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="str">
         <f>_xlfn.XLOOKUP(B62,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11915,23 +11915,23 @@
       <c r="B62" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="122"/>
-      <c r="D62" s="122"/>
-      <c r="E62" s="148"/>
-      <c r="F62" s="122"/>
-      <c r="G62" s="122"/>
-      <c r="H62" s="122"/>
-      <c r="I62" s="122"/>
-      <c r="J62" s="122"/>
-      <c r="K62" s="122"/>
-      <c r="L62" s="122"/>
-      <c r="M62" s="122"/>
-      <c r="N62" s="148"/>
-      <c r="O62" s="153"/>
-      <c r="P62" s="153"/>
-      <c r="Q62" s="153"/>
-    </row>
-    <row r="63" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C62" s="120"/>
+      <c r="D62" s="120"/>
+      <c r="E62" s="129"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="120"/>
+      <c r="H62" s="120"/>
+      <c r="I62" s="120"/>
+      <c r="J62" s="120"/>
+      <c r="K62" s="120"/>
+      <c r="L62" s="120"/>
+      <c r="M62" s="120"/>
+      <c r="N62" s="129"/>
+      <c r="O62" s="123"/>
+      <c r="P62" s="123"/>
+      <c r="Q62" s="123"/>
+    </row>
+    <row r="63" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="str">
         <f>_xlfn.XLOOKUP(B63,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11939,23 +11939,23 @@
       <c r="B63" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="C63" s="122"/>
-      <c r="D63" s="122"/>
-      <c r="E63" s="148"/>
-      <c r="F63" s="122"/>
-      <c r="G63" s="122"/>
-      <c r="H63" s="122"/>
-      <c r="I63" s="122"/>
-      <c r="J63" s="122"/>
-      <c r="K63" s="122"/>
-      <c r="L63" s="122"/>
-      <c r="M63" s="122"/>
-      <c r="N63" s="148"/>
-      <c r="O63" s="153"/>
-      <c r="P63" s="153"/>
-      <c r="Q63" s="153"/>
-    </row>
-    <row r="64" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C63" s="120"/>
+      <c r="D63" s="120"/>
+      <c r="E63" s="129"/>
+      <c r="F63" s="120"/>
+      <c r="G63" s="120"/>
+      <c r="H63" s="120"/>
+      <c r="I63" s="120"/>
+      <c r="J63" s="120"/>
+      <c r="K63" s="120"/>
+      <c r="L63" s="120"/>
+      <c r="M63" s="120"/>
+      <c r="N63" s="129"/>
+      <c r="O63" s="123"/>
+      <c r="P63" s="123"/>
+      <c r="Q63" s="123"/>
+    </row>
+    <row r="64" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="95" t="str">
         <f>_xlfn.XLOOKUP(B64,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11963,23 +11963,23 @@
       <c r="B64" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="146"/>
-      <c r="D64" s="146"/>
-      <c r="E64" s="149"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="146"/>
-      <c r="H64" s="146"/>
-      <c r="I64" s="146"/>
-      <c r="J64" s="146"/>
-      <c r="K64" s="146"/>
-      <c r="L64" s="146"/>
-      <c r="M64" s="146"/>
-      <c r="N64" s="149"/>
-      <c r="O64" s="154"/>
-      <c r="P64" s="154"/>
-      <c r="Q64" s="154"/>
-    </row>
-    <row r="65" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C64" s="121"/>
+      <c r="D64" s="121"/>
+      <c r="E64" s="130"/>
+      <c r="F64" s="121"/>
+      <c r="G64" s="121"/>
+      <c r="H64" s="121"/>
+      <c r="I64" s="121"/>
+      <c r="J64" s="121"/>
+      <c r="K64" s="121"/>
+      <c r="L64" s="121"/>
+      <c r="M64" s="121"/>
+      <c r="N64" s="130"/>
+      <c r="O64" s="124"/>
+      <c r="P64" s="124"/>
+      <c r="Q64" s="124"/>
+    </row>
+    <row r="65" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="str">
         <f>_xlfn.XLOOKUP(B65,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11987,52 +11987,52 @@
       <c r="B65" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C65" s="145">
+      <c r="C65" s="119">
         <v>4</v>
       </c>
-      <c r="D65" s="145" t="s">
+      <c r="D65" s="119" t="s">
         <v>247</v>
       </c>
-      <c r="E65" s="147" t="s">
+      <c r="E65" s="125" t="s">
         <v>248</v>
       </c>
-      <c r="F65" s="145" t="s">
+      <c r="F65" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G65" s="145"/>
-      <c r="H65" s="145" t="s">
+      <c r="G65" s="119"/>
+      <c r="H65" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I65" s="145"/>
-      <c r="J65" s="145">
+      <c r="I65" s="119"/>
+      <c r="J65" s="119">
         <v>3</v>
       </c>
-      <c r="K65" s="145">
+      <c r="K65" s="119">
         <f>J65*12</f>
         <v>36</v>
       </c>
-      <c r="L65" s="145">
+      <c r="L65" s="119">
         <f>36*J65</f>
         <v>108</v>
       </c>
-      <c r="M65" s="145">
+      <c r="M65" s="119">
         <f>SUM(K65:L65)</f>
         <v>144</v>
       </c>
-      <c r="N65" s="147" t="s">
+      <c r="N65" s="125" t="s">
         <v>249</v>
       </c>
-      <c r="O65" s="152" t="s">
+      <c r="O65" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P65" s="147" t="s">
+      <c r="P65" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="Q65" s="152" t="s">
+      <c r="Q65" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="str">
         <f>_xlfn.XLOOKUP(B66,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12040,23 +12040,23 @@
       <c r="B66" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C66" s="122"/>
-      <c r="D66" s="122"/>
-      <c r="E66" s="148"/>
-      <c r="F66" s="122"/>
-      <c r="G66" s="122"/>
-      <c r="H66" s="122"/>
-      <c r="I66" s="122"/>
-      <c r="J66" s="122"/>
-      <c r="K66" s="122"/>
-      <c r="L66" s="122"/>
-      <c r="M66" s="122"/>
-      <c r="N66" s="148"/>
-      <c r="O66" s="153"/>
-      <c r="P66" s="148"/>
-      <c r="Q66" s="153"/>
-    </row>
-    <row r="67" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C66" s="120"/>
+      <c r="D66" s="120"/>
+      <c r="E66" s="129"/>
+      <c r="F66" s="120"/>
+      <c r="G66" s="120"/>
+      <c r="H66" s="120"/>
+      <c r="I66" s="120"/>
+      <c r="J66" s="120"/>
+      <c r="K66" s="120"/>
+      <c r="L66" s="120"/>
+      <c r="M66" s="120"/>
+      <c r="N66" s="129"/>
+      <c r="O66" s="123"/>
+      <c r="P66" s="129"/>
+      <c r="Q66" s="123"/>
+    </row>
+    <row r="67" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="str">
         <f>_xlfn.XLOOKUP(B67,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12064,23 +12064,23 @@
       <c r="B67" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C67" s="122"/>
-      <c r="D67" s="122"/>
-      <c r="E67" s="148"/>
-      <c r="F67" s="122"/>
-      <c r="G67" s="122"/>
-      <c r="H67" s="122"/>
-      <c r="I67" s="122"/>
-      <c r="J67" s="122"/>
-      <c r="K67" s="122"/>
-      <c r="L67" s="122"/>
-      <c r="M67" s="122"/>
-      <c r="N67" s="148"/>
-      <c r="O67" s="153"/>
-      <c r="P67" s="148"/>
-      <c r="Q67" s="153"/>
-    </row>
-    <row r="68" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C67" s="120"/>
+      <c r="D67" s="120"/>
+      <c r="E67" s="129"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="120"/>
+      <c r="H67" s="120"/>
+      <c r="I67" s="120"/>
+      <c r="J67" s="120"/>
+      <c r="K67" s="120"/>
+      <c r="L67" s="120"/>
+      <c r="M67" s="120"/>
+      <c r="N67" s="129"/>
+      <c r="O67" s="123"/>
+      <c r="P67" s="129"/>
+      <c r="Q67" s="123"/>
+    </row>
+    <row r="68" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="str">
         <f>_xlfn.XLOOKUP(B68,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12088,23 +12088,23 @@
       <c r="B68" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="122"/>
-      <c r="D68" s="122"/>
-      <c r="E68" s="148"/>
-      <c r="F68" s="122"/>
-      <c r="G68" s="122"/>
-      <c r="H68" s="122"/>
-      <c r="I68" s="122"/>
-      <c r="J68" s="122"/>
-      <c r="K68" s="122"/>
-      <c r="L68" s="122"/>
-      <c r="M68" s="122"/>
-      <c r="N68" s="148"/>
-      <c r="O68" s="153"/>
-      <c r="P68" s="148"/>
-      <c r="Q68" s="153"/>
-    </row>
-    <row r="69" spans="1:17" s="55" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+      <c r="C68" s="120"/>
+      <c r="D68" s="120"/>
+      <c r="E68" s="129"/>
+      <c r="F68" s="120"/>
+      <c r="G68" s="120"/>
+      <c r="H68" s="120"/>
+      <c r="I68" s="120"/>
+      <c r="J68" s="120"/>
+      <c r="K68" s="120"/>
+      <c r="L68" s="120"/>
+      <c r="M68" s="120"/>
+      <c r="N68" s="129"/>
+      <c r="O68" s="123"/>
+      <c r="P68" s="129"/>
+      <c r="Q68" s="123"/>
+    </row>
+    <row r="69" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="95" t="str">
         <f>_xlfn.XLOOKUP(B69,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12112,23 +12112,23 @@
       <c r="B69" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="122"/>
-      <c r="D69" s="122"/>
-      <c r="E69" s="148"/>
-      <c r="F69" s="122"/>
-      <c r="G69" s="122"/>
-      <c r="H69" s="122"/>
-      <c r="I69" s="122"/>
-      <c r="J69" s="122"/>
-      <c r="K69" s="122"/>
-      <c r="L69" s="122"/>
-      <c r="M69" s="122"/>
-      <c r="N69" s="148"/>
-      <c r="O69" s="153"/>
-      <c r="P69" s="148"/>
-      <c r="Q69" s="153"/>
-    </row>
-    <row r="70" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C69" s="120"/>
+      <c r="D69" s="120"/>
+      <c r="E69" s="129"/>
+      <c r="F69" s="120"/>
+      <c r="G69" s="120"/>
+      <c r="H69" s="120"/>
+      <c r="I69" s="120"/>
+      <c r="J69" s="120"/>
+      <c r="K69" s="120"/>
+      <c r="L69" s="120"/>
+      <c r="M69" s="120"/>
+      <c r="N69" s="129"/>
+      <c r="O69" s="123"/>
+      <c r="P69" s="129"/>
+      <c r="Q69" s="123"/>
+    </row>
+    <row r="70" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="str">
         <f>_xlfn.XLOOKUP(B70,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12136,52 +12136,52 @@
       <c r="B70" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C70" s="145">
+      <c r="C70" s="119">
         <v>4</v>
       </c>
-      <c r="D70" s="145" t="s">
+      <c r="D70" s="119" t="s">
         <v>250</v>
       </c>
-      <c r="E70" s="147" t="s">
+      <c r="E70" s="125" t="s">
         <v>251</v>
       </c>
-      <c r="F70" s="145" t="s">
+      <c r="F70" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G70" s="145"/>
-      <c r="H70" s="145" t="s">
+      <c r="G70" s="119"/>
+      <c r="H70" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I70" s="145"/>
-      <c r="J70" s="145">
+      <c r="I70" s="119"/>
+      <c r="J70" s="119">
         <v>3</v>
       </c>
-      <c r="K70" s="145">
+      <c r="K70" s="119">
         <f>J70*12</f>
         <v>36</v>
       </c>
-      <c r="L70" s="145">
+      <c r="L70" s="119">
         <f>36*J70</f>
         <v>108</v>
       </c>
-      <c r="M70" s="145">
+      <c r="M70" s="119">
         <f>SUM(K70:L70)</f>
         <v>144</v>
       </c>
-      <c r="N70" s="152" t="s">
+      <c r="N70" s="122" t="s">
         <v>252</v>
       </c>
-      <c r="O70" s="152" t="s">
+      <c r="O70" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P70" s="147" t="s">
+      <c r="P70" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="Q70" s="152" t="s">
+      <c r="Q70" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="str">
         <f>_xlfn.XLOOKUP(B71,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12189,23 +12189,23 @@
       <c r="B71" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="122"/>
-      <c r="D71" s="122"/>
-      <c r="E71" s="148"/>
-      <c r="F71" s="122"/>
-      <c r="G71" s="122"/>
-      <c r="H71" s="122"/>
-      <c r="I71" s="122"/>
-      <c r="J71" s="122"/>
-      <c r="K71" s="122"/>
-      <c r="L71" s="122"/>
-      <c r="M71" s="122"/>
-      <c r="N71" s="153"/>
-      <c r="O71" s="153"/>
-      <c r="P71" s="148"/>
-      <c r="Q71" s="153"/>
-    </row>
-    <row r="72" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C71" s="120"/>
+      <c r="D71" s="120"/>
+      <c r="E71" s="129"/>
+      <c r="F71" s="120"/>
+      <c r="G71" s="120"/>
+      <c r="H71" s="120"/>
+      <c r="I71" s="120"/>
+      <c r="J71" s="120"/>
+      <c r="K71" s="120"/>
+      <c r="L71" s="120"/>
+      <c r="M71" s="120"/>
+      <c r="N71" s="123"/>
+      <c r="O71" s="123"/>
+      <c r="P71" s="129"/>
+      <c r="Q71" s="123"/>
+    </row>
+    <row r="72" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="str">
         <f>_xlfn.XLOOKUP(B72,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12213,23 +12213,23 @@
       <c r="B72" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="122"/>
-      <c r="D72" s="122"/>
-      <c r="E72" s="148"/>
-      <c r="F72" s="122"/>
-      <c r="G72" s="122"/>
-      <c r="H72" s="122"/>
-      <c r="I72" s="122"/>
-      <c r="J72" s="122"/>
-      <c r="K72" s="122"/>
-      <c r="L72" s="122"/>
-      <c r="M72" s="122"/>
-      <c r="N72" s="153"/>
-      <c r="O72" s="153"/>
-      <c r="P72" s="148"/>
-      <c r="Q72" s="153"/>
-    </row>
-    <row r="73" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C72" s="120"/>
+      <c r="D72" s="120"/>
+      <c r="E72" s="129"/>
+      <c r="F72" s="120"/>
+      <c r="G72" s="120"/>
+      <c r="H72" s="120"/>
+      <c r="I72" s="120"/>
+      <c r="J72" s="120"/>
+      <c r="K72" s="120"/>
+      <c r="L72" s="120"/>
+      <c r="M72" s="120"/>
+      <c r="N72" s="123"/>
+      <c r="O72" s="123"/>
+      <c r="P72" s="129"/>
+      <c r="Q72" s="123"/>
+    </row>
+    <row r="73" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="str">
         <f>_xlfn.XLOOKUP(B73,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12237,23 +12237,23 @@
       <c r="B73" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="122"/>
-      <c r="D73" s="122"/>
-      <c r="E73" s="148"/>
-      <c r="F73" s="122"/>
-      <c r="G73" s="122"/>
-      <c r="H73" s="122"/>
-      <c r="I73" s="122"/>
-      <c r="J73" s="122"/>
-      <c r="K73" s="122"/>
-      <c r="L73" s="122"/>
-      <c r="M73" s="122"/>
-      <c r="N73" s="153"/>
-      <c r="O73" s="153"/>
-      <c r="P73" s="148"/>
-      <c r="Q73" s="153"/>
-    </row>
-    <row r="74" spans="1:17" s="55" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+      <c r="C73" s="120"/>
+      <c r="D73" s="120"/>
+      <c r="E73" s="129"/>
+      <c r="F73" s="120"/>
+      <c r="G73" s="120"/>
+      <c r="H73" s="120"/>
+      <c r="I73" s="120"/>
+      <c r="J73" s="120"/>
+      <c r="K73" s="120"/>
+      <c r="L73" s="120"/>
+      <c r="M73" s="120"/>
+      <c r="N73" s="123"/>
+      <c r="O73" s="123"/>
+      <c r="P73" s="129"/>
+      <c r="Q73" s="123"/>
+    </row>
+    <row r="74" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="95" t="str">
         <f>_xlfn.XLOOKUP(B74,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12261,23 +12261,23 @@
       <c r="B74" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="122"/>
-      <c r="D74" s="122"/>
-      <c r="E74" s="158"/>
-      <c r="F74" s="159"/>
-      <c r="G74" s="159"/>
-      <c r="H74" s="159"/>
-      <c r="I74" s="159"/>
-      <c r="J74" s="159"/>
-      <c r="K74" s="159"/>
-      <c r="L74" s="159"/>
-      <c r="M74" s="159"/>
-      <c r="N74" s="160"/>
-      <c r="O74" s="160"/>
-      <c r="P74" s="149"/>
-      <c r="Q74" s="153"/>
-    </row>
-    <row r="75" spans="1:17" s="55" customFormat="1" ht="346.5" x14ac:dyDescent="0.35">
+      <c r="C74" s="120"/>
+      <c r="D74" s="120"/>
+      <c r="E74" s="132"/>
+      <c r="F74" s="131"/>
+      <c r="G74" s="131"/>
+      <c r="H74" s="131"/>
+      <c r="I74" s="131"/>
+      <c r="J74" s="131"/>
+      <c r="K74" s="131"/>
+      <c r="L74" s="131"/>
+      <c r="M74" s="131"/>
+      <c r="N74" s="133"/>
+      <c r="O74" s="133"/>
+      <c r="P74" s="130"/>
+      <c r="Q74" s="123"/>
+    </row>
+    <row r="75" spans="1:17" s="55" customFormat="1" ht="378.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="96" t="str">
         <f>_xlfn.XLOOKUP(B75,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12330,7 +12330,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="str">
         <f>_xlfn.XLOOKUP(B76,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12338,52 +12338,52 @@
       <c r="B76" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="145">
+      <c r="C76" s="119">
         <v>4</v>
       </c>
-      <c r="D76" s="145" t="s">
+      <c r="D76" s="119" t="s">
         <v>257</v>
       </c>
-      <c r="E76" s="152" t="s">
+      <c r="E76" s="122" t="s">
         <v>258</v>
       </c>
-      <c r="F76" s="145" t="s">
+      <c r="F76" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G76" s="145"/>
-      <c r="H76" s="145" t="s">
+      <c r="G76" s="119"/>
+      <c r="H76" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I76" s="145"/>
-      <c r="J76" s="145">
+      <c r="I76" s="119"/>
+      <c r="J76" s="119">
         <v>3</v>
       </c>
-      <c r="K76" s="145">
+      <c r="K76" s="119">
         <f>J76*12</f>
         <v>36</v>
       </c>
-      <c r="L76" s="145">
+      <c r="L76" s="119">
         <f>36*J76</f>
         <v>108</v>
       </c>
-      <c r="M76" s="145">
+      <c r="M76" s="119">
         <f>SUM(K76:L76)</f>
         <v>144</v>
       </c>
-      <c r="N76" s="152" t="s">
+      <c r="N76" s="122" t="s">
         <v>259</v>
       </c>
-      <c r="O76" s="152" t="s">
+      <c r="O76" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P76" s="152" t="s">
+      <c r="P76" s="122" t="s">
         <v>260</v>
       </c>
-      <c r="Q76" s="152" t="s">
+      <c r="Q76" s="122" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="str">
         <f>_xlfn.XLOOKUP(B77,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12391,23 +12391,23 @@
       <c r="B77" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C77" s="122"/>
-      <c r="D77" s="122"/>
-      <c r="E77" s="153"/>
-      <c r="F77" s="122"/>
-      <c r="G77" s="122"/>
-      <c r="H77" s="122"/>
-      <c r="I77" s="122"/>
-      <c r="J77" s="122"/>
-      <c r="K77" s="122"/>
-      <c r="L77" s="122"/>
-      <c r="M77" s="122"/>
-      <c r="N77" s="153"/>
-      <c r="O77" s="153"/>
-      <c r="P77" s="153"/>
-      <c r="Q77" s="153"/>
-    </row>
-    <row r="78" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C77" s="120"/>
+      <c r="D77" s="120"/>
+      <c r="E77" s="123"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="120"/>
+      <c r="H77" s="120"/>
+      <c r="I77" s="120"/>
+      <c r="J77" s="120"/>
+      <c r="K77" s="120"/>
+      <c r="L77" s="120"/>
+      <c r="M77" s="120"/>
+      <c r="N77" s="123"/>
+      <c r="O77" s="123"/>
+      <c r="P77" s="123"/>
+      <c r="Q77" s="123"/>
+    </row>
+    <row r="78" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="str">
         <f>_xlfn.XLOOKUP(B78,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12415,23 +12415,23 @@
       <c r="B78" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C78" s="122"/>
-      <c r="D78" s="122"/>
-      <c r="E78" s="153"/>
-      <c r="F78" s="122"/>
-      <c r="G78" s="122"/>
-      <c r="H78" s="122"/>
-      <c r="I78" s="122"/>
-      <c r="J78" s="122"/>
-      <c r="K78" s="122"/>
-      <c r="L78" s="122"/>
-      <c r="M78" s="122"/>
-      <c r="N78" s="153"/>
-      <c r="O78" s="153"/>
-      <c r="P78" s="153"/>
-      <c r="Q78" s="153"/>
-    </row>
-    <row r="79" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C78" s="120"/>
+      <c r="D78" s="120"/>
+      <c r="E78" s="123"/>
+      <c r="F78" s="120"/>
+      <c r="G78" s="120"/>
+      <c r="H78" s="120"/>
+      <c r="I78" s="120"/>
+      <c r="J78" s="120"/>
+      <c r="K78" s="120"/>
+      <c r="L78" s="120"/>
+      <c r="M78" s="120"/>
+      <c r="N78" s="123"/>
+      <c r="O78" s="123"/>
+      <c r="P78" s="123"/>
+      <c r="Q78" s="123"/>
+    </row>
+    <row r="79" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="str">
         <f>_xlfn.XLOOKUP(B79,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12439,23 +12439,23 @@
       <c r="B79" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C79" s="122"/>
-      <c r="D79" s="122"/>
-      <c r="E79" s="153"/>
-      <c r="F79" s="122"/>
-      <c r="G79" s="122"/>
-      <c r="H79" s="122"/>
-      <c r="I79" s="122"/>
-      <c r="J79" s="122"/>
-      <c r="K79" s="122"/>
-      <c r="L79" s="122"/>
-      <c r="M79" s="122"/>
-      <c r="N79" s="153"/>
-      <c r="O79" s="153"/>
-      <c r="P79" s="153"/>
-      <c r="Q79" s="153"/>
-    </row>
-    <row r="80" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C79" s="120"/>
+      <c r="D79" s="120"/>
+      <c r="E79" s="123"/>
+      <c r="F79" s="120"/>
+      <c r="G79" s="120"/>
+      <c r="H79" s="120"/>
+      <c r="I79" s="120"/>
+      <c r="J79" s="120"/>
+      <c r="K79" s="120"/>
+      <c r="L79" s="120"/>
+      <c r="M79" s="120"/>
+      <c r="N79" s="123"/>
+      <c r="O79" s="123"/>
+      <c r="P79" s="123"/>
+      <c r="Q79" s="123"/>
+    </row>
+    <row r="80" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="95" t="str">
         <f>_xlfn.XLOOKUP(B80,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12463,23 +12463,23 @@
       <c r="B80" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C80" s="122"/>
-      <c r="D80" s="122"/>
-      <c r="E80" s="153"/>
-      <c r="F80" s="122"/>
-      <c r="G80" s="122"/>
-      <c r="H80" s="122"/>
-      <c r="I80" s="122"/>
-      <c r="J80" s="122"/>
-      <c r="K80" s="122"/>
-      <c r="L80" s="122"/>
-      <c r="M80" s="122"/>
-      <c r="N80" s="153"/>
-      <c r="O80" s="153"/>
-      <c r="P80" s="153"/>
-      <c r="Q80" s="153"/>
-    </row>
-    <row r="81" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C80" s="120"/>
+      <c r="D80" s="120"/>
+      <c r="E80" s="123"/>
+      <c r="F80" s="120"/>
+      <c r="G80" s="120"/>
+      <c r="H80" s="120"/>
+      <c r="I80" s="120"/>
+      <c r="J80" s="120"/>
+      <c r="K80" s="120"/>
+      <c r="L80" s="120"/>
+      <c r="M80" s="120"/>
+      <c r="N80" s="123"/>
+      <c r="O80" s="123"/>
+      <c r="P80" s="123"/>
+      <c r="Q80" s="123"/>
+    </row>
+    <row r="81" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="str">
         <f>_xlfn.XLOOKUP(B81,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12487,52 +12487,52 @@
       <c r="B81" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C81" s="145">
+      <c r="C81" s="119">
         <v>4</v>
       </c>
-      <c r="D81" s="145" t="s">
+      <c r="D81" s="119" t="s">
         <v>262</v>
       </c>
-      <c r="E81" s="152" t="s">
+      <c r="E81" s="122" t="s">
         <v>263</v>
       </c>
-      <c r="F81" s="145" t="s">
+      <c r="F81" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G81" s="145"/>
-      <c r="H81" s="145" t="s">
+      <c r="G81" s="119"/>
+      <c r="H81" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I81" s="145"/>
-      <c r="J81" s="145">
+      <c r="I81" s="119"/>
+      <c r="J81" s="119">
         <v>3</v>
       </c>
-      <c r="K81" s="145">
+      <c r="K81" s="119">
         <f>J81*12</f>
         <v>36</v>
       </c>
-      <c r="L81" s="145">
+      <c r="L81" s="119">
         <f>36*J81</f>
         <v>108</v>
       </c>
-      <c r="M81" s="145">
+      <c r="M81" s="119">
         <f>SUM(K81:L81)</f>
         <v>144</v>
       </c>
-      <c r="N81" s="152" t="s">
+      <c r="N81" s="122" t="s">
         <v>264</v>
       </c>
-      <c r="O81" s="152" t="s">
+      <c r="O81" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P81" s="152" t="s">
+      <c r="P81" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q81" s="152" t="s">
+      <c r="Q81" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="str">
         <f>_xlfn.XLOOKUP(B82,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12540,23 +12540,23 @@
       <c r="B82" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C82" s="122"/>
-      <c r="D82" s="122"/>
-      <c r="E82" s="153"/>
-      <c r="F82" s="122"/>
-      <c r="G82" s="122"/>
-      <c r="H82" s="122"/>
-      <c r="I82" s="122"/>
-      <c r="J82" s="122"/>
-      <c r="K82" s="122"/>
-      <c r="L82" s="122"/>
-      <c r="M82" s="122"/>
-      <c r="N82" s="153"/>
-      <c r="O82" s="153"/>
-      <c r="P82" s="153"/>
-      <c r="Q82" s="153"/>
-    </row>
-    <row r="83" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C82" s="120"/>
+      <c r="D82" s="120"/>
+      <c r="E82" s="123"/>
+      <c r="F82" s="120"/>
+      <c r="G82" s="120"/>
+      <c r="H82" s="120"/>
+      <c r="I82" s="120"/>
+      <c r="J82" s="120"/>
+      <c r="K82" s="120"/>
+      <c r="L82" s="120"/>
+      <c r="M82" s="120"/>
+      <c r="N82" s="123"/>
+      <c r="O82" s="123"/>
+      <c r="P82" s="123"/>
+      <c r="Q82" s="123"/>
+    </row>
+    <row r="83" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A83" s="24" t="str">
         <f>_xlfn.XLOOKUP(B83,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12564,23 +12564,23 @@
       <c r="B83" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C83" s="122"/>
-      <c r="D83" s="122"/>
-      <c r="E83" s="153"/>
-      <c r="F83" s="122"/>
-      <c r="G83" s="122"/>
-      <c r="H83" s="122"/>
-      <c r="I83" s="122"/>
-      <c r="J83" s="122"/>
-      <c r="K83" s="122"/>
-      <c r="L83" s="122"/>
-      <c r="M83" s="122"/>
-      <c r="N83" s="153"/>
-      <c r="O83" s="153"/>
-      <c r="P83" s="153"/>
-      <c r="Q83" s="153"/>
-    </row>
-    <row r="84" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C83" s="120"/>
+      <c r="D83" s="120"/>
+      <c r="E83" s="123"/>
+      <c r="F83" s="120"/>
+      <c r="G83" s="120"/>
+      <c r="H83" s="120"/>
+      <c r="I83" s="120"/>
+      <c r="J83" s="120"/>
+      <c r="K83" s="120"/>
+      <c r="L83" s="120"/>
+      <c r="M83" s="120"/>
+      <c r="N83" s="123"/>
+      <c r="O83" s="123"/>
+      <c r="P83" s="123"/>
+      <c r="Q83" s="123"/>
+    </row>
+    <row r="84" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="95" t="str">
         <f>_xlfn.XLOOKUP(B84,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12588,23 +12588,23 @@
       <c r="B84" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C84" s="122"/>
-      <c r="D84" s="122"/>
-      <c r="E84" s="153"/>
-      <c r="F84" s="122"/>
-      <c r="G84" s="122"/>
-      <c r="H84" s="122"/>
-      <c r="I84" s="122"/>
-      <c r="J84" s="122"/>
-      <c r="K84" s="122"/>
-      <c r="L84" s="122"/>
-      <c r="M84" s="122"/>
-      <c r="N84" s="153"/>
-      <c r="O84" s="153"/>
-      <c r="P84" s="153"/>
-      <c r="Q84" s="153"/>
-    </row>
-    <row r="85" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C84" s="120"/>
+      <c r="D84" s="120"/>
+      <c r="E84" s="123"/>
+      <c r="F84" s="120"/>
+      <c r="G84" s="120"/>
+      <c r="H84" s="120"/>
+      <c r="I84" s="120"/>
+      <c r="J84" s="120"/>
+      <c r="K84" s="120"/>
+      <c r="L84" s="120"/>
+      <c r="M84" s="120"/>
+      <c r="N84" s="123"/>
+      <c r="O84" s="123"/>
+      <c r="P84" s="123"/>
+      <c r="Q84" s="123"/>
+    </row>
+    <row r="85" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="str">
         <f>_xlfn.XLOOKUP(B85,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12612,52 +12612,52 @@
       <c r="B85" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C85" s="145">
+      <c r="C85" s="119">
         <v>5</v>
       </c>
-      <c r="D85" s="145" t="s">
+      <c r="D85" s="119" t="s">
         <v>265</v>
       </c>
-      <c r="E85" s="152" t="s">
+      <c r="E85" s="122" t="s">
         <v>266</v>
       </c>
-      <c r="F85" s="145" t="s">
+      <c r="F85" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G85" s="145"/>
-      <c r="H85" s="145" t="s">
+      <c r="G85" s="119"/>
+      <c r="H85" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I85" s="145"/>
-      <c r="J85" s="145">
+      <c r="I85" s="119"/>
+      <c r="J85" s="119">
         <v>3</v>
       </c>
-      <c r="K85" s="145">
+      <c r="K85" s="119">
         <f>J85*12</f>
         <v>36</v>
       </c>
-      <c r="L85" s="145">
+      <c r="L85" s="119">
         <f>36*J85</f>
         <v>108</v>
       </c>
-      <c r="M85" s="145">
+      <c r="M85" s="119">
         <f>SUM(K85:L85)</f>
         <v>144</v>
       </c>
-      <c r="N85" s="152" t="s">
+      <c r="N85" s="122" t="s">
         <v>267</v>
       </c>
-      <c r="O85" s="152" t="s">
+      <c r="O85" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P85" s="152" t="s">
+      <c r="P85" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q85" s="152" t="s">
+      <c r="Q85" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="str">
         <f>_xlfn.XLOOKUP(B86,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12665,23 +12665,23 @@
       <c r="B86" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C86" s="122"/>
-      <c r="D86" s="122"/>
-      <c r="E86" s="153"/>
-      <c r="F86" s="122"/>
-      <c r="G86" s="122"/>
-      <c r="H86" s="122"/>
-      <c r="I86" s="122"/>
-      <c r="J86" s="122"/>
-      <c r="K86" s="122"/>
-      <c r="L86" s="122"/>
-      <c r="M86" s="122"/>
-      <c r="N86" s="153"/>
-      <c r="O86" s="153"/>
-      <c r="P86" s="153"/>
-      <c r="Q86" s="153"/>
-    </row>
-    <row r="87" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C86" s="120"/>
+      <c r="D86" s="120"/>
+      <c r="E86" s="123"/>
+      <c r="F86" s="120"/>
+      <c r="G86" s="120"/>
+      <c r="H86" s="120"/>
+      <c r="I86" s="120"/>
+      <c r="J86" s="120"/>
+      <c r="K86" s="120"/>
+      <c r="L86" s="120"/>
+      <c r="M86" s="120"/>
+      <c r="N86" s="123"/>
+      <c r="O86" s="123"/>
+      <c r="P86" s="123"/>
+      <c r="Q86" s="123"/>
+    </row>
+    <row r="87" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="str">
         <f>_xlfn.XLOOKUP(B87,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12689,23 +12689,23 @@
       <c r="B87" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C87" s="122"/>
-      <c r="D87" s="122"/>
-      <c r="E87" s="153"/>
-      <c r="F87" s="122"/>
-      <c r="G87" s="122"/>
-      <c r="H87" s="122"/>
-      <c r="I87" s="122"/>
-      <c r="J87" s="122"/>
-      <c r="K87" s="122"/>
-      <c r="L87" s="122"/>
-      <c r="M87" s="122"/>
-      <c r="N87" s="153"/>
-      <c r="O87" s="153"/>
-      <c r="P87" s="153"/>
-      <c r="Q87" s="153"/>
-    </row>
-    <row r="88" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C87" s="120"/>
+      <c r="D87" s="120"/>
+      <c r="E87" s="123"/>
+      <c r="F87" s="120"/>
+      <c r="G87" s="120"/>
+      <c r="H87" s="120"/>
+      <c r="I87" s="120"/>
+      <c r="J87" s="120"/>
+      <c r="K87" s="120"/>
+      <c r="L87" s="120"/>
+      <c r="M87" s="120"/>
+      <c r="N87" s="123"/>
+      <c r="O87" s="123"/>
+      <c r="P87" s="123"/>
+      <c r="Q87" s="123"/>
+    </row>
+    <row r="88" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="str">
         <f>_xlfn.XLOOKUP(B88,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12713,23 +12713,23 @@
       <c r="B88" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C88" s="122"/>
-      <c r="D88" s="122"/>
-      <c r="E88" s="153"/>
-      <c r="F88" s="122"/>
-      <c r="G88" s="122"/>
-      <c r="H88" s="122"/>
-      <c r="I88" s="122"/>
-      <c r="J88" s="122"/>
-      <c r="K88" s="122"/>
-      <c r="L88" s="122"/>
-      <c r="M88" s="122"/>
-      <c r="N88" s="153"/>
-      <c r="O88" s="153"/>
-      <c r="P88" s="153"/>
-      <c r="Q88" s="153"/>
-    </row>
-    <row r="89" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C88" s="120"/>
+      <c r="D88" s="120"/>
+      <c r="E88" s="123"/>
+      <c r="F88" s="120"/>
+      <c r="G88" s="120"/>
+      <c r="H88" s="120"/>
+      <c r="I88" s="120"/>
+      <c r="J88" s="120"/>
+      <c r="K88" s="120"/>
+      <c r="L88" s="120"/>
+      <c r="M88" s="120"/>
+      <c r="N88" s="123"/>
+      <c r="O88" s="123"/>
+      <c r="P88" s="123"/>
+      <c r="Q88" s="123"/>
+    </row>
+    <row r="89" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="95" t="str">
         <f>_xlfn.XLOOKUP(B89,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12737,23 +12737,23 @@
       <c r="B89" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C89" s="122"/>
-      <c r="D89" s="122"/>
-      <c r="E89" s="153"/>
-      <c r="F89" s="122"/>
-      <c r="G89" s="122"/>
-      <c r="H89" s="122"/>
-      <c r="I89" s="122"/>
-      <c r="J89" s="122"/>
-      <c r="K89" s="122"/>
-      <c r="L89" s="122"/>
-      <c r="M89" s="122"/>
-      <c r="N89" s="153"/>
-      <c r="O89" s="153"/>
-      <c r="P89" s="153"/>
-      <c r="Q89" s="153"/>
-    </row>
-    <row r="90" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C89" s="120"/>
+      <c r="D89" s="120"/>
+      <c r="E89" s="123"/>
+      <c r="F89" s="120"/>
+      <c r="G89" s="120"/>
+      <c r="H89" s="120"/>
+      <c r="I89" s="120"/>
+      <c r="J89" s="120"/>
+      <c r="K89" s="120"/>
+      <c r="L89" s="120"/>
+      <c r="M89" s="120"/>
+      <c r="N89" s="123"/>
+      <c r="O89" s="123"/>
+      <c r="P89" s="123"/>
+      <c r="Q89" s="123"/>
+    </row>
+    <row r="90" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="str">
         <f>_xlfn.XLOOKUP(B90,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12761,52 +12761,52 @@
       <c r="B90" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C90" s="145">
+      <c r="C90" s="119">
         <v>5</v>
       </c>
-      <c r="D90" s="145" t="s">
+      <c r="D90" s="119" t="s">
         <v>268</v>
       </c>
-      <c r="E90" s="152" t="s">
+      <c r="E90" s="122" t="s">
         <v>269</v>
       </c>
-      <c r="F90" s="145" t="s">
+      <c r="F90" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G90" s="145"/>
-      <c r="H90" s="145" t="s">
+      <c r="G90" s="119"/>
+      <c r="H90" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I90" s="145"/>
-      <c r="J90" s="145">
+      <c r="I90" s="119"/>
+      <c r="J90" s="119">
         <v>3</v>
       </c>
-      <c r="K90" s="145">
+      <c r="K90" s="119">
         <f>J90*12</f>
         <v>36</v>
       </c>
-      <c r="L90" s="145">
+      <c r="L90" s="119">
         <f>36*J90</f>
         <v>108</v>
       </c>
-      <c r="M90" s="145">
+      <c r="M90" s="119">
         <f>SUM(K90:L90)</f>
         <v>144</v>
       </c>
-      <c r="N90" s="152" t="s">
+      <c r="N90" s="122" t="s">
         <v>270</v>
       </c>
-      <c r="O90" s="152" t="s">
+      <c r="O90" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P90" s="152" t="s">
+      <c r="P90" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q90" s="152" t="s">
+      <c r="Q90" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="str">
         <f>_xlfn.XLOOKUP(B91,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12814,23 +12814,23 @@
       <c r="B91" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C91" s="122"/>
-      <c r="D91" s="122"/>
-      <c r="E91" s="153"/>
-      <c r="F91" s="122"/>
-      <c r="G91" s="122"/>
-      <c r="H91" s="122"/>
-      <c r="I91" s="122"/>
-      <c r="J91" s="122"/>
-      <c r="K91" s="122"/>
-      <c r="L91" s="122"/>
-      <c r="M91" s="122"/>
-      <c r="N91" s="153"/>
-      <c r="O91" s="153"/>
-      <c r="P91" s="153"/>
-      <c r="Q91" s="153"/>
-    </row>
-    <row r="92" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C91" s="120"/>
+      <c r="D91" s="120"/>
+      <c r="E91" s="123"/>
+      <c r="F91" s="120"/>
+      <c r="G91" s="120"/>
+      <c r="H91" s="120"/>
+      <c r="I91" s="120"/>
+      <c r="J91" s="120"/>
+      <c r="K91" s="120"/>
+      <c r="L91" s="120"/>
+      <c r="M91" s="120"/>
+      <c r="N91" s="123"/>
+      <c r="O91" s="123"/>
+      <c r="P91" s="123"/>
+      <c r="Q91" s="123"/>
+    </row>
+    <row r="92" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="str">
         <f>_xlfn.XLOOKUP(B92,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12838,23 +12838,23 @@
       <c r="B92" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C92" s="122"/>
-      <c r="D92" s="122"/>
-      <c r="E92" s="153"/>
-      <c r="F92" s="122"/>
-      <c r="G92" s="122"/>
-      <c r="H92" s="122"/>
-      <c r="I92" s="122"/>
-      <c r="J92" s="122"/>
-      <c r="K92" s="122"/>
-      <c r="L92" s="122"/>
-      <c r="M92" s="122"/>
-      <c r="N92" s="153"/>
-      <c r="O92" s="153"/>
-      <c r="P92" s="153"/>
-      <c r="Q92" s="153"/>
-    </row>
-    <row r="93" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C92" s="120"/>
+      <c r="D92" s="120"/>
+      <c r="E92" s="123"/>
+      <c r="F92" s="120"/>
+      <c r="G92" s="120"/>
+      <c r="H92" s="120"/>
+      <c r="I92" s="120"/>
+      <c r="J92" s="120"/>
+      <c r="K92" s="120"/>
+      <c r="L92" s="120"/>
+      <c r="M92" s="120"/>
+      <c r="N92" s="123"/>
+      <c r="O92" s="123"/>
+      <c r="P92" s="123"/>
+      <c r="Q92" s="123"/>
+    </row>
+    <row r="93" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="str">
         <f>_xlfn.XLOOKUP(B93,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12862,23 +12862,23 @@
       <c r="B93" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="C93" s="122"/>
-      <c r="D93" s="122"/>
-      <c r="E93" s="153"/>
-      <c r="F93" s="122"/>
-      <c r="G93" s="122"/>
-      <c r="H93" s="122"/>
-      <c r="I93" s="122"/>
-      <c r="J93" s="122"/>
-      <c r="K93" s="122"/>
-      <c r="L93" s="122"/>
-      <c r="M93" s="122"/>
-      <c r="N93" s="153"/>
-      <c r="O93" s="153"/>
-      <c r="P93" s="153"/>
-      <c r="Q93" s="153"/>
-    </row>
-    <row r="94" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C93" s="120"/>
+      <c r="D93" s="120"/>
+      <c r="E93" s="123"/>
+      <c r="F93" s="120"/>
+      <c r="G93" s="120"/>
+      <c r="H93" s="120"/>
+      <c r="I93" s="120"/>
+      <c r="J93" s="120"/>
+      <c r="K93" s="120"/>
+      <c r="L93" s="120"/>
+      <c r="M93" s="120"/>
+      <c r="N93" s="123"/>
+      <c r="O93" s="123"/>
+      <c r="P93" s="123"/>
+      <c r="Q93" s="123"/>
+    </row>
+    <row r="94" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="95" t="str">
         <f>_xlfn.XLOOKUP(B94,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12886,23 +12886,23 @@
       <c r="B94" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="C94" s="122"/>
-      <c r="D94" s="122"/>
-      <c r="E94" s="153"/>
-      <c r="F94" s="122"/>
-      <c r="G94" s="122"/>
-      <c r="H94" s="122"/>
-      <c r="I94" s="122"/>
-      <c r="J94" s="122"/>
-      <c r="K94" s="122"/>
-      <c r="L94" s="122"/>
-      <c r="M94" s="122"/>
-      <c r="N94" s="153"/>
-      <c r="O94" s="153"/>
-      <c r="P94" s="153"/>
-      <c r="Q94" s="153"/>
-    </row>
-    <row r="95" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C94" s="120"/>
+      <c r="D94" s="120"/>
+      <c r="E94" s="123"/>
+      <c r="F94" s="120"/>
+      <c r="G94" s="120"/>
+      <c r="H94" s="120"/>
+      <c r="I94" s="120"/>
+      <c r="J94" s="120"/>
+      <c r="K94" s="120"/>
+      <c r="L94" s="120"/>
+      <c r="M94" s="120"/>
+      <c r="N94" s="123"/>
+      <c r="O94" s="123"/>
+      <c r="P94" s="123"/>
+      <c r="Q94" s="123"/>
+    </row>
+    <row r="95" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="str">
         <f>_xlfn.XLOOKUP(B95,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12910,52 +12910,52 @@
       <c r="B95" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C95" s="145">
+      <c r="C95" s="119">
         <v>5</v>
       </c>
-      <c r="D95" s="145" t="s">
+      <c r="D95" s="119" t="s">
         <v>271</v>
       </c>
-      <c r="E95" s="152" t="s">
+      <c r="E95" s="122" t="s">
         <v>272</v>
       </c>
-      <c r="F95" s="145" t="s">
+      <c r="F95" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G95" s="145"/>
-      <c r="H95" s="145" t="s">
+      <c r="G95" s="119"/>
+      <c r="H95" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I95" s="145"/>
-      <c r="J95" s="145">
+      <c r="I95" s="119"/>
+      <c r="J95" s="119">
         <v>3</v>
       </c>
-      <c r="K95" s="145">
+      <c r="K95" s="119">
         <f>J95*12</f>
         <v>36</v>
       </c>
-      <c r="L95" s="145">
+      <c r="L95" s="119">
         <f>36*J95</f>
         <v>108</v>
       </c>
-      <c r="M95" s="145">
+      <c r="M95" s="119">
         <f>SUM(K95:L95)</f>
         <v>144</v>
       </c>
-      <c r="N95" s="152" t="s">
+      <c r="N95" s="122" t="s">
         <v>273</v>
       </c>
-      <c r="O95" s="152" t="s">
+      <c r="O95" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P95" s="152" t="s">
+      <c r="P95" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q95" s="152" t="s">
+      <c r="Q95" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="str">
         <f>_xlfn.XLOOKUP(B96,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12963,23 +12963,23 @@
       <c r="B96" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="122"/>
-      <c r="D96" s="122"/>
-      <c r="E96" s="153"/>
-      <c r="F96" s="122"/>
-      <c r="G96" s="122"/>
-      <c r="H96" s="122"/>
-      <c r="I96" s="122"/>
-      <c r="J96" s="122"/>
-      <c r="K96" s="122"/>
-      <c r="L96" s="122"/>
-      <c r="M96" s="122"/>
-      <c r="N96" s="153"/>
-      <c r="O96" s="153"/>
-      <c r="P96" s="153"/>
-      <c r="Q96" s="153"/>
-    </row>
-    <row r="97" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C96" s="120"/>
+      <c r="D96" s="120"/>
+      <c r="E96" s="123"/>
+      <c r="F96" s="120"/>
+      <c r="G96" s="120"/>
+      <c r="H96" s="120"/>
+      <c r="I96" s="120"/>
+      <c r="J96" s="120"/>
+      <c r="K96" s="120"/>
+      <c r="L96" s="120"/>
+      <c r="M96" s="120"/>
+      <c r="N96" s="123"/>
+      <c r="O96" s="123"/>
+      <c r="P96" s="123"/>
+      <c r="Q96" s="123"/>
+    </row>
+    <row r="97" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="str">
         <f>_xlfn.XLOOKUP(B97,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12987,23 +12987,23 @@
       <c r="B97" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C97" s="122"/>
-      <c r="D97" s="122"/>
-      <c r="E97" s="153"/>
-      <c r="F97" s="122"/>
-      <c r="G97" s="122"/>
-      <c r="H97" s="122"/>
-      <c r="I97" s="122"/>
-      <c r="J97" s="122"/>
-      <c r="K97" s="122"/>
-      <c r="L97" s="122"/>
-      <c r="M97" s="122"/>
-      <c r="N97" s="153"/>
-      <c r="O97" s="153"/>
-      <c r="P97" s="153"/>
-      <c r="Q97" s="153"/>
-    </row>
-    <row r="98" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C97" s="120"/>
+      <c r="D97" s="120"/>
+      <c r="E97" s="123"/>
+      <c r="F97" s="120"/>
+      <c r="G97" s="120"/>
+      <c r="H97" s="120"/>
+      <c r="I97" s="120"/>
+      <c r="J97" s="120"/>
+      <c r="K97" s="120"/>
+      <c r="L97" s="120"/>
+      <c r="M97" s="120"/>
+      <c r="N97" s="123"/>
+      <c r="O97" s="123"/>
+      <c r="P97" s="123"/>
+      <c r="Q97" s="123"/>
+    </row>
+    <row r="98" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A98" s="24" t="str">
         <f>_xlfn.XLOOKUP(B98,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13011,23 +13011,23 @@
       <c r="B98" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C98" s="122"/>
-      <c r="D98" s="122"/>
-      <c r="E98" s="153"/>
-      <c r="F98" s="122"/>
-      <c r="G98" s="122"/>
-      <c r="H98" s="122"/>
-      <c r="I98" s="122"/>
-      <c r="J98" s="122"/>
-      <c r="K98" s="122"/>
-      <c r="L98" s="122"/>
-      <c r="M98" s="122"/>
-      <c r="N98" s="153"/>
-      <c r="O98" s="153"/>
-      <c r="P98" s="153"/>
-      <c r="Q98" s="153"/>
-    </row>
-    <row r="99" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C98" s="120"/>
+      <c r="D98" s="120"/>
+      <c r="E98" s="123"/>
+      <c r="F98" s="120"/>
+      <c r="G98" s="120"/>
+      <c r="H98" s="120"/>
+      <c r="I98" s="120"/>
+      <c r="J98" s="120"/>
+      <c r="K98" s="120"/>
+      <c r="L98" s="120"/>
+      <c r="M98" s="120"/>
+      <c r="N98" s="123"/>
+      <c r="O98" s="123"/>
+      <c r="P98" s="123"/>
+      <c r="Q98" s="123"/>
+    </row>
+    <row r="99" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="95" t="str">
         <f>_xlfn.XLOOKUP(B99,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13035,23 +13035,23 @@
       <c r="B99" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C99" s="122"/>
-      <c r="D99" s="122"/>
-      <c r="E99" s="153"/>
-      <c r="F99" s="122"/>
-      <c r="G99" s="122"/>
-      <c r="H99" s="122"/>
-      <c r="I99" s="122"/>
-      <c r="J99" s="122"/>
-      <c r="K99" s="122"/>
-      <c r="L99" s="122"/>
-      <c r="M99" s="122"/>
-      <c r="N99" s="153"/>
-      <c r="O99" s="153"/>
-      <c r="P99" s="153"/>
-      <c r="Q99" s="153"/>
-    </row>
-    <row r="100" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C99" s="120"/>
+      <c r="D99" s="120"/>
+      <c r="E99" s="123"/>
+      <c r="F99" s="120"/>
+      <c r="G99" s="120"/>
+      <c r="H99" s="120"/>
+      <c r="I99" s="120"/>
+      <c r="J99" s="120"/>
+      <c r="K99" s="120"/>
+      <c r="L99" s="120"/>
+      <c r="M99" s="120"/>
+      <c r="N99" s="123"/>
+      <c r="O99" s="123"/>
+      <c r="P99" s="123"/>
+      <c r="Q99" s="123"/>
+    </row>
+    <row r="100" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A100" s="24" t="str">
         <f>_xlfn.XLOOKUP(B100,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13059,52 +13059,52 @@
       <c r="B100" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C100" s="145">
+      <c r="C100" s="119">
         <v>5</v>
       </c>
-      <c r="D100" s="145" t="s">
+      <c r="D100" s="119" t="s">
         <v>274</v>
       </c>
-      <c r="E100" s="152" t="s">
+      <c r="E100" s="122" t="s">
         <v>275</v>
       </c>
-      <c r="F100" s="145" t="s">
+      <c r="F100" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G100" s="145"/>
-      <c r="H100" s="145" t="s">
+      <c r="G100" s="119"/>
+      <c r="H100" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I100" s="145"/>
-      <c r="J100" s="145">
+      <c r="I100" s="119"/>
+      <c r="J100" s="119">
         <v>3</v>
       </c>
-      <c r="K100" s="145">
+      <c r="K100" s="119">
         <f>J100*12</f>
         <v>36</v>
       </c>
-      <c r="L100" s="145">
+      <c r="L100" s="119">
         <f>36*J100</f>
         <v>108</v>
       </c>
-      <c r="M100" s="145">
+      <c r="M100" s="119">
         <f>SUM(K100:L100)</f>
         <v>144</v>
       </c>
-      <c r="N100" s="152" t="s">
+      <c r="N100" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="O100" s="152" t="s">
+      <c r="O100" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P100" s="152" t="s">
+      <c r="P100" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="Q100" s="152" t="s">
+      <c r="Q100" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="str">
         <f>_xlfn.XLOOKUP(B101,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13112,23 +13112,23 @@
       <c r="B101" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C101" s="122"/>
-      <c r="D101" s="122"/>
-      <c r="E101" s="153"/>
-      <c r="F101" s="122"/>
-      <c r="G101" s="122"/>
-      <c r="H101" s="122"/>
-      <c r="I101" s="122"/>
-      <c r="J101" s="122"/>
-      <c r="K101" s="122"/>
-      <c r="L101" s="122"/>
-      <c r="M101" s="122"/>
-      <c r="N101" s="153"/>
-      <c r="O101" s="153"/>
-      <c r="P101" s="153"/>
-      <c r="Q101" s="153"/>
-    </row>
-    <row r="102" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C101" s="120"/>
+      <c r="D101" s="120"/>
+      <c r="E101" s="123"/>
+      <c r="F101" s="120"/>
+      <c r="G101" s="120"/>
+      <c r="H101" s="120"/>
+      <c r="I101" s="120"/>
+      <c r="J101" s="120"/>
+      <c r="K101" s="120"/>
+      <c r="L101" s="120"/>
+      <c r="M101" s="120"/>
+      <c r="N101" s="123"/>
+      <c r="O101" s="123"/>
+      <c r="P101" s="123"/>
+      <c r="Q101" s="123"/>
+    </row>
+    <row r="102" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A102" s="24" t="str">
         <f>_xlfn.XLOOKUP(B102,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13136,23 +13136,23 @@
       <c r="B102" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C102" s="122"/>
-      <c r="D102" s="122"/>
-      <c r="E102" s="153"/>
-      <c r="F102" s="122"/>
-      <c r="G102" s="122"/>
-      <c r="H102" s="122"/>
-      <c r="I102" s="122"/>
-      <c r="J102" s="122"/>
-      <c r="K102" s="122"/>
-      <c r="L102" s="122"/>
-      <c r="M102" s="122"/>
-      <c r="N102" s="153"/>
-      <c r="O102" s="153"/>
-      <c r="P102" s="153"/>
-      <c r="Q102" s="153"/>
-    </row>
-    <row r="103" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C102" s="120"/>
+      <c r="D102" s="120"/>
+      <c r="E102" s="123"/>
+      <c r="F102" s="120"/>
+      <c r="G102" s="120"/>
+      <c r="H102" s="120"/>
+      <c r="I102" s="120"/>
+      <c r="J102" s="120"/>
+      <c r="K102" s="120"/>
+      <c r="L102" s="120"/>
+      <c r="M102" s="120"/>
+      <c r="N102" s="123"/>
+      <c r="O102" s="123"/>
+      <c r="P102" s="123"/>
+      <c r="Q102" s="123"/>
+    </row>
+    <row r="103" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="95" t="str">
         <f>_xlfn.XLOOKUP(B103,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13160,23 +13160,23 @@
       <c r="B103" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="122"/>
-      <c r="D103" s="122"/>
-      <c r="E103" s="154"/>
-      <c r="F103" s="122"/>
-      <c r="G103" s="122"/>
-      <c r="H103" s="122"/>
-      <c r="I103" s="122"/>
-      <c r="J103" s="122"/>
-      <c r="K103" s="122"/>
-      <c r="L103" s="122"/>
-      <c r="M103" s="122"/>
-      <c r="N103" s="153"/>
-      <c r="O103" s="153"/>
-      <c r="P103" s="153"/>
-      <c r="Q103" s="153"/>
-    </row>
-    <row r="104" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C103" s="120"/>
+      <c r="D103" s="120"/>
+      <c r="E103" s="124"/>
+      <c r="F103" s="120"/>
+      <c r="G103" s="120"/>
+      <c r="H103" s="120"/>
+      <c r="I103" s="120"/>
+      <c r="J103" s="120"/>
+      <c r="K103" s="120"/>
+      <c r="L103" s="120"/>
+      <c r="M103" s="120"/>
+      <c r="N103" s="123"/>
+      <c r="O103" s="123"/>
+      <c r="P103" s="123"/>
+      <c r="Q103" s="123"/>
+    </row>
+    <row r="104" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="str">
         <f>_xlfn.XLOOKUP(B104,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13184,52 +13184,52 @@
       <c r="B104" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C104" s="145">
+      <c r="C104" s="119">
         <v>5</v>
       </c>
-      <c r="D104" s="145" t="s">
+      <c r="D104" s="119" t="s">
         <v>278</v>
       </c>
-      <c r="E104" s="148" t="s">
+      <c r="E104" s="129" t="s">
         <v>279</v>
       </c>
-      <c r="F104" s="145" t="s">
+      <c r="F104" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G104" s="145"/>
-      <c r="H104" s="145" t="s">
+      <c r="G104" s="119"/>
+      <c r="H104" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I104" s="145"/>
-      <c r="J104" s="145">
+      <c r="I104" s="119"/>
+      <c r="J104" s="119">
         <v>3</v>
       </c>
-      <c r="K104" s="145">
+      <c r="K104" s="119">
         <f>J104*12</f>
         <v>36</v>
       </c>
-      <c r="L104" s="145">
+      <c r="L104" s="119">
         <f>36*J104</f>
         <v>108</v>
       </c>
-      <c r="M104" s="145">
+      <c r="M104" s="119">
         <f>SUM(K104:L104)</f>
         <v>144</v>
       </c>
-      <c r="N104" s="152" t="s">
+      <c r="N104" s="122" t="s">
         <v>280</v>
       </c>
-      <c r="O104" s="152" t="s">
+      <c r="O104" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P104" s="152" t="s">
+      <c r="P104" s="122" t="s">
         <v>277</v>
       </c>
-      <c r="Q104" s="152" t="s">
+      <c r="Q104" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A105" s="24" t="str">
         <f>_xlfn.XLOOKUP(B105,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13237,23 +13237,23 @@
       <c r="B105" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="122"/>
-      <c r="D105" s="122"/>
-      <c r="E105" s="148"/>
-      <c r="F105" s="122"/>
-      <c r="G105" s="122"/>
-      <c r="H105" s="122"/>
-      <c r="I105" s="122"/>
-      <c r="J105" s="122"/>
-      <c r="K105" s="122"/>
-      <c r="L105" s="122"/>
-      <c r="M105" s="122"/>
-      <c r="N105" s="153"/>
-      <c r="O105" s="153"/>
-      <c r="P105" s="153"/>
-      <c r="Q105" s="153"/>
-    </row>
-    <row r="106" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C105" s="120"/>
+      <c r="D105" s="120"/>
+      <c r="E105" s="129"/>
+      <c r="F105" s="120"/>
+      <c r="G105" s="120"/>
+      <c r="H105" s="120"/>
+      <c r="I105" s="120"/>
+      <c r="J105" s="120"/>
+      <c r="K105" s="120"/>
+      <c r="L105" s="120"/>
+      <c r="M105" s="120"/>
+      <c r="N105" s="123"/>
+      <c r="O105" s="123"/>
+      <c r="P105" s="123"/>
+      <c r="Q105" s="123"/>
+    </row>
+    <row r="106" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="str">
         <f>_xlfn.XLOOKUP(B106,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13261,23 +13261,23 @@
       <c r="B106" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C106" s="122"/>
-      <c r="D106" s="122"/>
-      <c r="E106" s="148"/>
-      <c r="F106" s="122"/>
-      <c r="G106" s="122"/>
-      <c r="H106" s="122"/>
-      <c r="I106" s="122"/>
-      <c r="J106" s="122"/>
-      <c r="K106" s="122"/>
-      <c r="L106" s="122"/>
-      <c r="M106" s="122"/>
-      <c r="N106" s="153"/>
-      <c r="O106" s="153"/>
-      <c r="P106" s="153"/>
-      <c r="Q106" s="153"/>
-    </row>
-    <row r="107" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C106" s="120"/>
+      <c r="D106" s="120"/>
+      <c r="E106" s="129"/>
+      <c r="F106" s="120"/>
+      <c r="G106" s="120"/>
+      <c r="H106" s="120"/>
+      <c r="I106" s="120"/>
+      <c r="J106" s="120"/>
+      <c r="K106" s="120"/>
+      <c r="L106" s="120"/>
+      <c r="M106" s="120"/>
+      <c r="N106" s="123"/>
+      <c r="O106" s="123"/>
+      <c r="P106" s="123"/>
+      <c r="Q106" s="123"/>
+    </row>
+    <row r="107" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="str">
         <f>_xlfn.XLOOKUP(B107,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13285,23 +13285,23 @@
       <c r="B107" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C107" s="122"/>
-      <c r="D107" s="122"/>
-      <c r="E107" s="148"/>
-      <c r="F107" s="122"/>
-      <c r="G107" s="122"/>
-      <c r="H107" s="122"/>
-      <c r="I107" s="122"/>
-      <c r="J107" s="122"/>
-      <c r="K107" s="122"/>
-      <c r="L107" s="122"/>
-      <c r="M107" s="122"/>
-      <c r="N107" s="153"/>
-      <c r="O107" s="153"/>
-      <c r="P107" s="153"/>
-      <c r="Q107" s="153"/>
-    </row>
-    <row r="108" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C107" s="120"/>
+      <c r="D107" s="120"/>
+      <c r="E107" s="129"/>
+      <c r="F107" s="120"/>
+      <c r="G107" s="120"/>
+      <c r="H107" s="120"/>
+      <c r="I107" s="120"/>
+      <c r="J107" s="120"/>
+      <c r="K107" s="120"/>
+      <c r="L107" s="120"/>
+      <c r="M107" s="120"/>
+      <c r="N107" s="123"/>
+      <c r="O107" s="123"/>
+      <c r="P107" s="123"/>
+      <c r="Q107" s="123"/>
+    </row>
+    <row r="108" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="95" t="str">
         <f>_xlfn.XLOOKUP(B108,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13309,23 +13309,23 @@
       <c r="B108" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C108" s="122"/>
-      <c r="D108" s="122"/>
-      <c r="E108" s="149"/>
-      <c r="F108" s="146"/>
-      <c r="G108" s="146"/>
-      <c r="H108" s="146"/>
-      <c r="I108" s="146"/>
-      <c r="J108" s="146"/>
-      <c r="K108" s="146"/>
-      <c r="L108" s="146"/>
-      <c r="M108" s="146"/>
-      <c r="N108" s="154"/>
-      <c r="O108" s="153"/>
-      <c r="P108" s="153"/>
-      <c r="Q108" s="153"/>
-    </row>
-    <row r="109" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C108" s="120"/>
+      <c r="D108" s="120"/>
+      <c r="E108" s="130"/>
+      <c r="F108" s="121"/>
+      <c r="G108" s="121"/>
+      <c r="H108" s="121"/>
+      <c r="I108" s="121"/>
+      <c r="J108" s="121"/>
+      <c r="K108" s="121"/>
+      <c r="L108" s="121"/>
+      <c r="M108" s="121"/>
+      <c r="N108" s="124"/>
+      <c r="O108" s="123"/>
+      <c r="P108" s="123"/>
+      <c r="Q108" s="123"/>
+    </row>
+    <row r="109" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A109" s="24" t="str">
         <f>_xlfn.XLOOKUP(B109,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13333,52 +13333,52 @@
       <c r="B109" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C109" s="145">
+      <c r="C109" s="119">
         <v>6</v>
       </c>
-      <c r="D109" s="145" t="s">
+      <c r="D109" s="119" t="s">
         <v>281</v>
       </c>
-      <c r="E109" s="153" t="s">
+      <c r="E109" s="123" t="s">
         <v>282</v>
       </c>
-      <c r="F109" s="122" t="s">
+      <c r="F109" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="G109" s="122"/>
-      <c r="H109" s="122" t="s">
+      <c r="G109" s="120"/>
+      <c r="H109" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="I109" s="122"/>
-      <c r="J109" s="122">
+      <c r="I109" s="120"/>
+      <c r="J109" s="120">
         <v>3</v>
       </c>
-      <c r="K109" s="122">
+      <c r="K109" s="120">
         <f>J109*12</f>
         <v>36</v>
       </c>
-      <c r="L109" s="122">
+      <c r="L109" s="120">
         <f>36*J109</f>
         <v>108</v>
       </c>
-      <c r="M109" s="122">
+      <c r="M109" s="120">
         <f>SUM(K109:L109)</f>
         <v>144</v>
       </c>
-      <c r="N109" s="153" t="s">
+      <c r="N109" s="123" t="s">
         <v>283</v>
       </c>
-      <c r="O109" s="152" t="s">
+      <c r="O109" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P109" s="152" t="s">
+      <c r="P109" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q109" s="152" t="s">
+      <c r="Q109" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="str">
         <f>_xlfn.XLOOKUP(B110,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13386,23 +13386,23 @@
       <c r="B110" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C110" s="122"/>
-      <c r="D110" s="122"/>
-      <c r="E110" s="153"/>
-      <c r="F110" s="122"/>
-      <c r="G110" s="122"/>
-      <c r="H110" s="122"/>
-      <c r="I110" s="122"/>
-      <c r="J110" s="122"/>
-      <c r="K110" s="122"/>
-      <c r="L110" s="122"/>
-      <c r="M110" s="122"/>
-      <c r="N110" s="153"/>
-      <c r="O110" s="153"/>
-      <c r="P110" s="153"/>
-      <c r="Q110" s="153"/>
-    </row>
-    <row r="111" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C110" s="120"/>
+      <c r="D110" s="120"/>
+      <c r="E110" s="123"/>
+      <c r="F110" s="120"/>
+      <c r="G110" s="120"/>
+      <c r="H110" s="120"/>
+      <c r="I110" s="120"/>
+      <c r="J110" s="120"/>
+      <c r="K110" s="120"/>
+      <c r="L110" s="120"/>
+      <c r="M110" s="120"/>
+      <c r="N110" s="123"/>
+      <c r="O110" s="123"/>
+      <c r="P110" s="123"/>
+      <c r="Q110" s="123"/>
+    </row>
+    <row r="111" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A111" s="24" t="str">
         <f>_xlfn.XLOOKUP(B111,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13410,23 +13410,23 @@
       <c r="B111" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C111" s="122"/>
-      <c r="D111" s="122"/>
-      <c r="E111" s="153"/>
-      <c r="F111" s="122"/>
-      <c r="G111" s="122"/>
-      <c r="H111" s="122"/>
-      <c r="I111" s="122"/>
-      <c r="J111" s="122"/>
-      <c r="K111" s="122"/>
-      <c r="L111" s="122"/>
-      <c r="M111" s="122"/>
-      <c r="N111" s="153"/>
-      <c r="O111" s="153"/>
-      <c r="P111" s="153"/>
-      <c r="Q111" s="153"/>
-    </row>
-    <row r="112" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C111" s="120"/>
+      <c r="D111" s="120"/>
+      <c r="E111" s="123"/>
+      <c r="F111" s="120"/>
+      <c r="G111" s="120"/>
+      <c r="H111" s="120"/>
+      <c r="I111" s="120"/>
+      <c r="J111" s="120"/>
+      <c r="K111" s="120"/>
+      <c r="L111" s="120"/>
+      <c r="M111" s="120"/>
+      <c r="N111" s="123"/>
+      <c r="O111" s="123"/>
+      <c r="P111" s="123"/>
+      <c r="Q111" s="123"/>
+    </row>
+    <row r="112" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A112" s="24" t="str">
         <f>_xlfn.XLOOKUP(B112,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13434,23 +13434,23 @@
       <c r="B112" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C112" s="122"/>
-      <c r="D112" s="122"/>
-      <c r="E112" s="153"/>
-      <c r="F112" s="122"/>
-      <c r="G112" s="122"/>
-      <c r="H112" s="122"/>
-      <c r="I112" s="122"/>
-      <c r="J112" s="122"/>
-      <c r="K112" s="122"/>
-      <c r="L112" s="122"/>
-      <c r="M112" s="122"/>
-      <c r="N112" s="153"/>
-      <c r="O112" s="153"/>
-      <c r="P112" s="153"/>
-      <c r="Q112" s="153"/>
-    </row>
-    <row r="113" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C112" s="120"/>
+      <c r="D112" s="120"/>
+      <c r="E112" s="123"/>
+      <c r="F112" s="120"/>
+      <c r="G112" s="120"/>
+      <c r="H112" s="120"/>
+      <c r="I112" s="120"/>
+      <c r="J112" s="120"/>
+      <c r="K112" s="120"/>
+      <c r="L112" s="120"/>
+      <c r="M112" s="120"/>
+      <c r="N112" s="123"/>
+      <c r="O112" s="123"/>
+      <c r="P112" s="123"/>
+      <c r="Q112" s="123"/>
+    </row>
+    <row r="113" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A113" s="24" t="str">
         <f>_xlfn.XLOOKUP(B113,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13458,23 +13458,23 @@
       <c r="B113" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C113" s="122"/>
-      <c r="D113" s="122"/>
-      <c r="E113" s="153"/>
-      <c r="F113" s="122"/>
-      <c r="G113" s="122"/>
-      <c r="H113" s="122"/>
-      <c r="I113" s="122"/>
-      <c r="J113" s="122"/>
-      <c r="K113" s="122"/>
-      <c r="L113" s="122"/>
-      <c r="M113" s="122"/>
-      <c r="N113" s="153"/>
-      <c r="O113" s="153"/>
-      <c r="P113" s="153"/>
-      <c r="Q113" s="153"/>
-    </row>
-    <row r="114" spans="1:17" s="55" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+      <c r="C113" s="120"/>
+      <c r="D113" s="120"/>
+      <c r="E113" s="123"/>
+      <c r="F113" s="120"/>
+      <c r="G113" s="120"/>
+      <c r="H113" s="120"/>
+      <c r="I113" s="120"/>
+      <c r="J113" s="120"/>
+      <c r="K113" s="120"/>
+      <c r="L113" s="120"/>
+      <c r="M113" s="120"/>
+      <c r="N113" s="123"/>
+      <c r="O113" s="123"/>
+      <c r="P113" s="123"/>
+      <c r="Q113" s="123"/>
+    </row>
+    <row r="114" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="95" t="str">
         <f>_xlfn.XLOOKUP(B114,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13482,23 +13482,23 @@
       <c r="B114" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C114" s="122"/>
-      <c r="D114" s="122"/>
-      <c r="E114" s="153"/>
-      <c r="F114" s="122"/>
-      <c r="G114" s="122"/>
-      <c r="H114" s="122"/>
-      <c r="I114" s="122"/>
-      <c r="J114" s="122"/>
-      <c r="K114" s="122"/>
-      <c r="L114" s="122"/>
-      <c r="M114" s="122"/>
-      <c r="N114" s="153"/>
-      <c r="O114" s="153"/>
-      <c r="P114" s="153"/>
-      <c r="Q114" s="153"/>
-    </row>
-    <row r="115" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C114" s="120"/>
+      <c r="D114" s="120"/>
+      <c r="E114" s="123"/>
+      <c r="F114" s="120"/>
+      <c r="G114" s="120"/>
+      <c r="H114" s="120"/>
+      <c r="I114" s="120"/>
+      <c r="J114" s="120"/>
+      <c r="K114" s="120"/>
+      <c r="L114" s="120"/>
+      <c r="M114" s="120"/>
+      <c r="N114" s="123"/>
+      <c r="O114" s="123"/>
+      <c r="P114" s="123"/>
+      <c r="Q114" s="123"/>
+    </row>
+    <row r="115" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A115" s="24" t="str">
         <f>_xlfn.XLOOKUP(B115,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13506,52 +13506,52 @@
       <c r="B115" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C115" s="145">
+      <c r="C115" s="119">
         <v>6</v>
       </c>
-      <c r="D115" s="145" t="s">
+      <c r="D115" s="119" t="s">
         <v>284</v>
       </c>
-      <c r="E115" s="156" t="s">
+      <c r="E115" s="127" t="s">
         <v>285</v>
       </c>
-      <c r="F115" s="145" t="s">
+      <c r="F115" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G115" s="145"/>
-      <c r="H115" s="145" t="s">
+      <c r="G115" s="119"/>
+      <c r="H115" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I115" s="145"/>
-      <c r="J115" s="145">
+      <c r="I115" s="119"/>
+      <c r="J115" s="119">
         <v>3</v>
       </c>
-      <c r="K115" s="145">
+      <c r="K115" s="119">
         <f>J115*12</f>
         <v>36</v>
       </c>
-      <c r="L115" s="145">
+      <c r="L115" s="119">
         <f>36*J115</f>
         <v>108</v>
       </c>
-      <c r="M115" s="145">
+      <c r="M115" s="119">
         <f>SUM(K115:L115)</f>
         <v>144</v>
       </c>
-      <c r="N115" s="152" t="s">
+      <c r="N115" s="122" t="s">
         <v>286</v>
       </c>
-      <c r="O115" s="152" t="s">
+      <c r="O115" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P115" s="152" t="s">
+      <c r="P115" s="122" t="s">
         <v>260</v>
       </c>
-      <c r="Q115" s="152" t="s">
+      <c r="Q115" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A116" s="24" t="str">
         <f>_xlfn.XLOOKUP(B116,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13559,23 +13559,23 @@
       <c r="B116" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C116" s="122"/>
-      <c r="D116" s="122"/>
-      <c r="E116" s="157"/>
-      <c r="F116" s="122"/>
-      <c r="G116" s="122"/>
-      <c r="H116" s="122"/>
-      <c r="I116" s="122"/>
-      <c r="J116" s="122"/>
-      <c r="K116" s="122"/>
-      <c r="L116" s="122"/>
-      <c r="M116" s="122"/>
-      <c r="N116" s="153"/>
-      <c r="O116" s="153"/>
-      <c r="P116" s="153"/>
-      <c r="Q116" s="153"/>
-    </row>
-    <row r="117" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C116" s="120"/>
+      <c r="D116" s="120"/>
+      <c r="E116" s="128"/>
+      <c r="F116" s="120"/>
+      <c r="G116" s="120"/>
+      <c r="H116" s="120"/>
+      <c r="I116" s="120"/>
+      <c r="J116" s="120"/>
+      <c r="K116" s="120"/>
+      <c r="L116" s="120"/>
+      <c r="M116" s="120"/>
+      <c r="N116" s="123"/>
+      <c r="O116" s="123"/>
+      <c r="P116" s="123"/>
+      <c r="Q116" s="123"/>
+    </row>
+    <row r="117" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A117" s="24" t="str">
         <f>_xlfn.XLOOKUP(B117,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13583,23 +13583,23 @@
       <c r="B117" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C117" s="122"/>
-      <c r="D117" s="122"/>
-      <c r="E117" s="157"/>
-      <c r="F117" s="122"/>
-      <c r="G117" s="122"/>
-      <c r="H117" s="122"/>
-      <c r="I117" s="122"/>
-      <c r="J117" s="122"/>
-      <c r="K117" s="122"/>
-      <c r="L117" s="122"/>
-      <c r="M117" s="122"/>
-      <c r="N117" s="153"/>
-      <c r="O117" s="153"/>
-      <c r="P117" s="153"/>
-      <c r="Q117" s="153"/>
-    </row>
-    <row r="118" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C117" s="120"/>
+      <c r="D117" s="120"/>
+      <c r="E117" s="128"/>
+      <c r="F117" s="120"/>
+      <c r="G117" s="120"/>
+      <c r="H117" s="120"/>
+      <c r="I117" s="120"/>
+      <c r="J117" s="120"/>
+      <c r="K117" s="120"/>
+      <c r="L117" s="120"/>
+      <c r="M117" s="120"/>
+      <c r="N117" s="123"/>
+      <c r="O117" s="123"/>
+      <c r="P117" s="123"/>
+      <c r="Q117" s="123"/>
+    </row>
+    <row r="118" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A118" s="24" t="str">
         <f>_xlfn.XLOOKUP(B118,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13607,23 +13607,23 @@
       <c r="B118" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C118" s="122"/>
-      <c r="D118" s="122"/>
-      <c r="E118" s="157"/>
-      <c r="F118" s="122"/>
-      <c r="G118" s="122"/>
-      <c r="H118" s="122"/>
-      <c r="I118" s="122"/>
-      <c r="J118" s="122"/>
-      <c r="K118" s="122"/>
-      <c r="L118" s="122"/>
-      <c r="M118" s="122"/>
-      <c r="N118" s="153"/>
-      <c r="O118" s="153"/>
-      <c r="P118" s="153"/>
-      <c r="Q118" s="153"/>
-    </row>
-    <row r="119" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C118" s="120"/>
+      <c r="D118" s="120"/>
+      <c r="E118" s="128"/>
+      <c r="F118" s="120"/>
+      <c r="G118" s="120"/>
+      <c r="H118" s="120"/>
+      <c r="I118" s="120"/>
+      <c r="J118" s="120"/>
+      <c r="K118" s="120"/>
+      <c r="L118" s="120"/>
+      <c r="M118" s="120"/>
+      <c r="N118" s="123"/>
+      <c r="O118" s="123"/>
+      <c r="P118" s="123"/>
+      <c r="Q118" s="123"/>
+    </row>
+    <row r="119" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A119" s="24" t="str">
         <f>_xlfn.XLOOKUP(B119,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13631,23 +13631,23 @@
       <c r="B119" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C119" s="122"/>
-      <c r="D119" s="122"/>
-      <c r="E119" s="157"/>
-      <c r="F119" s="122"/>
-      <c r="G119" s="122"/>
-      <c r="H119" s="122"/>
-      <c r="I119" s="122"/>
-      <c r="J119" s="122"/>
-      <c r="K119" s="122"/>
-      <c r="L119" s="122"/>
-      <c r="M119" s="122"/>
-      <c r="N119" s="153"/>
-      <c r="O119" s="153"/>
-      <c r="P119" s="153"/>
-      <c r="Q119" s="153"/>
-    </row>
-    <row r="120" spans="1:17" s="55" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+      <c r="C119" s="120"/>
+      <c r="D119" s="120"/>
+      <c r="E119" s="128"/>
+      <c r="F119" s="120"/>
+      <c r="G119" s="120"/>
+      <c r="H119" s="120"/>
+      <c r="I119" s="120"/>
+      <c r="J119" s="120"/>
+      <c r="K119" s="120"/>
+      <c r="L119" s="120"/>
+      <c r="M119" s="120"/>
+      <c r="N119" s="123"/>
+      <c r="O119" s="123"/>
+      <c r="P119" s="123"/>
+      <c r="Q119" s="123"/>
+    </row>
+    <row r="120" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="95" t="str">
         <f>_xlfn.XLOOKUP(B120,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13655,23 +13655,23 @@
       <c r="B120" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C120" s="122"/>
-      <c r="D120" s="122"/>
-      <c r="E120" s="157"/>
-      <c r="F120" s="122"/>
-      <c r="G120" s="122"/>
-      <c r="H120" s="122"/>
-      <c r="I120" s="122"/>
-      <c r="J120" s="122"/>
-      <c r="K120" s="122"/>
-      <c r="L120" s="122"/>
-      <c r="M120" s="122"/>
-      <c r="N120" s="154"/>
-      <c r="O120" s="153"/>
-      <c r="P120" s="153"/>
-      <c r="Q120" s="153"/>
-    </row>
-    <row r="121" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C120" s="120"/>
+      <c r="D120" s="120"/>
+      <c r="E120" s="128"/>
+      <c r="F120" s="120"/>
+      <c r="G120" s="120"/>
+      <c r="H120" s="120"/>
+      <c r="I120" s="120"/>
+      <c r="J120" s="120"/>
+      <c r="K120" s="120"/>
+      <c r="L120" s="120"/>
+      <c r="M120" s="120"/>
+      <c r="N120" s="124"/>
+      <c r="O120" s="123"/>
+      <c r="P120" s="123"/>
+      <c r="Q120" s="123"/>
+    </row>
+    <row r="121" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="str">
         <f>_xlfn.XLOOKUP(B121,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13679,52 +13679,52 @@
       <c r="B121" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C121" s="145">
+      <c r="C121" s="119">
         <v>6</v>
       </c>
-      <c r="D121" s="145" t="s">
+      <c r="D121" s="119" t="s">
         <v>287</v>
       </c>
-      <c r="E121" s="152" t="s">
+      <c r="E121" s="122" t="s">
         <v>288</v>
       </c>
-      <c r="F121" s="145" t="s">
+      <c r="F121" s="119" t="s">
         <v>289</v>
       </c>
-      <c r="G121" s="145"/>
-      <c r="H121" s="145" t="s">
+      <c r="G121" s="119"/>
+      <c r="H121" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I121" s="145"/>
-      <c r="J121" s="145">
+      <c r="I121" s="119"/>
+      <c r="J121" s="119">
         <v>3</v>
       </c>
-      <c r="K121" s="145">
+      <c r="K121" s="119">
         <f>J121*12</f>
         <v>36</v>
       </c>
-      <c r="L121" s="145">
+      <c r="L121" s="119">
         <f>36*J121</f>
         <v>108</v>
       </c>
-      <c r="M121" s="145">
+      <c r="M121" s="119">
         <f>SUM(K121:L121)</f>
         <v>144</v>
       </c>
-      <c r="N121" s="152" t="s">
+      <c r="N121" s="122" t="s">
         <v>290</v>
       </c>
-      <c r="O121" s="152" t="s">
+      <c r="O121" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P121" s="147" t="s">
+      <c r="P121" s="125" t="s">
         <v>291</v>
       </c>
-      <c r="Q121" s="152" t="s">
+      <c r="Q121" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A122" s="24" t="str">
         <f>_xlfn.XLOOKUP(B122,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13732,23 +13732,23 @@
       <c r="B122" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C122" s="122"/>
-      <c r="D122" s="122"/>
-      <c r="E122" s="153"/>
-      <c r="F122" s="122"/>
-      <c r="G122" s="122"/>
-      <c r="H122" s="122"/>
-      <c r="I122" s="122"/>
-      <c r="J122" s="122"/>
-      <c r="K122" s="122"/>
-      <c r="L122" s="122"/>
-      <c r="M122" s="122"/>
-      <c r="N122" s="153"/>
-      <c r="O122" s="153"/>
-      <c r="P122" s="161"/>
-      <c r="Q122" s="153"/>
-    </row>
-    <row r="123" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C122" s="120"/>
+      <c r="D122" s="120"/>
+      <c r="E122" s="123"/>
+      <c r="F122" s="120"/>
+      <c r="G122" s="120"/>
+      <c r="H122" s="120"/>
+      <c r="I122" s="120"/>
+      <c r="J122" s="120"/>
+      <c r="K122" s="120"/>
+      <c r="L122" s="120"/>
+      <c r="M122" s="120"/>
+      <c r="N122" s="123"/>
+      <c r="O122" s="123"/>
+      <c r="P122" s="126"/>
+      <c r="Q122" s="123"/>
+    </row>
+    <row r="123" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A123" s="24" t="str">
         <f>_xlfn.XLOOKUP(B123,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13756,23 +13756,23 @@
       <c r="B123" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C123" s="122"/>
-      <c r="D123" s="122"/>
-      <c r="E123" s="153"/>
-      <c r="F123" s="122"/>
-      <c r="G123" s="122"/>
-      <c r="H123" s="122"/>
-      <c r="I123" s="122"/>
-      <c r="J123" s="122"/>
-      <c r="K123" s="122"/>
-      <c r="L123" s="122"/>
-      <c r="M123" s="122"/>
-      <c r="N123" s="153"/>
-      <c r="O123" s="153"/>
-      <c r="P123" s="161"/>
-      <c r="Q123" s="153"/>
-    </row>
-    <row r="124" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C123" s="120"/>
+      <c r="D123" s="120"/>
+      <c r="E123" s="123"/>
+      <c r="F123" s="120"/>
+      <c r="G123" s="120"/>
+      <c r="H123" s="120"/>
+      <c r="I123" s="120"/>
+      <c r="J123" s="120"/>
+      <c r="K123" s="120"/>
+      <c r="L123" s="120"/>
+      <c r="M123" s="120"/>
+      <c r="N123" s="123"/>
+      <c r="O123" s="123"/>
+      <c r="P123" s="126"/>
+      <c r="Q123" s="123"/>
+    </row>
+    <row r="124" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="str">
         <f>_xlfn.XLOOKUP(B124,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13780,23 +13780,23 @@
       <c r="B124" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C124" s="122"/>
-      <c r="D124" s="122"/>
-      <c r="E124" s="153"/>
-      <c r="F124" s="122"/>
-      <c r="G124" s="122"/>
-      <c r="H124" s="122"/>
-      <c r="I124" s="122"/>
-      <c r="J124" s="122"/>
-      <c r="K124" s="122"/>
-      <c r="L124" s="122"/>
-      <c r="M124" s="122"/>
-      <c r="N124" s="153"/>
-      <c r="O124" s="153"/>
-      <c r="P124" s="161"/>
-      <c r="Q124" s="153"/>
-    </row>
-    <row r="125" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C124" s="120"/>
+      <c r="D124" s="120"/>
+      <c r="E124" s="123"/>
+      <c r="F124" s="120"/>
+      <c r="G124" s="120"/>
+      <c r="H124" s="120"/>
+      <c r="I124" s="120"/>
+      <c r="J124" s="120"/>
+      <c r="K124" s="120"/>
+      <c r="L124" s="120"/>
+      <c r="M124" s="120"/>
+      <c r="N124" s="123"/>
+      <c r="O124" s="123"/>
+      <c r="P124" s="126"/>
+      <c r="Q124" s="123"/>
+    </row>
+    <row r="125" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A125" s="24" t="str">
         <f>_xlfn.XLOOKUP(B125,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13804,23 +13804,23 @@
       <c r="B125" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C125" s="122"/>
-      <c r="D125" s="122"/>
-      <c r="E125" s="153"/>
-      <c r="F125" s="122"/>
-      <c r="G125" s="122"/>
-      <c r="H125" s="122"/>
-      <c r="I125" s="122"/>
-      <c r="J125" s="122"/>
-      <c r="K125" s="122"/>
-      <c r="L125" s="122"/>
-      <c r="M125" s="122"/>
-      <c r="N125" s="153"/>
-      <c r="O125" s="153"/>
-      <c r="P125" s="161"/>
-      <c r="Q125" s="153"/>
-    </row>
-    <row r="126" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C125" s="120"/>
+      <c r="D125" s="120"/>
+      <c r="E125" s="123"/>
+      <c r="F125" s="120"/>
+      <c r="G125" s="120"/>
+      <c r="H125" s="120"/>
+      <c r="I125" s="120"/>
+      <c r="J125" s="120"/>
+      <c r="K125" s="120"/>
+      <c r="L125" s="120"/>
+      <c r="M125" s="120"/>
+      <c r="N125" s="123"/>
+      <c r="O125" s="123"/>
+      <c r="P125" s="126"/>
+      <c r="Q125" s="123"/>
+    </row>
+    <row r="126" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="95" t="str">
         <f>_xlfn.XLOOKUP(B126,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13828,23 +13828,23 @@
       <c r="B126" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C126" s="122"/>
-      <c r="D126" s="122"/>
-      <c r="E126" s="153"/>
-      <c r="F126" s="122"/>
-      <c r="G126" s="122"/>
-      <c r="H126" s="122"/>
-      <c r="I126" s="122"/>
-      <c r="J126" s="122"/>
-      <c r="K126" s="122"/>
-      <c r="L126" s="122"/>
-      <c r="M126" s="122"/>
-      <c r="N126" s="153"/>
-      <c r="O126" s="153"/>
-      <c r="P126" s="161"/>
-      <c r="Q126" s="153"/>
-    </row>
-    <row r="127" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C126" s="120"/>
+      <c r="D126" s="120"/>
+      <c r="E126" s="123"/>
+      <c r="F126" s="120"/>
+      <c r="G126" s="120"/>
+      <c r="H126" s="120"/>
+      <c r="I126" s="120"/>
+      <c r="J126" s="120"/>
+      <c r="K126" s="120"/>
+      <c r="L126" s="120"/>
+      <c r="M126" s="120"/>
+      <c r="N126" s="123"/>
+      <c r="O126" s="123"/>
+      <c r="P126" s="126"/>
+      <c r="Q126" s="123"/>
+    </row>
+    <row r="127" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A127" s="24" t="str">
         <f>_xlfn.XLOOKUP(B127,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13852,52 +13852,52 @@
       <c r="B127" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C127" s="145">
+      <c r="C127" s="119">
         <v>6</v>
       </c>
-      <c r="D127" s="145" t="s">
+      <c r="D127" s="119" t="s">
         <v>292</v>
       </c>
-      <c r="E127" s="152" t="s">
+      <c r="E127" s="122" t="s">
         <v>293</v>
       </c>
-      <c r="F127" s="145" t="s">
+      <c r="F127" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="G127" s="145"/>
-      <c r="H127" s="145" t="s">
+      <c r="G127" s="119"/>
+      <c r="H127" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I127" s="145"/>
-      <c r="J127" s="145">
+      <c r="I127" s="119"/>
+      <c r="J127" s="119">
         <v>3</v>
       </c>
-      <c r="K127" s="145">
+      <c r="K127" s="119">
         <f>J127*12</f>
         <v>36</v>
       </c>
-      <c r="L127" s="145">
+      <c r="L127" s="119">
         <f>36*J127</f>
         <v>108</v>
       </c>
-      <c r="M127" s="145">
+      <c r="M127" s="119">
         <f>SUM(K127:L127)</f>
         <v>144</v>
       </c>
-      <c r="N127" s="152" t="s">
+      <c r="N127" s="122" t="s">
         <v>294</v>
       </c>
-      <c r="O127" s="152" t="s">
+      <c r="O127" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P127" s="152" t="s">
+      <c r="P127" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="Q127" s="152" t="s">
+      <c r="Q127" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A128" s="24" t="str">
         <f>_xlfn.XLOOKUP(B128,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13905,23 +13905,23 @@
       <c r="B128" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="C128" s="122"/>
-      <c r="D128" s="122"/>
-      <c r="E128" s="153"/>
-      <c r="F128" s="122"/>
-      <c r="G128" s="122"/>
-      <c r="H128" s="122"/>
-      <c r="I128" s="122"/>
-      <c r="J128" s="122"/>
-      <c r="K128" s="122"/>
-      <c r="L128" s="122"/>
-      <c r="M128" s="122"/>
-      <c r="N128" s="153"/>
-      <c r="O128" s="153"/>
-      <c r="P128" s="153"/>
-      <c r="Q128" s="153"/>
-    </row>
-    <row r="129" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C128" s="120"/>
+      <c r="D128" s="120"/>
+      <c r="E128" s="123"/>
+      <c r="F128" s="120"/>
+      <c r="G128" s="120"/>
+      <c r="H128" s="120"/>
+      <c r="I128" s="120"/>
+      <c r="J128" s="120"/>
+      <c r="K128" s="120"/>
+      <c r="L128" s="120"/>
+      <c r="M128" s="120"/>
+      <c r="N128" s="123"/>
+      <c r="O128" s="123"/>
+      <c r="P128" s="123"/>
+      <c r="Q128" s="123"/>
+    </row>
+    <row r="129" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A129" s="24" t="str">
         <f>_xlfn.XLOOKUP(B129,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13929,23 +13929,23 @@
       <c r="B129" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="C129" s="122"/>
-      <c r="D129" s="122"/>
-      <c r="E129" s="153"/>
-      <c r="F129" s="122"/>
-      <c r="G129" s="122"/>
-      <c r="H129" s="122"/>
-      <c r="I129" s="122"/>
-      <c r="J129" s="122"/>
-      <c r="K129" s="122"/>
-      <c r="L129" s="122"/>
-      <c r="M129" s="122"/>
-      <c r="N129" s="153"/>
-      <c r="O129" s="153"/>
-      <c r="P129" s="153"/>
-      <c r="Q129" s="153"/>
-    </row>
-    <row r="130" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C129" s="120"/>
+      <c r="D129" s="120"/>
+      <c r="E129" s="123"/>
+      <c r="F129" s="120"/>
+      <c r="G129" s="120"/>
+      <c r="H129" s="120"/>
+      <c r="I129" s="120"/>
+      <c r="J129" s="120"/>
+      <c r="K129" s="120"/>
+      <c r="L129" s="120"/>
+      <c r="M129" s="120"/>
+      <c r="N129" s="123"/>
+      <c r="O129" s="123"/>
+      <c r="P129" s="123"/>
+      <c r="Q129" s="123"/>
+    </row>
+    <row r="130" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A130" s="24" t="str">
         <f>_xlfn.XLOOKUP(B130,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13953,23 +13953,23 @@
       <c r="B130" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C130" s="122"/>
-      <c r="D130" s="122"/>
-      <c r="E130" s="153"/>
-      <c r="F130" s="122"/>
-      <c r="G130" s="122"/>
-      <c r="H130" s="122"/>
-      <c r="I130" s="122"/>
-      <c r="J130" s="122"/>
-      <c r="K130" s="122"/>
-      <c r="L130" s="122"/>
-      <c r="M130" s="122"/>
-      <c r="N130" s="153"/>
-      <c r="O130" s="153"/>
-      <c r="P130" s="153"/>
-      <c r="Q130" s="153"/>
-    </row>
-    <row r="131" spans="1:17" s="55" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C130" s="120"/>
+      <c r="D130" s="120"/>
+      <c r="E130" s="123"/>
+      <c r="F130" s="120"/>
+      <c r="G130" s="120"/>
+      <c r="H130" s="120"/>
+      <c r="I130" s="120"/>
+      <c r="J130" s="120"/>
+      <c r="K130" s="120"/>
+      <c r="L130" s="120"/>
+      <c r="M130" s="120"/>
+      <c r="N130" s="123"/>
+      <c r="O130" s="123"/>
+      <c r="P130" s="123"/>
+      <c r="Q130" s="123"/>
+    </row>
+    <row r="131" spans="1:17" s="55" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="95" t="str">
         <f>_xlfn.XLOOKUP(B131,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13977,23 +13977,23 @@
       <c r="B131" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C131" s="122"/>
-      <c r="D131" s="122"/>
-      <c r="E131" s="153"/>
-      <c r="F131" s="122"/>
-      <c r="G131" s="122"/>
-      <c r="H131" s="122"/>
-      <c r="I131" s="122"/>
-      <c r="J131" s="122"/>
-      <c r="K131" s="122"/>
-      <c r="L131" s="122"/>
-      <c r="M131" s="122"/>
-      <c r="N131" s="153"/>
-      <c r="O131" s="153"/>
-      <c r="P131" s="153"/>
-      <c r="Q131" s="153"/>
-    </row>
-    <row r="132" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C131" s="120"/>
+      <c r="D131" s="120"/>
+      <c r="E131" s="123"/>
+      <c r="F131" s="120"/>
+      <c r="G131" s="120"/>
+      <c r="H131" s="120"/>
+      <c r="I131" s="120"/>
+      <c r="J131" s="120"/>
+      <c r="K131" s="120"/>
+      <c r="L131" s="120"/>
+      <c r="M131" s="120"/>
+      <c r="N131" s="123"/>
+      <c r="O131" s="123"/>
+      <c r="P131" s="123"/>
+      <c r="Q131" s="123"/>
+    </row>
+    <row r="132" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A132" s="24" t="str">
         <f>_xlfn.XLOOKUP(B132,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14001,52 +14001,52 @@
       <c r="B132" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C132" s="145">
+      <c r="C132" s="119">
         <v>6</v>
       </c>
-      <c r="D132" s="145" t="s">
+      <c r="D132" s="119" t="s">
         <v>295</v>
       </c>
-      <c r="E132" s="152" t="s">
+      <c r="E132" s="122" t="s">
         <v>296</v>
       </c>
-      <c r="F132" s="145" t="s">
+      <c r="F132" s="119" t="s">
         <v>201</v>
       </c>
-      <c r="G132" s="145"/>
-      <c r="H132" s="145" t="s">
+      <c r="G132" s="119"/>
+      <c r="H132" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="I132" s="145"/>
-      <c r="J132" s="145">
+      <c r="I132" s="119"/>
+      <c r="J132" s="119">
         <v>3</v>
       </c>
-      <c r="K132" s="145">
+      <c r="K132" s="119">
         <f>J132*12</f>
         <v>36</v>
       </c>
-      <c r="L132" s="145">
+      <c r="L132" s="119">
         <f>36*J132</f>
         <v>108</v>
       </c>
-      <c r="M132" s="145">
+      <c r="M132" s="119">
         <f>SUM(K132:L132)</f>
         <v>144</v>
       </c>
-      <c r="N132" s="152" t="s">
+      <c r="N132" s="122" t="s">
         <v>297</v>
       </c>
-      <c r="O132" s="152" t="s">
+      <c r="O132" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="P132" s="152" t="s">
+      <c r="P132" s="122" t="s">
         <v>298</v>
       </c>
-      <c r="Q132" s="152" t="s">
+      <c r="Q132" s="122" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A133" s="24" t="str">
         <f>_xlfn.XLOOKUP(B133,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -14054,23 +14054,23 @@
       <c r="B133" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C133" s="122"/>
-      <c r="D133" s="122"/>
-      <c r="E133" s="153"/>
-      <c r="F133" s="122"/>
-      <c r="G133" s="122"/>
-      <c r="H133" s="122"/>
-      <c r="I133" s="122"/>
-      <c r="J133" s="122"/>
-      <c r="K133" s="122"/>
-      <c r="L133" s="122"/>
-      <c r="M133" s="122"/>
-      <c r="N133" s="153"/>
-      <c r="O133" s="153"/>
-      <c r="P133" s="153"/>
-      <c r="Q133" s="153"/>
-    </row>
-    <row r="134" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C133" s="120"/>
+      <c r="D133" s="120"/>
+      <c r="E133" s="123"/>
+      <c r="F133" s="120"/>
+      <c r="G133" s="120"/>
+      <c r="H133" s="120"/>
+      <c r="I133" s="120"/>
+      <c r="J133" s="120"/>
+      <c r="K133" s="120"/>
+      <c r="L133" s="120"/>
+      <c r="M133" s="120"/>
+      <c r="N133" s="123"/>
+      <c r="O133" s="123"/>
+      <c r="P133" s="123"/>
+      <c r="Q133" s="123"/>
+    </row>
+    <row r="134" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A134" s="24" t="str">
         <f>_xlfn.XLOOKUP(B134,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14078,23 +14078,23 @@
       <c r="B134" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C134" s="122"/>
-      <c r="D134" s="122"/>
-      <c r="E134" s="153"/>
-      <c r="F134" s="122"/>
-      <c r="G134" s="122"/>
-      <c r="H134" s="122"/>
-      <c r="I134" s="122"/>
-      <c r="J134" s="122"/>
-      <c r="K134" s="122"/>
-      <c r="L134" s="122"/>
-      <c r="M134" s="122"/>
-      <c r="N134" s="153"/>
-      <c r="O134" s="153"/>
-      <c r="P134" s="153"/>
-      <c r="Q134" s="153"/>
-    </row>
-    <row r="135" spans="1:17" s="55" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C134" s="120"/>
+      <c r="D134" s="120"/>
+      <c r="E134" s="123"/>
+      <c r="F134" s="120"/>
+      <c r="G134" s="120"/>
+      <c r="H134" s="120"/>
+      <c r="I134" s="120"/>
+      <c r="J134" s="120"/>
+      <c r="K134" s="120"/>
+      <c r="L134" s="120"/>
+      <c r="M134" s="120"/>
+      <c r="N134" s="123"/>
+      <c r="O134" s="123"/>
+      <c r="P134" s="123"/>
+      <c r="Q134" s="123"/>
+    </row>
+    <row r="135" spans="1:17" s="55" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A135" s="24" t="str">
         <f>_xlfn.XLOOKUP(B135,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14102,23 +14102,23 @@
       <c r="B135" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C135" s="122"/>
-      <c r="D135" s="122"/>
-      <c r="E135" s="153"/>
-      <c r="F135" s="122"/>
-      <c r="G135" s="122"/>
-      <c r="H135" s="122"/>
-      <c r="I135" s="122"/>
-      <c r="J135" s="122"/>
-      <c r="K135" s="122"/>
-      <c r="L135" s="122"/>
-      <c r="M135" s="122"/>
-      <c r="N135" s="153"/>
-      <c r="O135" s="153"/>
-      <c r="P135" s="153"/>
-      <c r="Q135" s="153"/>
-    </row>
-    <row r="136" spans="1:17" s="55" customFormat="1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C135" s="120"/>
+      <c r="D135" s="120"/>
+      <c r="E135" s="123"/>
+      <c r="F135" s="120"/>
+      <c r="G135" s="120"/>
+      <c r="H135" s="120"/>
+      <c r="I135" s="120"/>
+      <c r="J135" s="120"/>
+      <c r="K135" s="120"/>
+      <c r="L135" s="120"/>
+      <c r="M135" s="120"/>
+      <c r="N135" s="123"/>
+      <c r="O135" s="123"/>
+      <c r="P135" s="123"/>
+      <c r="Q135" s="123"/>
+    </row>
+    <row r="136" spans="1:17" s="55" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="95" t="str">
         <f>_xlfn.XLOOKUP(B136,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -14126,23 +14126,23 @@
       <c r="B136" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="C136" s="146"/>
-      <c r="D136" s="146"/>
-      <c r="E136" s="154"/>
-      <c r="F136" s="146"/>
-      <c r="G136" s="146"/>
-      <c r="H136" s="146"/>
-      <c r="I136" s="146"/>
-      <c r="J136" s="146"/>
-      <c r="K136" s="146"/>
-      <c r="L136" s="146"/>
-      <c r="M136" s="146"/>
-      <c r="N136" s="154"/>
-      <c r="O136" s="154"/>
-      <c r="P136" s="154"/>
-      <c r="Q136" s="154"/>
-    </row>
-    <row r="137" spans="1:17" s="55" customFormat="1" ht="32" x14ac:dyDescent="0.35">
+      <c r="C136" s="121"/>
+      <c r="D136" s="121"/>
+      <c r="E136" s="124"/>
+      <c r="F136" s="121"/>
+      <c r="G136" s="121"/>
+      <c r="H136" s="121"/>
+      <c r="I136" s="121"/>
+      <c r="J136" s="121"/>
+      <c r="K136" s="121"/>
+      <c r="L136" s="121"/>
+      <c r="M136" s="121"/>
+      <c r="N136" s="124"/>
+      <c r="O136" s="124"/>
+      <c r="P136" s="124"/>
+      <c r="Q136" s="124"/>
+    </row>
+    <row r="137" spans="1:17" s="55" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A137" s="24"/>
       <c r="B137" s="16"/>
       <c r="C137" s="86" t="s">
@@ -14171,7 +14171,7 @@
       <c r="P137" s="16"/>
       <c r="Q137" s="16"/>
     </row>
-    <row r="138" spans="1:17" s="55" customFormat="1" ht="32" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" s="55" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A138" s="24"/>
       <c r="B138" s="16"/>
       <c r="D138" s="19"/>
@@ -14194,7 +14194,7 @@
       <c r="P138" s="16"/>
       <c r="Q138" s="16"/>
     </row>
-    <row r="139" spans="1:17" s="55" customFormat="1" ht="32" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" s="55" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A139" s="24"/>
       <c r="B139" s="16"/>
       <c r="D139" s="35"/>
@@ -14217,7 +14217,7 @@
       <c r="P139" s="75"/>
       <c r="Q139" s="75"/>
     </row>
-    <row r="140" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A140" s="24"/>
       <c r="B140" s="16"/>
       <c r="D140" s="35"/>
@@ -14235,7 +14235,7 @@
       <c r="P140" s="75"/>
       <c r="Q140" s="75"/>
     </row>
-    <row r="141" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A141" s="24"/>
       <c r="B141" s="16"/>
       <c r="D141" s="35"/>
@@ -14253,7 +14253,7 @@
       <c r="P141" s="75"/>
       <c r="Q141" s="75"/>
     </row>
-    <row r="142" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A142" s="24"/>
       <c r="B142" s="16"/>
       <c r="D142" s="19"/>
@@ -14271,7 +14271,7 @@
       <c r="P142" s="16"/>
       <c r="Q142" s="16"/>
     </row>
-    <row r="143" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A143" s="24"/>
       <c r="B143" s="16"/>
       <c r="D143" s="19"/>
@@ -14289,7 +14289,7 @@
       <c r="P143" s="16"/>
       <c r="Q143" s="16"/>
     </row>
-    <row r="144" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A144" s="24"/>
       <c r="B144" s="16"/>
       <c r="D144" s="19"/>
@@ -14307,7 +14307,7 @@
       <c r="P144" s="16"/>
       <c r="Q144" s="16"/>
     </row>
-    <row r="145" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A145" s="24"/>
       <c r="B145" s="16"/>
       <c r="D145" s="19"/>
@@ -14325,7 +14325,7 @@
       <c r="P145" s="16"/>
       <c r="Q145" s="16"/>
     </row>
-    <row r="146" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A146" s="24"/>
       <c r="B146" s="16"/>
       <c r="D146" s="19"/>
@@ -14343,7 +14343,7 @@
       <c r="P146" s="16"/>
       <c r="Q146" s="16"/>
     </row>
-    <row r="147" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A147" s="24"/>
       <c r="B147" s="16"/>
       <c r="D147" s="19"/>
@@ -14361,7 +14361,7 @@
       <c r="P147" s="16"/>
       <c r="Q147" s="16"/>
     </row>
-    <row r="148" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A148" s="24"/>
       <c r="B148" s="16"/>
       <c r="D148" s="19"/>
@@ -14379,7 +14379,7 @@
       <c r="P148" s="16"/>
       <c r="Q148" s="16"/>
     </row>
-    <row r="149" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A149" s="24"/>
       <c r="B149" s="16"/>
       <c r="D149" s="19"/>
@@ -14397,7 +14397,7 @@
       <c r="P149" s="16"/>
       <c r="Q149" s="16"/>
     </row>
-    <row r="150" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A150" s="24"/>
       <c r="B150" s="16"/>
       <c r="D150" s="19"/>
@@ -14415,7 +14415,7 @@
       <c r="P150" s="16"/>
       <c r="Q150" s="16"/>
     </row>
-    <row r="151" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A151" s="24"/>
       <c r="B151" s="16"/>
       <c r="D151" s="19"/>
@@ -14433,7 +14433,7 @@
       <c r="P151" s="16"/>
       <c r="Q151" s="16"/>
     </row>
-    <row r="152" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A152" s="24"/>
       <c r="B152" s="22"/>
       <c r="D152" s="19"/>
@@ -14451,7 +14451,7 @@
       <c r="P152" s="22"/>
       <c r="Q152" s="22"/>
     </row>
-    <row r="153" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A153" s="24"/>
       <c r="B153" s="22"/>
       <c r="D153" s="19"/>
@@ -14469,7 +14469,7 @@
       <c r="P153" s="22"/>
       <c r="Q153" s="22"/>
     </row>
-    <row r="154" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A154" s="24"/>
       <c r="B154" s="22"/>
       <c r="D154" s="19"/>
@@ -14487,7 +14487,7 @@
       <c r="P154" s="22"/>
       <c r="Q154" s="22"/>
     </row>
-    <row r="155" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A155" s="24"/>
       <c r="B155" s="22"/>
       <c r="D155" s="19"/>
@@ -14505,7 +14505,7 @@
       <c r="P155" s="22"/>
       <c r="Q155" s="22"/>
     </row>
-    <row r="156" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A156" s="24"/>
       <c r="B156" s="16"/>
       <c r="D156" s="35"/>
@@ -14523,7 +14523,7 @@
       <c r="P156" s="75"/>
       <c r="Q156" s="75"/>
     </row>
-    <row r="157" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A157" s="24"/>
       <c r="B157" s="16"/>
       <c r="D157" s="35"/>
@@ -14541,7 +14541,7 @@
       <c r="P157" s="75"/>
       <c r="Q157" s="75"/>
     </row>
-    <row r="158" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A158" s="24"/>
       <c r="B158" s="16"/>
       <c r="D158" s="35"/>
@@ -14559,7 +14559,7 @@
       <c r="P158" s="75"/>
       <c r="Q158" s="75"/>
     </row>
-    <row r="159" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A159" s="24"/>
       <c r="B159" s="16"/>
       <c r="D159" s="35"/>
@@ -14577,7 +14577,7 @@
       <c r="P159" s="75"/>
       <c r="Q159" s="75"/>
     </row>
-    <row r="160" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A160" s="24"/>
       <c r="B160" s="16"/>
       <c r="D160" s="19"/>
@@ -14590,7 +14590,7 @@
       <c r="P160" s="16"/>
       <c r="Q160" s="16"/>
     </row>
-    <row r="161" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A161" s="24"/>
       <c r="B161" s="16"/>
       <c r="D161" s="19"/>
@@ -14603,7 +14603,7 @@
       <c r="P161" s="16"/>
       <c r="Q161" s="16"/>
     </row>
-    <row r="162" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A162" s="24"/>
       <c r="B162" s="16"/>
       <c r="D162" s="19"/>
@@ -14616,7 +14616,7 @@
       <c r="P162" s="16"/>
       <c r="Q162" s="16"/>
     </row>
-    <row r="163" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A163" s="24"/>
       <c r="B163" s="16"/>
       <c r="D163" s="19"/>
@@ -14629,7 +14629,7 @@
       <c r="P163" s="16"/>
       <c r="Q163" s="16"/>
     </row>
-    <row r="164" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A164" s="24"/>
       <c r="B164" s="16"/>
       <c r="D164" s="19"/>
@@ -14647,7 +14647,7 @@
       <c r="P164" s="76"/>
       <c r="Q164" s="76"/>
     </row>
-    <row r="165" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A165" s="24"/>
       <c r="B165" s="16"/>
       <c r="D165" s="35"/>
@@ -14665,7 +14665,7 @@
       <c r="P165" s="75"/>
       <c r="Q165" s="75"/>
     </row>
-    <row r="166" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A166" s="24"/>
       <c r="B166" s="16"/>
       <c r="D166" s="35"/>
@@ -14683,7 +14683,7 @@
       <c r="P166" s="75"/>
       <c r="Q166" s="75"/>
     </row>
-    <row r="167" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A167" s="24"/>
       <c r="B167" s="16"/>
       <c r="D167" s="35"/>
@@ -14701,7 +14701,7 @@
       <c r="P167" s="75"/>
       <c r="Q167" s="75"/>
     </row>
-    <row r="168" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A168" s="24"/>
       <c r="B168" s="16"/>
       <c r="D168" s="35"/>
@@ -14719,7 +14719,7 @@
       <c r="P168" s="75"/>
       <c r="Q168" s="75"/>
     </row>
-    <row r="169" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A169" s="24"/>
       <c r="B169" s="16"/>
       <c r="D169" s="19"/>
@@ -14737,7 +14737,7 @@
       <c r="P169" s="75"/>
       <c r="Q169" s="75"/>
     </row>
-    <row r="170" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A170" s="24"/>
       <c r="B170" s="16"/>
       <c r="D170" s="19"/>
@@ -14755,7 +14755,7 @@
       <c r="P170" s="75"/>
       <c r="Q170" s="75"/>
     </row>
-    <row r="171" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A171" s="24"/>
       <c r="B171" s="16"/>
       <c r="D171" s="19"/>
@@ -14773,7 +14773,7 @@
       <c r="P171" s="75"/>
       <c r="Q171" s="75"/>
     </row>
-    <row r="172" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A172" s="24"/>
       <c r="B172" s="16"/>
       <c r="D172" s="19"/>
@@ -14791,7 +14791,7 @@
       <c r="P172" s="75"/>
       <c r="Q172" s="75"/>
     </row>
-    <row r="173" spans="1:17" s="55" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" s="55" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A173" s="24"/>
       <c r="B173" s="16"/>
       <c r="D173" s="19"/>
@@ -14804,7 +14804,7 @@
       <c r="P173" s="16"/>
       <c r="Q173" s="16"/>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E174" s="62"/>
       <c r="F174" s="57"/>
       <c r="L174" s="63"/>
@@ -14814,7 +14814,7 @@
       <c r="P174" s="62"/>
       <c r="Q174" s="62"/>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E175" s="62"/>
       <c r="F175" s="57"/>
       <c r="L175" s="63"/>
@@ -14824,7 +14824,7 @@
       <c r="P175" s="62"/>
       <c r="Q175" s="62"/>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E176" s="62"/>
       <c r="F176" s="57"/>
       <c r="L176" s="63"/>
@@ -14834,7 +14834,7 @@
       <c r="P176" s="62"/>
       <c r="Q176" s="62"/>
     </row>
-    <row r="177" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E177" s="66"/>
       <c r="F177" s="57"/>
       <c r="G177" s="59"/>
@@ -14849,7 +14849,7 @@
       <c r="P177" s="66"/>
       <c r="Q177" s="66"/>
     </row>
-    <row r="178" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E178" s="67"/>
       <c r="F178" s="57"/>
       <c r="G178" s="68"/>
@@ -14864,7 +14864,7 @@
       <c r="P178" s="67"/>
       <c r="Q178" s="67"/>
     </row>
-    <row r="179" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E179" s="58"/>
       <c r="F179" s="57"/>
       <c r="G179" s="59"/>
@@ -14879,7 +14879,7 @@
       <c r="P179" s="71"/>
       <c r="Q179" s="71"/>
     </row>
-    <row r="180" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E180" s="58"/>
       <c r="F180" s="57"/>
       <c r="G180" s="59"/>
@@ -14894,7 +14894,7 @@
       <c r="P180" s="71"/>
       <c r="Q180" s="71"/>
     </row>
-    <row r="181" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E181" s="58"/>
       <c r="F181" s="57"/>
       <c r="G181" s="59"/>
@@ -14909,7 +14909,7 @@
       <c r="P181" s="71"/>
       <c r="Q181" s="71"/>
     </row>
-    <row r="182" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="182" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E182" s="58"/>
       <c r="F182" s="57"/>
       <c r="G182" s="59"/>
@@ -14924,7 +14924,7 @@
       <c r="P182" s="71"/>
       <c r="Q182" s="71"/>
     </row>
-    <row r="183" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E183" s="62"/>
       <c r="F183" s="57"/>
       <c r="G183" s="63"/>
@@ -14939,7 +14939,7 @@
       <c r="P183" s="62"/>
       <c r="Q183" s="62"/>
     </row>
-    <row r="184" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E184" s="62"/>
       <c r="F184" s="57"/>
       <c r="G184" s="63"/>
@@ -14954,7 +14954,7 @@
       <c r="P184" s="62"/>
       <c r="Q184" s="62"/>
     </row>
-    <row r="185" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E185" s="62"/>
       <c r="F185" s="57"/>
       <c r="G185" s="63"/>
@@ -14969,7 +14969,7 @@
       <c r="P185" s="62"/>
       <c r="Q185" s="62"/>
     </row>
-    <row r="186" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E186" s="62"/>
       <c r="F186" s="57"/>
       <c r="G186" s="63"/>
@@ -14984,7 +14984,7 @@
       <c r="P186" s="62"/>
       <c r="Q186" s="62"/>
     </row>
-    <row r="187" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="187" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E187" s="62"/>
       <c r="F187" s="57"/>
       <c r="I187" s="57"/>
@@ -14993,7 +14993,7 @@
       <c r="P187" s="62"/>
       <c r="Q187" s="62"/>
     </row>
-    <row r="188" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="188" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E188" s="62"/>
       <c r="F188" s="57"/>
       <c r="I188" s="57"/>
@@ -15002,7 +15002,7 @@
       <c r="P188" s="62"/>
       <c r="Q188" s="62"/>
     </row>
-    <row r="189" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="189" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E189" s="62"/>
       <c r="F189" s="57"/>
       <c r="I189" s="57"/>
@@ -15011,7 +15011,7 @@
       <c r="P189" s="62"/>
       <c r="Q189" s="62"/>
     </row>
-    <row r="190" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="190" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E190" s="62"/>
       <c r="F190" s="57"/>
       <c r="I190" s="57"/>
@@ -15020,7 +15020,7 @@
       <c r="P190" s="62"/>
       <c r="Q190" s="62"/>
     </row>
-    <row r="191" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="191" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E191" s="69"/>
       <c r="F191" s="57"/>
       <c r="G191" s="59"/>
@@ -15035,7 +15035,7 @@
       <c r="P191" s="61"/>
       <c r="Q191" s="61"/>
     </row>
-    <row r="192" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="192" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E192" s="69"/>
       <c r="F192" s="57"/>
       <c r="G192" s="59"/>
@@ -15050,7 +15050,7 @@
       <c r="P192" s="61"/>
       <c r="Q192" s="61"/>
     </row>
-    <row r="193" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="193" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E193" s="69"/>
       <c r="F193" s="57"/>
       <c r="G193" s="59"/>
@@ -15065,7 +15065,7 @@
       <c r="P193" s="61"/>
       <c r="Q193" s="61"/>
     </row>
-    <row r="194" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="194" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E194" s="58"/>
       <c r="F194" s="57"/>
       <c r="G194" s="59"/>
@@ -15080,7 +15080,7 @@
       <c r="P194" s="71"/>
       <c r="Q194" s="71"/>
     </row>
-    <row r="195" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="195" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E195" s="58"/>
       <c r="F195" s="57"/>
       <c r="G195" s="59"/>
@@ -15095,7 +15095,7 @@
       <c r="P195" s="71"/>
       <c r="Q195" s="71"/>
     </row>
-    <row r="196" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="196" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E196" s="58"/>
       <c r="F196" s="57"/>
       <c r="G196" s="59"/>
@@ -15110,7 +15110,7 @@
       <c r="P196" s="71"/>
       <c r="Q196" s="71"/>
     </row>
-    <row r="197" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="197" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E197" s="58"/>
       <c r="F197" s="57"/>
       <c r="G197" s="59"/>
@@ -15125,7 +15125,7 @@
       <c r="P197" s="71"/>
       <c r="Q197" s="71"/>
     </row>
-    <row r="198" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="198" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E198" s="58"/>
       <c r="F198" s="57"/>
       <c r="G198" s="59"/>
@@ -15140,7 +15140,7 @@
       <c r="P198" s="71"/>
       <c r="Q198" s="71"/>
     </row>
-    <row r="199" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="199" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E199" s="58"/>
       <c r="F199" s="57"/>
       <c r="G199" s="59"/>
@@ -15155,7 +15155,7 @@
       <c r="P199" s="71"/>
       <c r="Q199" s="71"/>
     </row>
-    <row r="200" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="200" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E200" s="58"/>
       <c r="F200" s="57"/>
       <c r="G200" s="59"/>
@@ -15170,7 +15170,7 @@
       <c r="P200" s="71"/>
       <c r="Q200" s="71"/>
     </row>
-    <row r="201" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="201" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E201" s="58"/>
       <c r="F201" s="57"/>
       <c r="G201" s="59"/>
@@ -15185,7 +15185,7 @@
       <c r="P201" s="71"/>
       <c r="Q201" s="71"/>
     </row>
-    <row r="202" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="202" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E202" s="58"/>
       <c r="F202" s="57"/>
       <c r="G202" s="59"/>
@@ -15200,7 +15200,7 @@
       <c r="P202" s="71"/>
       <c r="Q202" s="71"/>
     </row>
-    <row r="203" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="203" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E203" s="58"/>
       <c r="F203" s="57"/>
       <c r="G203" s="59"/>
@@ -15215,7 +15215,7 @@
       <c r="P203" s="71"/>
       <c r="Q203" s="71"/>
     </row>
-    <row r="204" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="204" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E204" s="58"/>
       <c r="F204" s="57"/>
       <c r="G204" s="59"/>
@@ -15230,7 +15230,7 @@
       <c r="P204" s="71"/>
       <c r="Q204" s="71"/>
     </row>
-    <row r="205" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="205" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E205" s="58"/>
       <c r="F205" s="57"/>
       <c r="G205" s="59"/>
@@ -15245,7 +15245,7 @@
       <c r="P205" s="71"/>
       <c r="Q205" s="71"/>
     </row>
-    <row r="206" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="206" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E206" s="58"/>
       <c r="F206" s="57"/>
       <c r="G206" s="59"/>
@@ -15260,7 +15260,7 @@
       <c r="P206" s="71"/>
       <c r="Q206" s="71"/>
     </row>
-    <row r="207" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="207" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E207" s="58"/>
       <c r="F207" s="57"/>
       <c r="G207" s="59"/>
@@ -15275,7 +15275,7 @@
       <c r="P207" s="71"/>
       <c r="Q207" s="71"/>
     </row>
-    <row r="208" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="208" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E208" s="58"/>
       <c r="F208" s="57"/>
       <c r="G208" s="59"/>
@@ -15290,7 +15290,7 @@
       <c r="P208" s="71"/>
       <c r="Q208" s="71"/>
     </row>
-    <row r="209" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="209" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E209" s="58"/>
       <c r="F209" s="57"/>
       <c r="G209" s="59"/>
@@ -15305,7 +15305,7 @@
       <c r="P209" s="71"/>
       <c r="Q209" s="71"/>
     </row>
-    <row r="210" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="210" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D210" s="64"/>
       <c r="E210" s="58"/>
       <c r="F210" s="64"/>
@@ -15321,7 +15321,7 @@
       <c r="P210" s="71"/>
       <c r="Q210" s="71"/>
     </row>
-    <row r="211" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="211" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D211" s="64"/>
       <c r="E211" s="58"/>
       <c r="F211" s="64"/>
@@ -15337,7 +15337,7 @@
       <c r="P211" s="71"/>
       <c r="Q211" s="71"/>
     </row>
-    <row r="212" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="212" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D212" s="64"/>
       <c r="E212" s="58"/>
       <c r="F212" s="64"/>
@@ -15353,7 +15353,7 @@
       <c r="P212" s="71"/>
       <c r="Q212" s="71"/>
     </row>
-    <row r="213" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="213" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D213" s="64"/>
       <c r="E213" s="58"/>
       <c r="F213" s="64"/>
@@ -15370,206 +15370,179 @@
       <c r="Q213" s="71"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q139" xr:uid="{06CB1331-AF3E-489A-B433-09E21B4DF482}">
-    <filterColumn colId="6" showButton="0"/>
-    <filterColumn colId="7" showButton="0"/>
-  </autoFilter>
   <mergeCells count="391">
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="I132:I136"/>
-    <mergeCell ref="J132:J136"/>
-    <mergeCell ref="K132:K136"/>
-    <mergeCell ref="L132:L136"/>
-    <mergeCell ref="C132:C136"/>
-    <mergeCell ref="D132:D136"/>
-    <mergeCell ref="E132:E136"/>
-    <mergeCell ref="F132:F136"/>
-    <mergeCell ref="G132:G136"/>
-    <mergeCell ref="M127:M131"/>
-    <mergeCell ref="N127:N131"/>
-    <mergeCell ref="O127:O131"/>
-    <mergeCell ref="P127:P131"/>
-    <mergeCell ref="M132:M136"/>
-    <mergeCell ref="N132:N136"/>
-    <mergeCell ref="O132:O136"/>
-    <mergeCell ref="P132:P136"/>
-    <mergeCell ref="Q127:Q131"/>
-    <mergeCell ref="Q132:Q136"/>
-    <mergeCell ref="H127:H131"/>
-    <mergeCell ref="I127:I131"/>
-    <mergeCell ref="J127:J131"/>
-    <mergeCell ref="K127:K131"/>
-    <mergeCell ref="L127:L131"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="D127:D131"/>
-    <mergeCell ref="E127:E131"/>
-    <mergeCell ref="F127:F131"/>
-    <mergeCell ref="G127:G131"/>
-    <mergeCell ref="M121:M126"/>
-    <mergeCell ref="N121:N126"/>
-    <mergeCell ref="O121:O126"/>
-    <mergeCell ref="P121:P126"/>
-    <mergeCell ref="Q121:Q126"/>
-    <mergeCell ref="H121:H126"/>
-    <mergeCell ref="I121:I126"/>
-    <mergeCell ref="J121:J126"/>
-    <mergeCell ref="K121:K126"/>
-    <mergeCell ref="L121:L126"/>
-    <mergeCell ref="C115:C120"/>
-    <mergeCell ref="D115:D120"/>
-    <mergeCell ref="E115:E120"/>
-    <mergeCell ref="F115:F120"/>
-    <mergeCell ref="G115:G120"/>
-    <mergeCell ref="C121:C126"/>
-    <mergeCell ref="D121:D126"/>
-    <mergeCell ref="E121:E126"/>
-    <mergeCell ref="F121:F126"/>
-    <mergeCell ref="G121:G126"/>
-    <mergeCell ref="Q109:Q114"/>
-    <mergeCell ref="H109:H114"/>
-    <mergeCell ref="I109:I114"/>
-    <mergeCell ref="J109:J114"/>
-    <mergeCell ref="K109:K114"/>
-    <mergeCell ref="L109:L114"/>
-    <mergeCell ref="Q115:Q120"/>
-    <mergeCell ref="H115:H120"/>
-    <mergeCell ref="I115:I120"/>
-    <mergeCell ref="J115:J120"/>
-    <mergeCell ref="K115:K120"/>
-    <mergeCell ref="L115:L120"/>
-    <mergeCell ref="M115:M120"/>
-    <mergeCell ref="N115:N120"/>
-    <mergeCell ref="O115:O120"/>
-    <mergeCell ref="P115:P120"/>
-    <mergeCell ref="C109:C114"/>
-    <mergeCell ref="D109:D114"/>
-    <mergeCell ref="E109:E114"/>
-    <mergeCell ref="F109:F114"/>
-    <mergeCell ref="G109:G114"/>
-    <mergeCell ref="M104:M108"/>
-    <mergeCell ref="N104:N108"/>
-    <mergeCell ref="O104:O108"/>
-    <mergeCell ref="P104:P108"/>
-    <mergeCell ref="M109:M114"/>
-    <mergeCell ref="N109:N114"/>
-    <mergeCell ref="O109:O114"/>
-    <mergeCell ref="P109:P114"/>
-    <mergeCell ref="Q104:Q108"/>
-    <mergeCell ref="H104:H108"/>
-    <mergeCell ref="I104:I108"/>
-    <mergeCell ref="J104:J108"/>
-    <mergeCell ref="K104:K108"/>
-    <mergeCell ref="L104:L108"/>
-    <mergeCell ref="C104:C108"/>
-    <mergeCell ref="D104:D108"/>
-    <mergeCell ref="E104:E108"/>
-    <mergeCell ref="F104:F108"/>
-    <mergeCell ref="G104:G108"/>
-    <mergeCell ref="M100:M103"/>
-    <mergeCell ref="N100:N103"/>
-    <mergeCell ref="O100:O103"/>
-    <mergeCell ref="P100:P103"/>
-    <mergeCell ref="Q100:Q103"/>
-    <mergeCell ref="H100:H103"/>
-    <mergeCell ref="I100:I103"/>
-    <mergeCell ref="J100:J103"/>
-    <mergeCell ref="K100:K103"/>
-    <mergeCell ref="L100:L103"/>
-    <mergeCell ref="C95:C99"/>
-    <mergeCell ref="D95:D99"/>
-    <mergeCell ref="E95:E99"/>
-    <mergeCell ref="F95:F99"/>
-    <mergeCell ref="G95:G99"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="E100:E103"/>
-    <mergeCell ref="F100:F103"/>
-    <mergeCell ref="G100:G103"/>
-    <mergeCell ref="Q90:Q94"/>
-    <mergeCell ref="H90:H94"/>
-    <mergeCell ref="I90:I94"/>
-    <mergeCell ref="J90:J94"/>
-    <mergeCell ref="K90:K94"/>
-    <mergeCell ref="L90:L94"/>
-    <mergeCell ref="Q95:Q99"/>
-    <mergeCell ref="H95:H99"/>
-    <mergeCell ref="I95:I99"/>
-    <mergeCell ref="J95:J99"/>
-    <mergeCell ref="K95:K99"/>
-    <mergeCell ref="L95:L99"/>
-    <mergeCell ref="M95:M99"/>
-    <mergeCell ref="N95:N99"/>
-    <mergeCell ref="O95:O99"/>
-    <mergeCell ref="P95:P99"/>
-    <mergeCell ref="C90:C94"/>
-    <mergeCell ref="D90:D94"/>
-    <mergeCell ref="E90:E94"/>
-    <mergeCell ref="F90:F94"/>
-    <mergeCell ref="G90:G94"/>
-    <mergeCell ref="M85:M89"/>
-    <mergeCell ref="N85:N89"/>
-    <mergeCell ref="O85:O89"/>
-    <mergeCell ref="P85:P89"/>
-    <mergeCell ref="M90:M94"/>
-    <mergeCell ref="N90:N94"/>
-    <mergeCell ref="O90:O94"/>
-    <mergeCell ref="P90:P94"/>
-    <mergeCell ref="Q85:Q89"/>
-    <mergeCell ref="H85:H89"/>
-    <mergeCell ref="I85:I89"/>
-    <mergeCell ref="J85:J89"/>
-    <mergeCell ref="K85:K89"/>
-    <mergeCell ref="L85:L89"/>
-    <mergeCell ref="C85:C89"/>
-    <mergeCell ref="D85:D89"/>
-    <mergeCell ref="E85:E89"/>
-    <mergeCell ref="F85:F89"/>
-    <mergeCell ref="G85:G89"/>
-    <mergeCell ref="M81:M84"/>
-    <mergeCell ref="N81:N84"/>
-    <mergeCell ref="O81:O84"/>
-    <mergeCell ref="P81:P84"/>
-    <mergeCell ref="Q81:Q84"/>
-    <mergeCell ref="H81:H84"/>
-    <mergeCell ref="I81:I84"/>
-    <mergeCell ref="J81:J84"/>
-    <mergeCell ref="K81:K84"/>
-    <mergeCell ref="L81:L84"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="E76:E80"/>
-    <mergeCell ref="F76:F80"/>
-    <mergeCell ref="G76:G80"/>
-    <mergeCell ref="C81:C84"/>
-    <mergeCell ref="D81:D84"/>
-    <mergeCell ref="E81:E84"/>
-    <mergeCell ref="F81:F84"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="Q70:Q74"/>
-    <mergeCell ref="H70:H74"/>
-    <mergeCell ref="I70:I74"/>
-    <mergeCell ref="J70:J74"/>
-    <mergeCell ref="K70:K74"/>
-    <mergeCell ref="L70:L74"/>
-    <mergeCell ref="Q76:Q80"/>
-    <mergeCell ref="H76:H80"/>
-    <mergeCell ref="I76:I80"/>
-    <mergeCell ref="J76:J80"/>
-    <mergeCell ref="K76:K80"/>
-    <mergeCell ref="L76:L80"/>
-    <mergeCell ref="M76:M80"/>
-    <mergeCell ref="N76:N80"/>
-    <mergeCell ref="O76:O80"/>
-    <mergeCell ref="P76:P80"/>
-    <mergeCell ref="I65:I69"/>
-    <mergeCell ref="J65:J69"/>
-    <mergeCell ref="K65:K69"/>
-    <mergeCell ref="L65:L69"/>
-    <mergeCell ref="M65:M69"/>
-    <mergeCell ref="N65:N69"/>
-    <mergeCell ref="O65:O69"/>
-    <mergeCell ref="P65:P69"/>
-    <mergeCell ref="Q65:Q69"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="P3:P7"/>
+    <mergeCell ref="O3:O7"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="D15:D20"/>
+    <mergeCell ref="F15:F20"/>
+    <mergeCell ref="G15:G20"/>
+    <mergeCell ref="H15:H20"/>
+    <mergeCell ref="I15:I20"/>
+    <mergeCell ref="J15:J20"/>
+    <mergeCell ref="K15:K20"/>
+    <mergeCell ref="L15:L20"/>
+    <mergeCell ref="M15:M20"/>
+    <mergeCell ref="E15:E20"/>
+    <mergeCell ref="N15:N20"/>
+    <mergeCell ref="O15:O20"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="Q3:Q7"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="D10:D14"/>
+    <mergeCell ref="E10:E14"/>
+    <mergeCell ref="F10:F14"/>
+    <mergeCell ref="G10:G14"/>
+    <mergeCell ref="H10:H14"/>
+    <mergeCell ref="I10:I14"/>
+    <mergeCell ref="J10:J14"/>
+    <mergeCell ref="K10:K14"/>
+    <mergeCell ref="L10:L14"/>
+    <mergeCell ref="M10:M14"/>
+    <mergeCell ref="N10:N14"/>
+    <mergeCell ref="J3:J7"/>
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="L3:L7"/>
+    <mergeCell ref="M3:M7"/>
+    <mergeCell ref="N3:N7"/>
+    <mergeCell ref="O10:O14"/>
+    <mergeCell ref="P10:P14"/>
+    <mergeCell ref="Q10:Q14"/>
+    <mergeCell ref="P15:P20"/>
+    <mergeCell ref="Q15:Q20"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="N21:N24"/>
+    <mergeCell ref="O21:O24"/>
+    <mergeCell ref="P21:P24"/>
+    <mergeCell ref="Q21:Q24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="K21:K24"/>
+    <mergeCell ref="L21:L24"/>
+    <mergeCell ref="M21:M24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="G25:G28"/>
+    <mergeCell ref="M25:M28"/>
+    <mergeCell ref="N25:N28"/>
+    <mergeCell ref="O25:O28"/>
+    <mergeCell ref="P25:P28"/>
+    <mergeCell ref="Q25:Q28"/>
+    <mergeCell ref="H25:H28"/>
+    <mergeCell ref="I25:I28"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="K25:K28"/>
+    <mergeCell ref="L25:L28"/>
+    <mergeCell ref="Q29:Q32"/>
+    <mergeCell ref="H29:H32"/>
+    <mergeCell ref="I29:I32"/>
+    <mergeCell ref="J29:J32"/>
+    <mergeCell ref="K29:K32"/>
+    <mergeCell ref="L29:L32"/>
+    <mergeCell ref="M29:M32"/>
+    <mergeCell ref="N29:N32"/>
+    <mergeCell ref="O29:O32"/>
+    <mergeCell ref="P29:P32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="D33:D37"/>
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="F33:F37"/>
+    <mergeCell ref="G33:G37"/>
+    <mergeCell ref="M33:M37"/>
+    <mergeCell ref="N33:N37"/>
+    <mergeCell ref="O33:O37"/>
+    <mergeCell ref="P33:P37"/>
+    <mergeCell ref="Q33:Q37"/>
+    <mergeCell ref="H33:H37"/>
+    <mergeCell ref="I33:I37"/>
+    <mergeCell ref="J33:J37"/>
+    <mergeCell ref="K33:K37"/>
+    <mergeCell ref="L33:L37"/>
+    <mergeCell ref="Q39:Q43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="K39:K43"/>
+    <mergeCell ref="L39:L43"/>
+    <mergeCell ref="M39:M43"/>
+    <mergeCell ref="N39:N43"/>
+    <mergeCell ref="O39:O43"/>
+    <mergeCell ref="P39:P43"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C44:C47"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="F44:F47"/>
+    <mergeCell ref="G44:G47"/>
+    <mergeCell ref="M44:M47"/>
+    <mergeCell ref="N44:N47"/>
+    <mergeCell ref="O44:O47"/>
+    <mergeCell ref="P44:P47"/>
+    <mergeCell ref="Q44:Q47"/>
+    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="J44:J47"/>
+    <mergeCell ref="K44:K47"/>
+    <mergeCell ref="L44:L47"/>
+    <mergeCell ref="Q48:Q52"/>
+    <mergeCell ref="H48:H52"/>
+    <mergeCell ref="I48:I52"/>
+    <mergeCell ref="J48:J52"/>
+    <mergeCell ref="K48:K52"/>
+    <mergeCell ref="L48:L52"/>
+    <mergeCell ref="C48:C52"/>
+    <mergeCell ref="D48:D52"/>
+    <mergeCell ref="E48:E52"/>
+    <mergeCell ref="F48:F52"/>
+    <mergeCell ref="G48:G52"/>
+    <mergeCell ref="C54:C58"/>
+    <mergeCell ref="D54:D58"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="F54:F58"/>
+    <mergeCell ref="G54:G58"/>
+    <mergeCell ref="M48:M52"/>
+    <mergeCell ref="N48:N52"/>
+    <mergeCell ref="O48:O52"/>
+    <mergeCell ref="P48:P52"/>
+    <mergeCell ref="M54:M58"/>
+    <mergeCell ref="N54:N58"/>
+    <mergeCell ref="O54:O58"/>
+    <mergeCell ref="P54:P58"/>
+    <mergeCell ref="Q54:Q58"/>
+    <mergeCell ref="H54:H58"/>
+    <mergeCell ref="I54:I58"/>
+    <mergeCell ref="J54:J58"/>
+    <mergeCell ref="K54:K58"/>
+    <mergeCell ref="L54:L58"/>
+    <mergeCell ref="Q60:Q64"/>
+    <mergeCell ref="I60:I64"/>
+    <mergeCell ref="J60:J64"/>
+    <mergeCell ref="K60:K64"/>
+    <mergeCell ref="L60:L64"/>
+    <mergeCell ref="M60:M64"/>
     <mergeCell ref="C60:C64"/>
     <mergeCell ref="N60:N64"/>
     <mergeCell ref="O60:O64"/>
@@ -15594,178 +15567,201 @@
     <mergeCell ref="F65:F69"/>
     <mergeCell ref="G65:G69"/>
     <mergeCell ref="H65:H69"/>
-    <mergeCell ref="Q54:Q58"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="I54:I58"/>
-    <mergeCell ref="J54:J58"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="L54:L58"/>
-    <mergeCell ref="Q60:Q64"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="J60:J64"/>
-    <mergeCell ref="K60:K64"/>
-    <mergeCell ref="L60:L64"/>
-    <mergeCell ref="M60:M64"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="M48:M52"/>
-    <mergeCell ref="N48:N52"/>
-    <mergeCell ref="O48:O52"/>
-    <mergeCell ref="P48:P52"/>
-    <mergeCell ref="M54:M58"/>
-    <mergeCell ref="N54:N58"/>
-    <mergeCell ref="O54:O58"/>
-    <mergeCell ref="P54:P58"/>
-    <mergeCell ref="Q48:Q52"/>
-    <mergeCell ref="H48:H52"/>
-    <mergeCell ref="I48:I52"/>
-    <mergeCell ref="J48:J52"/>
-    <mergeCell ref="K48:K52"/>
-    <mergeCell ref="L48:L52"/>
-    <mergeCell ref="C48:C52"/>
-    <mergeCell ref="D48:D52"/>
-    <mergeCell ref="E48:E52"/>
-    <mergeCell ref="F48:F52"/>
-    <mergeCell ref="G48:G52"/>
-    <mergeCell ref="M44:M47"/>
-    <mergeCell ref="N44:N47"/>
-    <mergeCell ref="O44:O47"/>
-    <mergeCell ref="P44:P47"/>
-    <mergeCell ref="Q44:Q47"/>
-    <mergeCell ref="H44:H47"/>
-    <mergeCell ref="I44:I47"/>
-    <mergeCell ref="J44:J47"/>
-    <mergeCell ref="K44:K47"/>
-    <mergeCell ref="L44:L47"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="D39:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C44:C47"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="E44:E47"/>
-    <mergeCell ref="F44:F47"/>
-    <mergeCell ref="G44:G47"/>
-    <mergeCell ref="Q39:Q43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="I39:I43"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="K39:K43"/>
-    <mergeCell ref="L39:L43"/>
-    <mergeCell ref="M39:M43"/>
-    <mergeCell ref="N39:N43"/>
-    <mergeCell ref="O39:O43"/>
-    <mergeCell ref="P39:P43"/>
-    <mergeCell ref="M33:M37"/>
-    <mergeCell ref="N33:N37"/>
-    <mergeCell ref="O33:O37"/>
-    <mergeCell ref="P33:P37"/>
-    <mergeCell ref="Q33:Q37"/>
-    <mergeCell ref="H33:H37"/>
-    <mergeCell ref="I33:I37"/>
-    <mergeCell ref="J33:J37"/>
-    <mergeCell ref="K33:K37"/>
-    <mergeCell ref="L33:L37"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="F29:F32"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="C33:C37"/>
-    <mergeCell ref="D33:D37"/>
-    <mergeCell ref="E33:E37"/>
-    <mergeCell ref="F33:F37"/>
-    <mergeCell ref="G33:G37"/>
-    <mergeCell ref="Q25:Q28"/>
-    <mergeCell ref="H25:H28"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="L25:L28"/>
-    <mergeCell ref="Q29:Q32"/>
-    <mergeCell ref="H29:H32"/>
-    <mergeCell ref="I29:I32"/>
-    <mergeCell ref="J29:J32"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="L29:L32"/>
-    <mergeCell ref="M29:M32"/>
-    <mergeCell ref="N29:N32"/>
-    <mergeCell ref="O29:O32"/>
-    <mergeCell ref="P29:P32"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="G25:G28"/>
-    <mergeCell ref="M25:M28"/>
-    <mergeCell ref="N25:N28"/>
-    <mergeCell ref="O25:O28"/>
-    <mergeCell ref="P25:P28"/>
-    <mergeCell ref="P15:P20"/>
-    <mergeCell ref="Q15:Q20"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="N21:N24"/>
-    <mergeCell ref="O21:O24"/>
-    <mergeCell ref="P21:P24"/>
-    <mergeCell ref="Q21:Q24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="K21:K24"/>
-    <mergeCell ref="L21:L24"/>
-    <mergeCell ref="M21:M24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="Q3:Q7"/>
-    <mergeCell ref="E3:E7"/>
-    <mergeCell ref="C10:C14"/>
-    <mergeCell ref="D10:D14"/>
-    <mergeCell ref="E10:E14"/>
-    <mergeCell ref="F10:F14"/>
-    <mergeCell ref="G10:G14"/>
-    <mergeCell ref="H10:H14"/>
-    <mergeCell ref="I10:I14"/>
-    <mergeCell ref="J10:J14"/>
-    <mergeCell ref="K10:K14"/>
-    <mergeCell ref="L10:L14"/>
-    <mergeCell ref="M10:M14"/>
-    <mergeCell ref="N10:N14"/>
-    <mergeCell ref="J3:J7"/>
-    <mergeCell ref="K3:K7"/>
-    <mergeCell ref="L3:L7"/>
-    <mergeCell ref="M3:M7"/>
-    <mergeCell ref="N3:N7"/>
-    <mergeCell ref="O10:O14"/>
-    <mergeCell ref="P10:P14"/>
-    <mergeCell ref="Q10:Q14"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="P3:P7"/>
-    <mergeCell ref="O3:O7"/>
-    <mergeCell ref="I3:I7"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="G3:G7"/>
-    <mergeCell ref="F3:F7"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="D15:D20"/>
-    <mergeCell ref="F15:F20"/>
-    <mergeCell ref="G15:G20"/>
-    <mergeCell ref="H15:H20"/>
-    <mergeCell ref="I15:I20"/>
-    <mergeCell ref="J15:J20"/>
-    <mergeCell ref="K15:K20"/>
-    <mergeCell ref="L15:L20"/>
-    <mergeCell ref="M15:M20"/>
-    <mergeCell ref="E15:E20"/>
-    <mergeCell ref="N15:N20"/>
-    <mergeCell ref="O15:O20"/>
-    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="I65:I69"/>
+    <mergeCell ref="J65:J69"/>
+    <mergeCell ref="K65:K69"/>
+    <mergeCell ref="L65:L69"/>
+    <mergeCell ref="M65:M69"/>
+    <mergeCell ref="N65:N69"/>
+    <mergeCell ref="O65:O69"/>
+    <mergeCell ref="P65:P69"/>
+    <mergeCell ref="Q65:Q69"/>
+    <mergeCell ref="Q70:Q74"/>
+    <mergeCell ref="H70:H74"/>
+    <mergeCell ref="I70:I74"/>
+    <mergeCell ref="J70:J74"/>
+    <mergeCell ref="K70:K74"/>
+    <mergeCell ref="L70:L74"/>
+    <mergeCell ref="Q76:Q80"/>
+    <mergeCell ref="H76:H80"/>
+    <mergeCell ref="I76:I80"/>
+    <mergeCell ref="J76:J80"/>
+    <mergeCell ref="K76:K80"/>
+    <mergeCell ref="L76:L80"/>
+    <mergeCell ref="M76:M80"/>
+    <mergeCell ref="N76:N80"/>
+    <mergeCell ref="O76:O80"/>
+    <mergeCell ref="P76:P80"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="E76:E80"/>
+    <mergeCell ref="F76:F80"/>
+    <mergeCell ref="G76:G80"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="D81:D84"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="F81:F84"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="M81:M84"/>
+    <mergeCell ref="N81:N84"/>
+    <mergeCell ref="O81:O84"/>
+    <mergeCell ref="P81:P84"/>
+    <mergeCell ref="Q81:Q84"/>
+    <mergeCell ref="H81:H84"/>
+    <mergeCell ref="I81:I84"/>
+    <mergeCell ref="J81:J84"/>
+    <mergeCell ref="K81:K84"/>
+    <mergeCell ref="L81:L84"/>
+    <mergeCell ref="Q85:Q89"/>
+    <mergeCell ref="H85:H89"/>
+    <mergeCell ref="I85:I89"/>
+    <mergeCell ref="J85:J89"/>
+    <mergeCell ref="K85:K89"/>
+    <mergeCell ref="L85:L89"/>
+    <mergeCell ref="C85:C89"/>
+    <mergeCell ref="D85:D89"/>
+    <mergeCell ref="E85:E89"/>
+    <mergeCell ref="F85:F89"/>
+    <mergeCell ref="G85:G89"/>
+    <mergeCell ref="C90:C94"/>
+    <mergeCell ref="D90:D94"/>
+    <mergeCell ref="E90:E94"/>
+    <mergeCell ref="F90:F94"/>
+    <mergeCell ref="G90:G94"/>
+    <mergeCell ref="M85:M89"/>
+    <mergeCell ref="N85:N89"/>
+    <mergeCell ref="O85:O89"/>
+    <mergeCell ref="P85:P89"/>
+    <mergeCell ref="M90:M94"/>
+    <mergeCell ref="N90:N94"/>
+    <mergeCell ref="O90:O94"/>
+    <mergeCell ref="P90:P94"/>
+    <mergeCell ref="Q90:Q94"/>
+    <mergeCell ref="H90:H94"/>
+    <mergeCell ref="I90:I94"/>
+    <mergeCell ref="J90:J94"/>
+    <mergeCell ref="K90:K94"/>
+    <mergeCell ref="L90:L94"/>
+    <mergeCell ref="Q95:Q99"/>
+    <mergeCell ref="H95:H99"/>
+    <mergeCell ref="I95:I99"/>
+    <mergeCell ref="J95:J99"/>
+    <mergeCell ref="K95:K99"/>
+    <mergeCell ref="L95:L99"/>
+    <mergeCell ref="M95:M99"/>
+    <mergeCell ref="N95:N99"/>
+    <mergeCell ref="O95:O99"/>
+    <mergeCell ref="P95:P99"/>
+    <mergeCell ref="C95:C99"/>
+    <mergeCell ref="D95:D99"/>
+    <mergeCell ref="E95:E99"/>
+    <mergeCell ref="F95:F99"/>
+    <mergeCell ref="G95:G99"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="E100:E103"/>
+    <mergeCell ref="F100:F103"/>
+    <mergeCell ref="G100:G103"/>
+    <mergeCell ref="M100:M103"/>
+    <mergeCell ref="N100:N103"/>
+    <mergeCell ref="O100:O103"/>
+    <mergeCell ref="P100:P103"/>
+    <mergeCell ref="Q100:Q103"/>
+    <mergeCell ref="H100:H103"/>
+    <mergeCell ref="I100:I103"/>
+    <mergeCell ref="J100:J103"/>
+    <mergeCell ref="K100:K103"/>
+    <mergeCell ref="L100:L103"/>
+    <mergeCell ref="Q104:Q108"/>
+    <mergeCell ref="H104:H108"/>
+    <mergeCell ref="I104:I108"/>
+    <mergeCell ref="J104:J108"/>
+    <mergeCell ref="K104:K108"/>
+    <mergeCell ref="L104:L108"/>
+    <mergeCell ref="C104:C108"/>
+    <mergeCell ref="D104:D108"/>
+    <mergeCell ref="E104:E108"/>
+    <mergeCell ref="F104:F108"/>
+    <mergeCell ref="G104:G108"/>
+    <mergeCell ref="C109:C114"/>
+    <mergeCell ref="D109:D114"/>
+    <mergeCell ref="E109:E114"/>
+    <mergeCell ref="F109:F114"/>
+    <mergeCell ref="G109:G114"/>
+    <mergeCell ref="M104:M108"/>
+    <mergeCell ref="N104:N108"/>
+    <mergeCell ref="O104:O108"/>
+    <mergeCell ref="P104:P108"/>
+    <mergeCell ref="M109:M114"/>
+    <mergeCell ref="N109:N114"/>
+    <mergeCell ref="O109:O114"/>
+    <mergeCell ref="P109:P114"/>
+    <mergeCell ref="Q109:Q114"/>
+    <mergeCell ref="H109:H114"/>
+    <mergeCell ref="I109:I114"/>
+    <mergeCell ref="J109:J114"/>
+    <mergeCell ref="K109:K114"/>
+    <mergeCell ref="L109:L114"/>
+    <mergeCell ref="Q115:Q120"/>
+    <mergeCell ref="H115:H120"/>
+    <mergeCell ref="I115:I120"/>
+    <mergeCell ref="J115:J120"/>
+    <mergeCell ref="K115:K120"/>
+    <mergeCell ref="L115:L120"/>
+    <mergeCell ref="M115:M120"/>
+    <mergeCell ref="N115:N120"/>
+    <mergeCell ref="O115:O120"/>
+    <mergeCell ref="P115:P120"/>
+    <mergeCell ref="C115:C120"/>
+    <mergeCell ref="D115:D120"/>
+    <mergeCell ref="E115:E120"/>
+    <mergeCell ref="F115:F120"/>
+    <mergeCell ref="G115:G120"/>
+    <mergeCell ref="C121:C126"/>
+    <mergeCell ref="D121:D126"/>
+    <mergeCell ref="E121:E126"/>
+    <mergeCell ref="F121:F126"/>
+    <mergeCell ref="G121:G126"/>
+    <mergeCell ref="M121:M126"/>
+    <mergeCell ref="N121:N126"/>
+    <mergeCell ref="O121:O126"/>
+    <mergeCell ref="P121:P126"/>
+    <mergeCell ref="Q121:Q126"/>
+    <mergeCell ref="H121:H126"/>
+    <mergeCell ref="I121:I126"/>
+    <mergeCell ref="J121:J126"/>
+    <mergeCell ref="K121:K126"/>
+    <mergeCell ref="L121:L126"/>
+    <mergeCell ref="H127:H131"/>
+    <mergeCell ref="I127:I131"/>
+    <mergeCell ref="J127:J131"/>
+    <mergeCell ref="K127:K131"/>
+    <mergeCell ref="L127:L131"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="E127:E131"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="G127:G131"/>
+    <mergeCell ref="M127:M131"/>
+    <mergeCell ref="N127:N131"/>
+    <mergeCell ref="O127:O131"/>
+    <mergeCell ref="P127:P131"/>
+    <mergeCell ref="M132:M136"/>
+    <mergeCell ref="N132:N136"/>
+    <mergeCell ref="O132:O136"/>
+    <mergeCell ref="P132:P136"/>
+    <mergeCell ref="Q127:Q131"/>
+    <mergeCell ref="Q132:Q136"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="I132:I136"/>
+    <mergeCell ref="J132:J136"/>
+    <mergeCell ref="K132:K136"/>
+    <mergeCell ref="L132:L136"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="D132:D136"/>
+    <mergeCell ref="E132:E136"/>
+    <mergeCell ref="F132:F136"/>
+    <mergeCell ref="G132:G136"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -15800,197 +15796,197 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8B1907-1808-45DB-89DB-D7AD15506F3A}">
   <dimension ref="B1:B38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
         <v>336</v>
       </c>
@@ -16006,126 +16002,126 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97597-49CE-4804-805A-84A20592BE98}">
   <dimension ref="A1:BC108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.7265625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.54296875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" style="1" customWidth="1"/>
     <col min="20" max="20" width="15" style="1" customWidth="1"/>
-    <col min="21" max="25" width="13.1796875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16.54296875" style="1" customWidth="1"/>
-    <col min="27" max="28" width="13.1796875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.81640625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.1796875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.453125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="30.7265625" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.54296875" style="1" customWidth="1"/>
-    <col min="38" max="43" width="16.7265625" style="1" customWidth="1"/>
-    <col min="44" max="45" width="13.26953125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="23.81640625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="22.54296875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="27.81640625" style="1" customWidth="1"/>
-    <col min="50" max="50" width="24.7265625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="22.7265625" style="1" customWidth="1"/>
-    <col min="52" max="55" width="13.26953125" style="1" customWidth="1"/>
-    <col min="56" max="16384" width="11.453125" style="1"/>
+    <col min="21" max="25" width="13.21875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16.5546875" style="1" customWidth="1"/>
+    <col min="27" max="28" width="13.21875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.21875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.44140625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="30.77734375" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" style="1" customWidth="1"/>
+    <col min="38" max="43" width="16.77734375" style="1" customWidth="1"/>
+    <col min="44" max="45" width="13.21875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="23.77734375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="22.5546875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="27.77734375" style="1" customWidth="1"/>
+    <col min="50" max="50" width="24.77734375" style="1" customWidth="1"/>
+    <col min="51" max="51" width="22.77734375" style="1" customWidth="1"/>
+    <col min="52" max="55" width="13.21875" style="1" customWidth="1"/>
+    <col min="56" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.5">
-      <c r="S1" s="162" t="s">
+      <c r="S1" s="163" t="s">
         <v>337</v>
       </c>
-      <c r="T1" s="162"/>
-      <c r="U1" s="162"/>
-      <c r="V1" s="162"/>
-      <c r="W1" s="162"/>
-      <c r="X1" s="162"/>
-      <c r="Y1" s="162"/>
-      <c r="Z1" s="162"/>
-      <c r="AA1" s="162"/>
-      <c r="AB1" s="162"/>
-      <c r="AC1" s="162"/>
-      <c r="AD1" s="162"/>
-      <c r="AE1" s="162"/>
-      <c r="AF1" s="162"/>
-      <c r="AG1" s="162"/>
+      <c r="T1" s="163"/>
+      <c r="U1" s="163"/>
+      <c r="V1" s="163"/>
+      <c r="W1" s="163"/>
+      <c r="X1" s="163"/>
+      <c r="Y1" s="163"/>
+      <c r="Z1" s="163"/>
+      <c r="AA1" s="163"/>
+      <c r="AB1" s="163"/>
+      <c r="AC1" s="163"/>
+      <c r="AD1" s="163"/>
+      <c r="AE1" s="163"/>
+      <c r="AF1" s="163"/>
+      <c r="AG1" s="163"/>
       <c r="AH1" s="14"/>
       <c r="AI1" s="14"/>
       <c r="AJ1" s="14"/>
-      <c r="AL1" s="162" t="s">
+      <c r="AL1" s="163" t="s">
         <v>338</v>
       </c>
-      <c r="AM1" s="162"/>
-      <c r="AN1" s="162"/>
-      <c r="AO1" s="162"/>
-      <c r="AP1" s="162"/>
-      <c r="AQ1" s="162"/>
+      <c r="AM1" s="163"/>
+      <c r="AN1" s="163"/>
+      <c r="AO1" s="163"/>
+      <c r="AP1" s="163"/>
+      <c r="AQ1" s="163"/>
       <c r="AR1" s="14"/>
       <c r="AS1" s="14"/>
-      <c r="AT1" s="162" t="s">
+      <c r="AT1" s="163" t="s">
         <v>339</v>
       </c>
-      <c r="AU1" s="162"/>
-      <c r="AV1" s="162"/>
-      <c r="AW1" s="162"/>
-      <c r="AX1" s="162"/>
-      <c r="AY1" s="162"/>
+      <c r="AU1" s="163"/>
+      <c r="AV1" s="163"/>
+      <c r="AW1" s="163"/>
+      <c r="AX1" s="163"/>
+      <c r="AY1" s="163"/>
       <c r="AZ1" s="14"/>
       <c r="BC1" s="14"/>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.5">
-      <c r="L2" s="162" t="s">
+      <c r="L2" s="163" t="s">
         <v>340</v>
       </c>
-      <c r="M2" s="162"/>
-      <c r="N2" s="162"/>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="S2" s="163" t="s">
+      <c r="M2" s="163"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="163"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="S2" s="164" t="s">
         <v>341</v>
       </c>
-      <c r="T2" s="163"/>
-      <c r="U2" s="163"/>
-      <c r="V2" s="163"/>
-      <c r="W2" s="163"/>
-      <c r="X2" s="163"/>
-      <c r="Y2" s="163" t="s">
+      <c r="T2" s="164"/>
+      <c r="U2" s="164"/>
+      <c r="V2" s="164"/>
+      <c r="W2" s="164"/>
+      <c r="X2" s="164"/>
+      <c r="Y2" s="164" t="s">
         <v>342</v>
       </c>
-      <c r="Z2" s="163"/>
-      <c r="AA2" s="163"/>
-      <c r="AB2" s="163"/>
-      <c r="AC2" s="163" t="s">
+      <c r="Z2" s="164"/>
+      <c r="AA2" s="164"/>
+      <c r="AB2" s="164"/>
+      <c r="AC2" s="164" t="s">
         <v>343</v>
       </c>
-      <c r="AD2" s="163"/>
-      <c r="AE2" s="163"/>
-      <c r="AF2" s="163"/>
-      <c r="AG2" s="163"/>
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="164"/>
+      <c r="AG2" s="164"/>
       <c r="AH2" s="14"/>
       <c r="AI2" s="14"/>
       <c r="AJ2" s="14"/>
-      <c r="AL2" s="162"/>
-      <c r="AM2" s="162"/>
-      <c r="AN2" s="162"/>
-      <c r="AO2" s="162"/>
-      <c r="AP2" s="162"/>
-      <c r="AQ2" s="162"/>
+      <c r="AL2" s="163"/>
+      <c r="AM2" s="163"/>
+      <c r="AN2" s="163"/>
+      <c r="AO2" s="163"/>
+      <c r="AP2" s="163"/>
+      <c r="AQ2" s="163"/>
       <c r="AR2" s="14"/>
       <c r="AS2" s="14"/>
       <c r="AT2" s="14"/>
@@ -16222,16 +16218,16 @@
       <c r="AG3" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="AL3" s="164" t="s">
+      <c r="AL3" s="162" t="s">
         <v>364</v>
       </c>
-      <c r="AM3" s="164"/>
-      <c r="AN3" s="164"/>
-      <c r="AO3" s="164" t="s">
+      <c r="AM3" s="162"/>
+      <c r="AN3" s="162"/>
+      <c r="AO3" s="162" t="s">
         <v>365</v>
       </c>
-      <c r="AP3" s="164"/>
-      <c r="AQ3" s="164"/>
+      <c r="AP3" s="162"/>
+      <c r="AQ3" s="162"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
@@ -21197,16 +21193,16 @@
     <sortCondition ref="AU5:AU66"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL3:AN3"/>
     <mergeCell ref="AO3:AQ3"/>
     <mergeCell ref="AT1:AY1"/>
     <mergeCell ref="S1:AG1"/>
     <mergeCell ref="AL1:AQ1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AL2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21263,21 +21259,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009AC520CAB569B54B8400FCA196E34CBB" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="928a0b24f7f0432e7883c4bfb1ed035d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54c3d757b4723c869c316db9996d807d" ns2:_="">
     <xsd:import namespace="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d"/>
@@ -21421,24 +21402,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1DB2B19-DC36-444C-A048-3E1CA129AB61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85901429-75D0-4AC6-828C-2813964A0F69}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00940B1D-0570-4DD1-9B1B-B7CB18B0E111}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21454,4 +21433,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85901429-75D0-4AC6-828C-2813964A0F69}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1DB2B19-DC36-444C-A048-3E1CA129AB61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>